--- a/public/downloads/underwriting-demo/sample-underwriting-pack.xlsx
+++ b/public/downloads/underwriting-demo/sample-underwriting-pack.xlsx
@@ -36888,11 +36888,11 @@
         </is>
       </c>
       <c r="B6" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A6,'T-12 Raw data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A6)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A6,'T-12 Raw data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C6" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A6,'T-12 Raw data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A6)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A6,'T-12 Raw data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D6" s="24">
@@ -36911,11 +36911,11 @@
         </is>
       </c>
       <c r="B7" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A7,'T-12 Raw data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A7)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A7,'T-12 Raw data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C7" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A7,'T-12 Raw data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A7)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A7,'T-12 Raw data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D7" s="24">
@@ -36934,11 +36934,11 @@
         </is>
       </c>
       <c r="B8" s="20">
-        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A8)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A8,'T-12 Raw data'!$O$6:$O$135),B6+B7)</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A8)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A8,'T-12 Raw data'!$O$6:$O$135),IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A6)+COUNTIF('T-12 Raw data'!$B$6:$B$135,$A7)&gt;0,IF(B6="",0,B6)+IF(B7="",0,B7),""))</f>
         <v/>
       </c>
       <c r="C8" s="20">
-        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A8)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A8,'T-12 Raw data'!$P$6:$P$135)*4,(C6+C7))</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A8)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A8,'T-12 Raw data'!$P$6:$P$135)*4,IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A6)+COUNTIF('T-12 Raw data'!$B$6:$B$135,$A7)&gt;0,IF(C6="",0,C6)+IF(C7="",0,C7),""))</f>
         <v/>
       </c>
       <c r="D8" s="20">
@@ -36957,11 +36957,11 @@
         </is>
       </c>
       <c r="B9" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A9,'T-12 Raw data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A9)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A9,'T-12 Raw data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C9" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A9,'T-12 Raw data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A9)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A9,'T-12 Raw data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D9" s="24">
@@ -36980,11 +36980,11 @@
         </is>
       </c>
       <c r="B10" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A10,'T-12 Raw data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A10)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A10,'T-12 Raw data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C10" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A10,'T-12 Raw data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A10)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A10,'T-12 Raw data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D10" s="24">
@@ -37003,11 +37003,11 @@
         </is>
       </c>
       <c r="B11" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A11,'T-12 Raw data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A11)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A11,'T-12 Raw data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C11" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A11,'T-12 Raw data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A11)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A11,'T-12 Raw data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D11" s="24">
@@ -37026,11 +37026,11 @@
         </is>
       </c>
       <c r="B12" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A12,'T-12 Raw data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A12)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A12,'T-12 Raw data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C12" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A12,'T-12 Raw data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A12)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A12,'T-12 Raw data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D12" s="24">
@@ -37049,11 +37049,11 @@
         </is>
       </c>
       <c r="B13" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A13,'T-12 Raw data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A13)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A13,'T-12 Raw data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C13" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A13,'T-12 Raw data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A13)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A13,'T-12 Raw data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D13" s="24">
@@ -37072,11 +37072,11 @@
         </is>
       </c>
       <c r="B14" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A14,'T-12 Raw data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A14)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A14,'T-12 Raw data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C14" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A14,'T-12 Raw data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A14)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A14,'T-12 Raw data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D14" s="24">
@@ -37095,11 +37095,11 @@
         </is>
       </c>
       <c r="B15" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A15,'T-12 Raw data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A15)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A15,'T-12 Raw data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C15" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A15,'T-12 Raw data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A15)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A15,'T-12 Raw data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D15" s="24">
@@ -37141,11 +37141,11 @@
         </is>
       </c>
       <c r="B17" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A17,'T-12 Raw data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A17)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A17,'T-12 Raw data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C17" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A17,'T-12 Raw data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A17)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A17,'T-12 Raw data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D17" s="24">
@@ -37164,11 +37164,11 @@
         </is>
       </c>
       <c r="B18" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A18,'T-12 Raw data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A18)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A18,'T-12 Raw data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C18" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A18,'T-12 Raw data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A18)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A18,'T-12 Raw data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D18" s="24">
@@ -37187,11 +37187,11 @@
         </is>
       </c>
       <c r="B19" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A19,'T-12 Raw data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A19)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A19,'T-12 Raw data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C19" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A19,'T-12 Raw data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A19)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A19,'T-12 Raw data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D19" s="24">
@@ -37210,11 +37210,11 @@
         </is>
       </c>
       <c r="B20" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A20,'T-12 Raw data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A20)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A20,'T-12 Raw data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C20" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A20,'T-12 Raw data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A20)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A20,'T-12 Raw data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D20" s="24">
@@ -37233,11 +37233,11 @@
         </is>
       </c>
       <c r="B21" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A21,'T-12 Raw data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A21)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A21,'T-12 Raw data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C21" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A21,'T-12 Raw data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A21)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A21,'T-12 Raw data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D21" s="24">
@@ -37256,11 +37256,11 @@
         </is>
       </c>
       <c r="B22" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A22,'T-12 Raw data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A22)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A22,'T-12 Raw data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C22" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A22,'T-12 Raw data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A22)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A22,'T-12 Raw data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D22" s="24">
@@ -37279,11 +37279,11 @@
         </is>
       </c>
       <c r="B23" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A23,'T-12 Raw data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A23)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A23,'T-12 Raw data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C23" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A23,'T-12 Raw data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A23)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A23,'T-12 Raw data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D23" s="24">
@@ -37302,11 +37302,11 @@
         </is>
       </c>
       <c r="B24" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A24,'T-12 Raw data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A24)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A24,'T-12 Raw data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C24" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A24,'T-12 Raw data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A24)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A24,'T-12 Raw data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D24" s="24">
@@ -37325,11 +37325,11 @@
         </is>
       </c>
       <c r="B25" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A25,'T-12 Raw data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A25)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A25,'T-12 Raw data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C25" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A25,'T-12 Raw data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A25)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A25,'T-12 Raw data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D25" s="24">
@@ -37348,11 +37348,11 @@
         </is>
       </c>
       <c r="B26" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A26,'T-12 Raw data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A26)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A26,'T-12 Raw data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C26" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A26,'T-12 Raw data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A26)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A26,'T-12 Raw data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D26" s="24">
@@ -37371,11 +37371,11 @@
         </is>
       </c>
       <c r="B27" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A27,'T-12 Raw data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A27)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A27,'T-12 Raw data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C27" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A27,'T-12 Raw data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A27)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A27,'T-12 Raw data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D27" s="24">
@@ -37394,11 +37394,11 @@
         </is>
       </c>
       <c r="B28" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A28,'T-12 Raw data'!$O$6:$O$135)</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A28)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A28,'T-12 Raw data'!$O$6:$O$135),"")</f>
         <v/>
       </c>
       <c r="C28" s="24">
-        <f>SUMIF('T-12 Raw data'!$B$6:$B$135,$A28,'T-12 Raw data'!$P$6:$P$135)*4</f>
+        <f>IF(COUNTIF('T-12 Raw data'!$B$6:$B$135,$A28)&gt;0,SUMIF('T-12 Raw data'!$B$6:$B$135,$A28,'T-12 Raw data'!$P$6:$P$135)*4,"")</f>
         <v/>
       </c>
       <c r="D28" s="24">
@@ -38202,7 +38202,7 @@
         <v>6166658.92</v>
       </c>
       <c r="D7" s="7">
-        <f>IFERROR(B7-C7,"")</f>
+        <f>IF(C7="","",IF(B7="",0,B7)-C7)</f>
         <v/>
       </c>
       <c r="E7" s="12">
@@ -38225,7 +38225,7 @@
         <v>2054907.91</v>
       </c>
       <c r="D8" s="7">
-        <f>IFERROR(B8-C8,"")</f>
+        <f>IF(C8="","",IF(B8="",0,B8)-C8)</f>
         <v/>
       </c>
       <c r="E8" s="12">
@@ -38248,7 +38248,7 @@
         <v>4111751.01</v>
       </c>
       <c r="D9" s="7">
-        <f>IFERROR(B9-C9,"")</f>
+        <f>IF(C9="","",IF(B9="",0,B9)-C9)</f>
         <v/>
       </c>
       <c r="E9" s="12">
@@ -38269,7 +38269,7 @@
       </c>
       <c r="C10" s="12" t="n"/>
       <c r="D10" s="7">
-        <f>IFERROR(B10-C10,"")</f>
+        <f>IF(C10="","",IF(B10="",0,B10)-C10)</f>
         <v/>
       </c>
       <c r="E10" s="12">
@@ -38294,7 +38294,7 @@
       </c>
       <c r="C11" s="12" t="n"/>
       <c r="D11" s="7">
-        <f>IFERROR(B11-C11,"")</f>
+        <f>IF(C11="","",IF(B11="",0,B11)-C11)</f>
         <v/>
       </c>
       <c r="E11" s="12">
@@ -38321,7 +38321,7 @@
         <v>337165.1</v>
       </c>
       <c r="D12" s="7">
-        <f>IFERROR(B12-C12,"")</f>
+        <f>IF(C12="","",IF(B12="",0,B12)-C12)</f>
         <v/>
       </c>
       <c r="E12" s="12">

--- a/public/downloads/underwriting-demo/sample-underwriting-pack.xlsx
+++ b/public/downloads/underwriting-demo/sample-underwriting-pack.xlsx
@@ -354,7 +354,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>In-place vs new-lease vs market rent for model</a:t>
+              <a:t>In-place vs new move-in vs market rent for model</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -393,30 +393,6 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'RR Analysis'!F8</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'RR Analysis'!$B$9:$B$18</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'RR Analysis'!$F$9:$F$18</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
               <f>'RR Analysis'!H8</f>
             </strRef>
           </tx>
@@ -433,6 +409,30 @@
           <val>
             <numRef>
               <f>'RR Analysis'!$H$9:$H$18</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'RR Analysis'!J8</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'RR Analysis'!$B$9:$B$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'RR Analysis'!$J$9:$J$18</f>
             </numRef>
           </val>
         </ser>
@@ -491,7 +491,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>10</col>
+      <col>12</col>
       <colOff>0</colOff>
       <row>8</row>
       <rowOff>0</rowOff>
@@ -513,7 +513,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>10</col>
+      <col>12</col>
       <colOff>0</colOff>
       <row>24</row>
       <rowOff>0</rowOff>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>New-lease average where the plan has new leases in the lookback window, otherwise in-place. Never a blend of new and renewal.</t>
+          <t>New move-in rent (residents who moved in inside the lookback window, by move-in date) where the plan has one, otherwise in-place (in-place outright when the roll has no usable lease start or move-in date). Never a blend of new and renewal.</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -1833,7 +1833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1842,9 +1842,11 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="34" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1939,20 +1941,30 @@
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>NEW LEASE rent</t>
+          <t>LEASES SIGNED rent</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>New #</t>
+          <t>Signed #</t>
         </is>
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
+          <t>NEW MOVE-IN rent</t>
+        </is>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>Move-In #</t>
+        </is>
+      </c>
+      <c r="J8" s="14" t="inlineStr">
+        <is>
           <t>Market rent for model</t>
         </is>
       </c>
-      <c r="I8" s="14" t="inlineStr">
+      <c r="K8" s="14" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
@@ -1980,17 +1992,23 @@
         <v/>
       </c>
       <c r="F9" s="7" t="n">
-        <v>1225.222222222222</v>
+        <v>1315.763157894737</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>27</v>
+        <v>76</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>1225.222222222222</v>
       </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>New leases (n=27)</t>
+      <c r="I9" s="7" t="n">
+        <v>27</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>1225.222222222222</v>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>New move-ins (n=27)</t>
         </is>
       </c>
     </row>
@@ -2016,17 +2034,23 @@
         <v/>
       </c>
       <c r="F10" s="7" t="n">
-        <v>1167.961538461539</v>
+        <v>1295.333333333333</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>26</v>
+        <v>66</v>
       </c>
       <c r="H10" s="7" t="n">
         <v>1167.961538461539</v>
       </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>New leases (n=26)</t>
+      <c r="I10" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>1167.961538461539</v>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>New move-ins (n=26)</t>
         </is>
       </c>
     </row>
@@ -2052,17 +2076,23 @@
         <v/>
       </c>
       <c r="F11" s="7" t="n">
-        <v>1355.214285714286</v>
+        <v>1494.53125</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="H11" s="7" t="n">
         <v>1355.214285714286</v>
       </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>New leases (n=14)</t>
+      <c r="I11" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>1355.214285714286</v>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>New move-ins (n=14)</t>
         </is>
       </c>
     </row>
@@ -2088,17 +2118,23 @@
         <v/>
       </c>
       <c r="F12" s="7" t="n">
-        <v>1322.75</v>
+        <v>1390.833333333333</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="H12" s="7" t="n">
         <v>1322.75</v>
       </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>New leases (n=12)</t>
+      <c r="I12" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="J12" s="7" t="n">
+        <v>1322.75</v>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>New move-ins (n=12)</t>
         </is>
       </c>
     </row>
@@ -2124,17 +2160,23 @@
         <v/>
       </c>
       <c r="F13" s="7" t="n">
-        <v>1533.307692307692</v>
+        <v>1652.377777777778</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="H13" s="7" t="n">
         <v>1533.307692307692</v>
       </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>New leases (n=13)</t>
+      <c r="I13" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>1533.307692307692</v>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>New move-ins (n=13)</t>
         </is>
       </c>
     </row>
@@ -2160,17 +2202,23 @@
         <v/>
       </c>
       <c r="F14" s="7" t="n">
-        <v>1422.4</v>
+        <v>1565.735294117647</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="H14" s="7" t="n">
         <v>1422.4</v>
       </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>New leases (n=15)</t>
+      <c r="I14" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="J14" s="7" t="n">
+        <v>1422.4</v>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>New move-ins (n=15)</t>
         </is>
       </c>
     </row>
@@ -2196,17 +2244,23 @@
         <v/>
       </c>
       <c r="F15" s="7" t="n">
-        <v>1687</v>
+        <v>1760.6</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H15" s="7" t="n">
         <v>1687</v>
       </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>New leases (n=3)</t>
+      <c r="I15" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>1687</v>
+      </c>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>New move-ins (n=3)</t>
         </is>
       </c>
     </row>
@@ -2232,17 +2286,23 @@
         <v/>
       </c>
       <c r="F16" s="7" t="n">
-        <v>1853.25</v>
+        <v>1915.714285714286</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H16" s="7" t="n">
         <v>1853.25</v>
       </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>New leases (n=4)</t>
+      <c r="I16" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J16" s="7" t="n">
+        <v>1853.25</v>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>New move-ins (n=4)</t>
         </is>
       </c>
     </row>
@@ -2268,17 +2328,23 @@
         <v/>
       </c>
       <c r="F17" s="7" t="n">
-        <v>1948</v>
+        <v>2103</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" s="7" t="n">
         <v>1948</v>
       </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>New leases (n=1)</t>
+      <c r="I17" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" s="7" t="n">
+        <v>1948</v>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>New move-ins (n=1)</t>
         </is>
       </c>
     </row>
@@ -2303,16 +2369,22 @@
         <f>IFERROR(AVERAGEIFS('RR Raw data'!$J$6:$J$339,'RR Raw data'!$B$6:$B$339,$B18,'RR Raw data'!$F$6:$F$339,"Occupied"),"")</f>
         <v/>
       </c>
-      <c r="F18" s="12" t="n"/>
+      <c r="F18" s="7" t="n">
+        <v>2288</v>
+      </c>
       <c r="G18" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" s="12" t="n"/>
+      <c r="I18" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="7" t="n">
+      <c r="J18" s="7" t="n">
         <v>2288</v>
       </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>In-place — no new leases in window</t>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>In-place — no new move-ins in window</t>
         </is>
       </c>
     </row>
@@ -2335,16 +2407,27 @@
         <f>IFERROR(AVERAGEIFS('RR Raw data'!$J$6:$J$339,'RR Raw data'!$F$6:$F$339,"Occupied"),"")</f>
         <v/>
       </c>
-      <c r="F20" s="19" t="n"/>
+      <c r="F20" s="20">
+        <f>IFERROR(SUMPRODUCT($F$9:$F$18,$G$9:$G$18)/SUM($G$9:$G$18),"")</f>
+        <v/>
+      </c>
       <c r="G20" s="20">
         <f>SUM(G9:G18)</f>
         <v/>
       </c>
       <c r="H20" s="20">
-        <f>IFERROR(SUMPRODUCT($D$9:$D$18,$H$9:$H$18)/SUM($D$9:$D$18),"")</f>
-        <v/>
-      </c>
-      <c r="I20" s="18" t="inlineStr">
+        <f>IFERROR(SUMPRODUCT($H$9:$H$18,$I$9:$I$18)/SUM($I$9:$I$18),"")</f>
+        <v/>
+      </c>
+      <c r="I20" s="20">
+        <f>SUM(I9:I18)</f>
+        <v/>
+      </c>
+      <c r="J20" s="20">
+        <f>IFERROR(SUMPRODUCT($D$9:$D$18,$J$9:$J$18)/SUM($D$9:$D$18),"")</f>
+        <v/>
+      </c>
+      <c r="K20" s="18" t="inlineStr">
         <is>
           <t>Weighted by unit count.</t>
         </is>
@@ -2512,14 +2595,14 @@
     <row r="39" ht="46" customHeight="1">
       <c r="A39" s="28" t="inlineStr">
         <is>
-          <t>Market rent for model is the new-lease average where the plan has new leases inside the lookback window, and the in-place average otherwise — the Basis column says which, per plan. No column on this tab blends lease types, and none of them claims a renewal rent: a roll cannot measure one. A blended "recently leased" average is a renewal average wearing a market-rent label, and on a stabilised property renewals outnumber new leases roughly three to two over twelve months.</t>
+          <t>Market rent for model is the NEW MOVE-IN rent — residents whose move-in date falls inside the lookback window, whatever their lease type — where the plan has one, and the in-place average otherwise; the Basis column says which, per plan; a roll with no usable lease start or move-in date reads in-place outright. LEASES SIGNED is every classified lease started in the window, new and renewal together, and is shown for context only: a blend of new and renewal rents is a renewal average wearing a market-rent label, and on a stabilised property renewals outnumber new leases roughly three to two over twelve months.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="32" customHeight="1">
       <c r="A40" s="28" t="inlineStr">
         <is>
-          <t>New-lease rent, its count and market rent for model are values rather than formulas on purpose: they depend on the window above, and a formula would re-window itself the day this file is reopened. Unit count, average SF and in-place rent are live formulas over the Rent Roll tab.</t>
+          <t>The signed and move-in rents, their counts and market rent for model are values rather than formulas on purpose: they depend on the window above, and a formula would re-window itself the day this file is reopened. Unit count, average SF and in-place rent are live formulas over the Rent Roll tab.</t>
         </is>
       </c>
     </row>
@@ -3447,7 +3530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H237"/>
+  <dimension ref="A1:H239"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3505,7 +3588,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7">
@@ -5104,7 +5187,7 @@
       </c>
       <c r="D51" s="26" t="inlineStr">
         <is>
-          <t>The rent to underwrite: new-lease average where the plan has new leases in the lookback window, otherwise in-place. Never a blend of new and renewal.</t>
+          <t>The rent to underwrite: new move-in rent (residents who moved in inside the lookback window, by move-in date) where the plan has one, otherwise in-place. Requires a usable lease start AND move-in date on the roll; without either it is in-place outright. Never a blend of new and renewal.</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -8986,7 +9069,7 @@
       </c>
       <c r="B149" s="5" t="inlineStr">
         <is>
-          <t>plan_new_lease_rent</t>
+          <t>plan_signed_rent</t>
         </is>
       </c>
       <c r="C149" s="5" t="inlineStr">
@@ -8996,7 +9079,7 @@
       </c>
       <c r="D149" s="26" t="inlineStr">
         <is>
-          <t>Average rent on the plan's new leases inside the lookback window. Renewals are excluded.</t>
+          <t>Average rent on every priced, CLASSIFIED lease start (new, renewal or month-to-month) inside the lookback window; a lease the roll cannot classify is left out, so this can undercount. Context only: a blend never feeds the model.</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr">
@@ -9006,7 +9089,7 @@
       </c>
       <c r="F149" s="26" t="inlineStr">
         <is>
-          <t>New-lease rent evidence</t>
+          <t>Leases signed</t>
         </is>
       </c>
       <c r="G149" s="26" t="inlineStr">
@@ -9028,7 +9111,7 @@
       </c>
       <c r="B150" s="5" t="inlineStr">
         <is>
-          <t>plan_new_lease_count</t>
+          <t>plan_signed_count</t>
         </is>
       </c>
       <c r="C150" s="5" t="inlineStr">
@@ -9038,7 +9121,7 @@
       </c>
       <c r="D150" s="26" t="inlineStr">
         <is>
-          <t>How many new leases the average rests on. A thin count is visible rather than implied.</t>
+          <t>How many leases were signed in the window. n/a where the roll has no usable lease-start or move-in date.</t>
         </is>
       </c>
       <c r="E150" s="5" t="inlineStr">
@@ -9070,7 +9153,7 @@
       </c>
       <c r="B151" s="5" t="inlineStr">
         <is>
-          <t>plan_market_rent_for_model</t>
+          <t>plan_movein_rent</t>
         </is>
       </c>
       <c r="C151" s="5" t="inlineStr">
@@ -9080,7 +9163,7 @@
       </c>
       <c r="D151" s="26" t="inlineStr">
         <is>
-          <t>The plan's rent to underwrite: new-lease average where one exists, otherwise in-place. This is the column a financial model consumes.</t>
+          <t>Average rent of residents whose move-in date falls inside the lookback window, whatever their lease type.</t>
         </is>
       </c>
       <c r="E151" s="5" t="inlineStr">
@@ -9090,7 +9173,7 @@
       </c>
       <c r="F151" s="26" t="inlineStr">
         <is>
-          <t>Unit-mix market rent</t>
+          <t>New move-in rent evidence</t>
         </is>
       </c>
       <c r="G151" s="26" t="inlineStr">
@@ -9112,17 +9195,17 @@
       </c>
       <c r="B152" s="5" t="inlineStr">
         <is>
-          <t>plan_market_rent_basis</t>
+          <t>plan_movein_count</t>
         </is>
       </c>
       <c r="C152" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D152" s="26" t="inlineStr">
         <is>
-          <t>Which of the two fired, stated per plan.</t>
+          <t>How many move-ins the average rests on. A thin count is visible rather than implied.</t>
         </is>
       </c>
       <c r="E152" s="5" t="inlineStr">
@@ -9132,7 +9215,7 @@
       </c>
       <c r="F152" s="26" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Sample size</t>
         </is>
       </c>
       <c r="G152" s="26" t="inlineStr">
@@ -9147,102 +9230,102 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="4" t="inlineStr">
-        <is>
-          <t>Rent roll — totals</t>
-        </is>
-      </c>
-      <c r="B153" s="4" t="n"/>
-      <c r="C153" s="4" t="n"/>
-      <c r="D153" s="4" t="n"/>
-      <c r="E153" s="4" t="n"/>
-      <c r="F153" s="4" t="n"/>
-      <c r="G153" s="4" t="n"/>
-      <c r="H153" s="4" t="n"/>
+      <c r="A153" s="5" t="inlineStr">
+        <is>
+          <t>Rent roll — plan</t>
+        </is>
+      </c>
+      <c r="B153" s="5" t="inlineStr">
+        <is>
+          <t>plan_market_rent_for_model</t>
+        </is>
+      </c>
+      <c r="C153" s="5" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D153" s="26" t="inlineStr">
+        <is>
+          <t>The plan's rent to underwrite: new move-in rent where one exists, otherwise in-place. This is the column a financial model consumes.</t>
+        </is>
+      </c>
+      <c r="E153" s="5" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F153" s="26" t="inlineStr">
+        <is>
+          <t>Unit-mix market rent</t>
+        </is>
+      </c>
+      <c r="G153" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H153" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="5" t="inlineStr">
         <is>
+          <t>Rent roll — plan</t>
+        </is>
+      </c>
+      <c r="B154" s="5" t="inlineStr">
+        <is>
+          <t>plan_market_rent_basis</t>
+        </is>
+      </c>
+      <c r="C154" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D154" s="26" t="inlineStr">
+        <is>
+          <t>Which of the two fired, stated per plan.</t>
+        </is>
+      </c>
+      <c r="E154" s="5" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F154" s="26" t="inlineStr">
+        <is>
+          <t>Reference only — not a model input</t>
+        </is>
+      </c>
+      <c r="G154" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H154" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
           <t>Rent roll — totals</t>
         </is>
       </c>
-      <c r="B154" s="5" t="inlineStr">
-        <is>
-          <t>reconciliation_verdict</t>
-        </is>
-      </c>
-      <c r="C154" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D154" s="26" t="inlineStr">
-        <is>
-          <t>PASS, FAIL or NOT CHECKED: the unit count (tolerance 0) and the export's stated market-rent total (tolerance $1) against what the export states, every duplicate row retaining the in-place lease, and no rent-readback mismatch.</t>
-        </is>
-      </c>
-      <c r="E154" s="5" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F154" s="26" t="inlineStr">
-        <is>
-          <t>Gate — the pack is partial until PASS</t>
-        </is>
-      </c>
-      <c r="G154" s="26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H154" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="5" t="inlineStr">
-        <is>
-          <t>Rent roll — totals</t>
-        </is>
-      </c>
-      <c r="B155" s="5" t="inlineStr">
-        <is>
-          <t>total_units</t>
-        </is>
-      </c>
-      <c r="C155" s="5" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D155" s="26" t="inlineStr">
-        <is>
-          <t>Units on the roll.</t>
-        </is>
-      </c>
-      <c r="E155" s="5" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F155" s="26" t="inlineStr">
-        <is>
-          <t>Unit count cross-check</t>
-        </is>
-      </c>
-      <c r="G155" s="26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H155" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="B155" s="4" t="n"/>
+      <c r="C155" s="4" t="n"/>
+      <c r="D155" s="4" t="n"/>
+      <c r="E155" s="4" t="n"/>
+      <c r="F155" s="4" t="n"/>
+      <c r="G155" s="4" t="n"/>
+      <c r="H155" s="4" t="n"/>
     </row>
     <row r="156">
       <c r="A156" s="5" t="inlineStr">
@@ -9252,17 +9335,17 @@
       </c>
       <c r="B156" s="5" t="inlineStr">
         <is>
-          <t>occupied_units</t>
+          <t>reconciliation_verdict</t>
         </is>
       </c>
       <c r="C156" s="5" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D156" s="26" t="inlineStr">
         <is>
-          <t>Occupied units.</t>
+          <t>PASS, FAIL or NOT CHECKED: the unit count (tolerance 0) and the export's stated market-rent total (tolerance $1) against what the export states, every duplicate row retaining the in-place lease, and no rent-readback mismatch.</t>
         </is>
       </c>
       <c r="E156" s="5" t="inlineStr">
@@ -9272,7 +9355,7 @@
       </c>
       <c r="F156" s="26" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Gate — the pack is partial until PASS</t>
         </is>
       </c>
       <c r="G156" s="26" t="inlineStr">
@@ -9294,7 +9377,7 @@
       </c>
       <c r="B157" s="5" t="inlineStr">
         <is>
-          <t>vacant_units</t>
+          <t>total_units</t>
         </is>
       </c>
       <c r="C157" s="5" t="inlineStr">
@@ -9304,7 +9387,7 @@
       </c>
       <c r="D157" s="26" t="inlineStr">
         <is>
-          <t>Vacant units.</t>
+          <t>Units on the roll.</t>
         </is>
       </c>
       <c r="E157" s="5" t="inlineStr">
@@ -9314,7 +9397,7 @@
       </c>
       <c r="F157" s="26" t="inlineStr">
         <is>
-          <t>Occupancy</t>
+          <t>Unit count cross-check</t>
         </is>
       </c>
       <c r="G157" s="26" t="inlineStr">
@@ -9336,17 +9419,17 @@
       </c>
       <c r="B158" s="5" t="inlineStr">
         <is>
-          <t>occupancy</t>
+          <t>occupied_units</t>
         </is>
       </c>
       <c r="C158" s="5" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D158" s="26" t="inlineStr">
         <is>
-          <t>Occupied over total.</t>
+          <t>Occupied units.</t>
         </is>
       </c>
       <c r="E158" s="5" t="inlineStr">
@@ -9356,7 +9439,7 @@
       </c>
       <c r="F158" s="26" t="inlineStr">
         <is>
-          <t>Vacancy assumption</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="G158" s="26" t="inlineStr">
@@ -9378,17 +9461,17 @@
       </c>
       <c r="B159" s="5" t="inlineStr">
         <is>
-          <t>vacancy</t>
+          <t>vacant_units</t>
         </is>
       </c>
       <c r="C159" s="5" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D159" s="26" t="inlineStr">
         <is>
-          <t>One less occupancy. The physical-vacancy input.</t>
+          <t>Vacant units.</t>
         </is>
       </c>
       <c r="E159" s="5" t="inlineStr">
@@ -9398,7 +9481,7 @@
       </c>
       <c r="F159" s="26" t="inlineStr">
         <is>
-          <t>Vacancy assumption</t>
+          <t>Occupancy</t>
         </is>
       </c>
       <c r="G159" s="26" t="inlineStr">
@@ -9420,17 +9503,17 @@
       </c>
       <c r="B160" s="5" t="inlineStr">
         <is>
-          <t>wavg_in_place_rent</t>
+          <t>occupancy</t>
         </is>
       </c>
       <c r="C160" s="5" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D160" s="26" t="inlineStr">
         <is>
-          <t>Unit-weighted in-place rent across the property.</t>
+          <t>Occupied over total.</t>
         </is>
       </c>
       <c r="E160" s="5" t="inlineStr">
@@ -9440,7 +9523,7 @@
       </c>
       <c r="F160" s="26" t="inlineStr">
         <is>
-          <t>In-place rent</t>
+          <t>Vacancy assumption</t>
         </is>
       </c>
       <c r="G160" s="26" t="inlineStr">
@@ -9462,17 +9545,17 @@
       </c>
       <c r="B161" s="5" t="inlineStr">
         <is>
-          <t>wavg_market_rent_for_model</t>
+          <t>vacancy</t>
         </is>
       </c>
       <c r="C161" s="5" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D161" s="26" t="inlineStr">
         <is>
-          <t>Unit-weighted market rent for model across the property.</t>
+          <t>One less occupancy. The physical-vacancy input.</t>
         </is>
       </c>
       <c r="E161" s="5" t="inlineStr">
@@ -9482,7 +9565,7 @@
       </c>
       <c r="F161" s="26" t="inlineStr">
         <is>
-          <t>Market rent</t>
+          <t>Vacancy assumption</t>
         </is>
       </c>
       <c r="G161" s="26" t="inlineStr">
@@ -9504,17 +9587,17 @@
       </c>
       <c r="B162" s="5" t="inlineStr">
         <is>
-          <t>annualized_turnover</t>
+          <t>wavg_in_place_rent</t>
         </is>
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D162" s="26" t="inlineStr">
         <is>
-          <t>Move-ins inside the lookback window, annualized against unit count.</t>
+          <t>Unit-weighted in-place rent across the property.</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -9524,7 +9607,7 @@
       </c>
       <c r="F162" s="26" t="inlineStr">
         <is>
-          <t>Turnover assumption</t>
+          <t>In-place rent</t>
         </is>
       </c>
       <c r="G162" s="26" t="inlineStr">
@@ -9546,27 +9629,27 @@
       </c>
       <c r="B163" s="5" t="inlineStr">
         <is>
-          <t>lookback_months</t>
+          <t>wavg_market_rent_for_model</t>
         </is>
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D163" s="26" t="inlineStr">
         <is>
-          <t>Length of the new-lease window, measured back from the roll's as-of date.</t>
+          <t>Unit-weighted market rent for model across the property.</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr">
         <is>
-          <t>Supplied by the operator</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F163" s="26" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Market rent</t>
         </is>
       </c>
       <c r="G163" s="26" t="inlineStr">
@@ -9576,7 +9659,7 @@
       </c>
       <c r="H163" s="26" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9588,27 +9671,27 @@
       </c>
       <c r="B164" s="5" t="inlineStr">
         <is>
-          <t>new_tenant_tolerance_days</t>
+          <t>annualized_turnover</t>
         </is>
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D164" s="26" t="inlineStr">
         <is>
-          <t>How far lease start may sit from move-in before a lease stops counting as a new tenant. A knob on the output, not a constant buried in code.</t>
+          <t>Move-ins inside the lookback window, annualized against unit count.</t>
         </is>
       </c>
       <c r="E164" s="5" t="inlineStr">
         <is>
-          <t>Supplied by the operator</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F164" s="26" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Turnover assumption</t>
         </is>
       </c>
       <c r="G164" s="26" t="inlineStr">
@@ -9618,7 +9701,7 @@
       </c>
       <c r="H164" s="26" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -9630,22 +9713,22 @@
       </c>
       <c r="B165" s="5" t="inlineStr">
         <is>
-          <t>absent_reason</t>
+          <t>lookback_months</t>
         </is>
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D165" s="26" t="inlineStr">
         <is>
-          <t>Why the rent-roll section is empty, when no roll was supplied. An empty block that says why is a deliverable; a block of zeroes is not.</t>
+          <t>Length of the move-in and lease-signed window, measured back from the roll's as-of date.</t>
         </is>
       </c>
       <c r="E165" s="5" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Supplied by the operator</t>
         </is>
       </c>
       <c r="F165" s="26" t="inlineStr">
@@ -9660,7 +9743,7 @@
       </c>
       <c r="H165" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -9672,27 +9755,27 @@
       </c>
       <c r="B166" s="5" t="inlineStr">
         <is>
-          <t>roll_as_of</t>
+          <t>new_tenant_tolerance_days</t>
         </is>
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D166" s="26" t="inlineStr">
         <is>
-          <t>As-of date of the roll. Every window is measured from here.</t>
+          <t>How far lease start may sit from move-in before a lease stops counting as a new tenant. A knob on the output, not a constant buried in code.</t>
         </is>
       </c>
       <c r="E166" s="5" t="inlineStr">
         <is>
-          <t>Rent roll export</t>
+          <t>Supplied by the operator</t>
         </is>
       </c>
       <c r="F166" s="26" t="inlineStr">
         <is>
-          <t>Analysis date</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G166" s="26" t="inlineStr">
@@ -9702,107 +9785,107 @@
       </c>
       <c r="H166" s="26" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>31</t>
         </is>
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="4" t="inlineStr">
-        <is>
-          <t>Trade-out</t>
-        </is>
-      </c>
-      <c r="B167" s="4" t="n"/>
-      <c r="C167" s="4" t="n"/>
-      <c r="D167" s="4" t="n"/>
-      <c r="E167" s="4" t="n"/>
-      <c r="F167" s="4" t="n"/>
-      <c r="G167" s="4" t="n"/>
-      <c r="H167" s="4" t="n"/>
+      <c r="A167" s="5" t="inlineStr">
+        <is>
+          <t>Rent roll — totals</t>
+        </is>
+      </c>
+      <c r="B167" s="5" t="inlineStr">
+        <is>
+          <t>absent_reason</t>
+        </is>
+      </c>
+      <c r="C167" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D167" s="26" t="inlineStr">
+        <is>
+          <t>Why the rent-roll section is empty, when no roll was supplied. An empty block that says why is a deliverable; a block of zeroes is not.</t>
+        </is>
+      </c>
+      <c r="E167" s="5" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F167" s="26" t="inlineStr">
+        <is>
+          <t>Reference only — not a model input</t>
+        </is>
+      </c>
+      <c r="G167" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H167" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="5" t="inlineStr">
         <is>
+          <t>Rent roll — totals</t>
+        </is>
+      </c>
+      <c r="B168" s="5" t="inlineStr">
+        <is>
+          <t>roll_as_of</t>
+        </is>
+      </c>
+      <c r="C168" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D168" s="26" t="inlineStr">
+        <is>
+          <t>As-of date of the roll. Every window is measured from here.</t>
+        </is>
+      </c>
+      <c r="E168" s="5" t="inlineStr">
+        <is>
+          <t>Rent roll export</t>
+        </is>
+      </c>
+      <c r="F168" s="26" t="inlineStr">
+        <is>
+          <t>Analysis date</t>
+        </is>
+      </c>
+      <c r="G168" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H168" s="26" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
           <t>Trade-out</t>
         </is>
       </c>
-      <c r="B168" s="5" t="inlineStr">
-        <is>
-          <t>cohort</t>
-        </is>
-      </c>
-      <c r="C168" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D168" s="26" t="inlineStr">
-        <is>
-          <t>New, Renewal, or First generation.</t>
-        </is>
-      </c>
-      <c r="E168" s="5" t="inlineStr">
-        <is>
-          <t>Lease trade-out report</t>
-        </is>
-      </c>
-      <c r="F168" s="26" t="inlineStr">
-        <is>
-          <t>New-vs-renewal growth evidence</t>
-        </is>
-      </c>
-      <c r="G168" s="26" t="inlineStr">
-        <is>
-          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
-        </is>
-      </c>
-      <c r="H168" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="5" t="inlineStr">
-        <is>
-          <t>Trade-out</t>
-        </is>
-      </c>
-      <c r="B169" s="5" t="inlineStr">
-        <is>
-          <t>cohort_leases</t>
-        </is>
-      </c>
-      <c r="C169" s="5" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D169" s="26" t="inlineStr">
-        <is>
-          <t>Leases in the cohort.</t>
-        </is>
-      </c>
-      <c r="E169" s="5" t="inlineStr">
-        <is>
-          <t>Lease trade-out report</t>
-        </is>
-      </c>
-      <c r="F169" s="26" t="inlineStr">
-        <is>
-          <t>Sample size</t>
-        </is>
-      </c>
-      <c r="G169" s="26" t="inlineStr">
-        <is>
-          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
-        </is>
-      </c>
-      <c r="H169" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="B169" s="4" t="n"/>
+      <c r="C169" s="4" t="n"/>
+      <c r="D169" s="4" t="n"/>
+      <c r="E169" s="4" t="n"/>
+      <c r="F169" s="4" t="n"/>
+      <c r="G169" s="4" t="n"/>
+      <c r="H169" s="4" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="5" t="inlineStr">
@@ -9812,17 +9895,17 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>cohort_prior_rent</t>
+          <t>cohort</t>
         </is>
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D170" s="26" t="inlineStr">
         <is>
-          <t>Average rent before the trade.</t>
+          <t>New, Renewal, or First generation.</t>
         </is>
       </c>
       <c r="E170" s="5" t="inlineStr">
@@ -9832,7 +9915,7 @@
       </c>
       <c r="F170" s="26" t="inlineStr">
         <is>
-          <t>Prior rent</t>
+          <t>New-vs-renewal growth evidence</t>
         </is>
       </c>
       <c r="G170" s="26" t="inlineStr">
@@ -9854,17 +9937,17 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>cohort_new_rent_gross</t>
+          <t>cohort_leases</t>
         </is>
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D171" s="26" t="inlineStr">
         <is>
-          <t>Average new rent before concessions.</t>
+          <t>Leases in the cohort.</t>
         </is>
       </c>
       <c r="E171" s="5" t="inlineStr">
@@ -9874,7 +9957,7 @@
       </c>
       <c r="F171" s="26" t="inlineStr">
         <is>
-          <t>Gross trade-out</t>
+          <t>Sample size</t>
         </is>
       </c>
       <c r="G171" s="26" t="inlineStr">
@@ -9896,7 +9979,7 @@
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>cohort_new_rent_effective</t>
+          <t>cohort_prior_rent</t>
         </is>
       </c>
       <c r="C172" s="5" t="inlineStr">
@@ -9906,7 +9989,7 @@
       </c>
       <c r="D172" s="26" t="inlineStr">
         <is>
-          <t>Average new rent after concessions. Quoted separately from gross, because quoting one as the other is how a trade-out number becomes wrong.</t>
+          <t>Average rent before the trade.</t>
         </is>
       </c>
       <c r="E172" s="5" t="inlineStr">
@@ -9916,7 +9999,7 @@
       </c>
       <c r="F172" s="26" t="inlineStr">
         <is>
-          <t>Effective trade-out</t>
+          <t>Prior rent</t>
         </is>
       </c>
       <c r="G172" s="26" t="inlineStr">
@@ -9938,32 +10021,32 @@
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>cohort_gross_change_pct</t>
+          <t>cohort_new_rent_gross</t>
         </is>
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D173" s="26" t="inlineStr">
         <is>
-          <t>Gross change over prior rent.</t>
+          <t>Average new rent before concessions.</t>
         </is>
       </c>
       <c r="E173" s="5" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Lease trade-out report</t>
         </is>
       </c>
       <c r="F173" s="26" t="inlineStr">
         <is>
-          <t>Rent growth evidence</t>
+          <t>Gross trade-out</t>
         </is>
       </c>
       <c r="G173" s="26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
         </is>
       </c>
       <c r="H173" s="26" t="inlineStr">
@@ -9980,32 +10063,32 @@
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>cohort_effective_change_pct</t>
+          <t>cohort_new_rent_effective</t>
         </is>
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D174" s="26" t="inlineStr">
         <is>
-          <t>Effective change over prior rent.</t>
+          <t>Average new rent after concessions. Quoted separately from gross, because quoting one as the other is how a trade-out number becomes wrong.</t>
         </is>
       </c>
       <c r="E174" s="5" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Lease trade-out report</t>
         </is>
       </c>
       <c r="F174" s="26" t="inlineStr">
         <is>
-          <t>Rent growth evidence</t>
+          <t>Effective trade-out</t>
         </is>
       </c>
       <c r="G174" s="26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
         </is>
       </c>
       <c r="H174" s="26" t="inlineStr">
@@ -10022,17 +10105,17 @@
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>absent_reason</t>
+          <t>cohort_gross_change_pct</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D175" s="26" t="inlineStr">
         <is>
-          <t>Why the block is empty, when no trade-out report exists. An empty block that says why is a deliverable; a block of plausible numbers is not.</t>
+          <t>Gross change over prior rent.</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
@@ -10042,117 +10125,117 @@
       </c>
       <c r="F175" s="26" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Rent growth evidence</t>
         </is>
       </c>
       <c r="G175" s="26" t="inlineStr">
         <is>
-          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H175" s="26" t="inlineStr">
         <is>
-          <t>Lease trade-out is an internal-pipeline input: the demo does not ask for a trade-out report, on the sample or on an upload.</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="4" t="inlineStr">
-        <is>
-          <t>Comps</t>
-        </is>
-      </c>
-      <c r="B176" s="4" t="n"/>
-      <c r="C176" s="4" t="n"/>
-      <c r="D176" s="4" t="n"/>
-      <c r="E176" s="4" t="n"/>
-      <c r="F176" s="4" t="n"/>
-      <c r="G176" s="4" t="n"/>
-      <c r="H176" s="4" t="n"/>
+      <c r="A176" s="5" t="inlineStr">
+        <is>
+          <t>Trade-out</t>
+        </is>
+      </c>
+      <c r="B176" s="5" t="inlineStr">
+        <is>
+          <t>cohort_effective_change_pct</t>
+        </is>
+      </c>
+      <c r="C176" s="5" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D176" s="26" t="inlineStr">
+        <is>
+          <t>Effective change over prior rent.</t>
+        </is>
+      </c>
+      <c r="E176" s="5" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F176" s="26" t="inlineStr">
+        <is>
+          <t>Rent growth evidence</t>
+        </is>
+      </c>
+      <c r="G176" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H176" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
         <is>
+          <t>Trade-out</t>
+        </is>
+      </c>
+      <c r="B177" s="5" t="inlineStr">
+        <is>
+          <t>absent_reason</t>
+        </is>
+      </c>
+      <c r="C177" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D177" s="26" t="inlineStr">
+        <is>
+          <t>Why the block is empty, when no trade-out report exists. An empty block that says why is a deliverable; a block of plausible numbers is not.</t>
+        </is>
+      </c>
+      <c r="E177" s="5" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F177" s="26" t="inlineStr">
+        <is>
+          <t>Reference only — not a model input</t>
+        </is>
+      </c>
+      <c r="G177" s="26" t="inlineStr">
+        <is>
+          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
+        </is>
+      </c>
+      <c r="H177" s="26" t="inlineStr">
+        <is>
+          <t>Lease trade-out is an internal-pipeline input: the demo does not ask for a trade-out report, on the sample or on an upload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="4" t="inlineStr">
+        <is>
           <t>Comps</t>
         </is>
       </c>
-      <c r="B177" s="5" t="inlineStr">
-        <is>
-          <t>comp_community</t>
-        </is>
-      </c>
-      <c r="C177" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D177" s="26" t="inlineStr">
-        <is>
-          <t>Comparable community name.</t>
-        </is>
-      </c>
-      <c r="E177" s="5" t="inlineStr">
-        <is>
-          <t>Operator's own weekly rent scrape</t>
-        </is>
-      </c>
-      <c r="F177" s="26" t="inlineStr">
-        <is>
-          <t>Comp set</t>
-        </is>
-      </c>
-      <c r="G177" s="26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H177" s="26" t="inlineStr">
-        <is>
-          <t>Saltera Apartments</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="5" t="inlineStr">
-        <is>
-          <t>Comps</t>
-        </is>
-      </c>
-      <c r="B178" s="5" t="inlineStr">
-        <is>
-          <t>comp_distance_mi</t>
-        </is>
-      </c>
-      <c r="C178" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="D178" s="26" t="inlineStr">
-        <is>
-          <t>Straight-line distance from the subject.</t>
-        </is>
-      </c>
-      <c r="E178" s="5" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F178" s="26" t="inlineStr">
-        <is>
-          <t>Comp set</t>
-        </is>
-      </c>
-      <c r="G178" s="26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H178" s="26" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
+      <c r="B178" s="4" t="n"/>
+      <c r="C178" s="4" t="n"/>
+      <c r="D178" s="4" t="n"/>
+      <c r="E178" s="4" t="n"/>
+      <c r="F178" s="4" t="n"/>
+      <c r="G178" s="4" t="n"/>
+      <c r="H178" s="4" t="n"/>
     </row>
     <row r="179">
       <c r="A179" s="5" t="inlineStr">
@@ -10162,7 +10245,7 @@
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>comp_floor_plan</t>
+          <t>comp_community</t>
         </is>
       </c>
       <c r="C179" s="5" t="inlineStr">
@@ -10172,7 +10255,7 @@
       </c>
       <c r="D179" s="26" t="inlineStr">
         <is>
-          <t>Comp floor plan the row describes. Comps are stated per plan, not as one blended community number.</t>
+          <t>Comparable community name.</t>
         </is>
       </c>
       <c r="E179" s="5" t="inlineStr">
@@ -10192,7 +10275,7 @@
       </c>
       <c r="H179" s="26" t="inlineStr">
         <is>
-          <t>1BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>Saltera Apartments</t>
         </is>
       </c>
     </row>
@@ -10204,17 +10287,17 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>comp_tier</t>
+          <t>comp_distance_mi</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D180" s="26" t="inlineStr">
         <is>
-          <t>1 = top comps (the closest five matching the subject's product and vintage), 2 = additional comps (the next fifteen). The identity-only third group carries no rent; since 2026-09-28 it is carried in the interchange file only and is not shown as a table.</t>
+          <t>Straight-line distance from the subject.</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
@@ -10234,7 +10317,7 @@
       </c>
       <c r="H180" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.1</t>
         </is>
       </c>
     </row>
@@ -10246,17 +10329,17 @@
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>comp_year_built</t>
+          <t>comp_floor_plan</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D181" s="26" t="inlineStr">
         <is>
-          <t>Comp vintage where one is published. Blank means nobody published one — the tracker has no year-built column — never that the community is new.</t>
+          <t>Comp floor plan the row describes. Comps are stated per plan, not as one blended community number.</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
@@ -10276,7 +10359,7 @@
       </c>
       <c r="H181" s="26" t="inlineStr">
         <is>
-          <t>1,984</t>
+          <t>1BR — group floor (lowest listing); the lowest-five measure was not provided</t>
         </is>
       </c>
     </row>
@@ -10288,27 +10371,27 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>comp_year_built_source</t>
+          <t>comp_tier</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D182" s="26" t="inlineStr">
         <is>
-          <t>Where that year came from. Blank alongside a blank year; a year with no source is rejected at validation.</t>
+          <t>1 = top comps (the closest five matching the subject's product and vintage), 2 = additional comps (the next fifteen). The identity-only third group carries no rent; since 2026-09-28 it is carried in the interchange file only and is not shown as a table.</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F182" s="26" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G182" s="26" t="inlineStr">
@@ -10318,7 +10401,7 @@
       </c>
       <c r="H182" s="26" t="inlineStr">
         <is>
-          <t>vendor note on the tracked community record, via the market-report service</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -10330,17 +10413,17 @@
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>nearby_community</t>
+          <t>comp_year_built</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D183" s="26" t="inlineStr">
         <is>
-          <t>A tracked community inside the radius that is NOT a comp. Carried in the interchange file; the ~340-row table was taken off the page on 2026-09-28.</t>
+          <t>Comp vintage where one is published. Blank means nobody published one — the tracker has no year-built column — never that the community is new.</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
@@ -10350,7 +10433,7 @@
       </c>
       <c r="F183" s="26" t="inlineStr">
         <is>
-          <t>Market context</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G183" s="26" t="inlineStr">
@@ -10360,7 +10443,7 @@
       </c>
       <c r="H183" s="26" t="inlineStr">
         <is>
-          <t>Trails at Harris</t>
+          <t>1,984</t>
         </is>
       </c>
     </row>
@@ -10372,7 +10455,7 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>nearby_address</t>
+          <t>comp_year_built_source</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
@@ -10382,7 +10465,7 @@
       </c>
       <c r="D184" s="26" t="inlineStr">
         <is>
-          <t>Its address, so the reader can place it.</t>
+          <t>Where that year came from. Blank alongside a blank year; a year with no source is rejected at validation.</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
@@ -10392,7 +10475,7 @@
       </c>
       <c r="F184" s="26" t="inlineStr">
         <is>
-          <t>Market context</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G184" s="26" t="inlineStr">
@@ -10402,7 +10485,7 @@
       </c>
       <c r="H184" s="26" t="inlineStr">
         <is>
-          <t>1653 S Harris Dr, Mesa, AZ 85204</t>
+          <t>vendor note on the tracked community record, via the market-report service</t>
         </is>
       </c>
     </row>
@@ -10414,22 +10497,22 @@
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>nearby_distance_mi</t>
+          <t>nearby_community</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D185" s="26" t="inlineStr">
         <is>
-          <t>Distance from the subject.</t>
+          <t>A tracked community inside the radius that is NOT a comp. Carried in the interchange file; the ~340-row table was taken off the page on 2026-09-28.</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F185" s="26" t="inlineStr">
@@ -10444,7 +10527,7 @@
       </c>
       <c r="H185" s="26" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>Trails at Harris</t>
         </is>
       </c>
     </row>
@@ -10456,17 +10539,17 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>nearby_units</t>
+          <t>nearby_address</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D186" s="26" t="inlineStr">
         <is>
-          <t>Unit count where the registry has one.</t>
+          <t>Its address, so the reader can place it.</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
@@ -10486,7 +10569,7 @@
       </c>
       <c r="H186" s="26" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>1653 S Harris Dr, Mesa, AZ 85204</t>
         </is>
       </c>
     </row>
@@ -10498,17 +10581,17 @@
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>nearby_reason</t>
+          <t>nearby_distance_mi</t>
         </is>
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D187" s="26" t="inlineStr">
         <is>
-          <t>Why it is not a comp: wrong product, vintage outside the band, no quoted rent, excluded by the tracker, or simply beyond the closest twenty. The field that answers 'why isn't the property across the street in your comp set?' for every community in the radius.</t>
+          <t>Distance from the subject.</t>
         </is>
       </c>
       <c r="E187" s="5" t="inlineStr">
@@ -10528,7 +10611,7 @@
       </c>
       <c r="H187" s="26" t="inlineStr">
         <is>
-          <t>its 2 unit group(s) were withheld (flagged for review, no bedroom count or no rent), so nothing could be quoted</t>
+          <t>0.9</t>
         </is>
       </c>
     </row>
@@ -10540,27 +10623,27 @@
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>compset_vintage_footnote</t>
+          <t>nearby_units</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D188" s="26" t="inlineStr">
         <is>
-          <t>The disclosure on the detailed tiers: the band applied, and whether some communities carried no year and so could not be tested.</t>
+          <t>Unit count where the registry has one.</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F188" s="26" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Market context</t>
         </is>
       </c>
       <c r="G188" s="26" t="inlineStr">
@@ -10570,7 +10653,7 @@
       </c>
       <c r="H188" s="26" t="inlineStr">
         <is>
-          <t>Vintage filter: +/-10 years of the subject's year built.</t>
+          <t>209</t>
         </is>
       </c>
     </row>
@@ -10582,27 +10665,27 @@
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
-          <t>comp_beds</t>
+          <t>nearby_reason</t>
         </is>
       </c>
       <c r="C189" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D189" s="26" t="inlineStr">
         <is>
-          <t>Bedrooms in the comp plan.</t>
+          <t>Why it is not a comp: wrong product, vintage outside the band, no quoted rent, excluded by the tracker, or simply beyond the closest twenty. The field that answers 'why isn't the property across the street in your comp set?' for every community in the radius.</t>
         </is>
       </c>
       <c r="E189" s="5" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F189" s="26" t="inlineStr">
         <is>
-          <t>Comp set</t>
+          <t>Market context</t>
         </is>
       </c>
       <c r="G189" s="26" t="inlineStr">
@@ -10612,7 +10695,7 @@
       </c>
       <c r="H189" s="26" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>its 2 unit group(s) were withheld (flagged for review, no bedroom count or no rent), so nothing could be quoted</t>
         </is>
       </c>
     </row>
@@ -10624,27 +10707,27 @@
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
-          <t>comp_baths</t>
+          <t>compset_vintage_footnote</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D190" s="26" t="inlineStr">
         <is>
-          <t>Bathrooms in the comp plan.</t>
+          <t>The disclosure on the detailed tiers: the band applied, and whether some communities carried no year and so could not be tested.</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F190" s="26" t="inlineStr">
         <is>
-          <t>Comp set</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G190" s="26" t="inlineStr">
@@ -10654,7 +10737,7 @@
       </c>
       <c r="H190" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Vintage filter: +/-10 years of the subject's year built.</t>
         </is>
       </c>
     </row>
@@ -10666,7 +10749,7 @@
       </c>
       <c r="B191" s="5" t="inlineStr">
         <is>
-          <t>comp_sqft</t>
+          <t>comp_beds</t>
         </is>
       </c>
       <c r="C191" s="5" t="inlineStr">
@@ -10676,7 +10759,7 @@
       </c>
       <c r="D191" s="26" t="inlineStr">
         <is>
-          <t>Square footage of the comp plan.</t>
+          <t>Bedrooms in the comp plan.</t>
         </is>
       </c>
       <c r="E191" s="5" t="inlineStr">
@@ -10696,7 +10779,7 @@
       </c>
       <c r="H191" s="26" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -10708,17 +10791,17 @@
       </c>
       <c r="B192" s="5" t="inlineStr">
         <is>
-          <t>comp_asking_rent</t>
+          <t>comp_baths</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D192" s="26" t="inlineStr">
         <is>
-          <t>Advertised asking rent.</t>
+          <t>Bathrooms in the comp plan.</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
@@ -10728,7 +10811,7 @@
       </c>
       <c r="F192" s="26" t="inlineStr">
         <is>
-          <t>Market rent evidence</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G192" s="26" t="inlineStr">
@@ -10738,7 +10821,7 @@
       </c>
       <c r="H192" s="26" t="inlineStr">
         <is>
-          <t>$1,047</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10750,17 +10833,17 @@
       </c>
       <c r="B193" s="5" t="inlineStr">
         <is>
-          <t>comp_concession</t>
+          <t>comp_sqft</t>
         </is>
       </c>
       <c r="C193" s="5" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D193" s="26" t="inlineStr">
         <is>
-          <t>Monthly value of the advertised concession.</t>
+          <t>Square footage of the comp plan.</t>
         </is>
       </c>
       <c r="E193" s="5" t="inlineStr">
@@ -10770,7 +10853,7 @@
       </c>
       <c r="F193" s="26" t="inlineStr">
         <is>
-          <t>Concession assumption</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G193" s="26" t="inlineStr">
@@ -10780,7 +10863,7 @@
       </c>
       <c r="H193" s="26" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>688.0</t>
         </is>
       </c>
     </row>
@@ -10792,7 +10875,7 @@
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>comp_net_effective_rent</t>
+          <t>comp_asking_rent</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
@@ -10802,12 +10885,12 @@
       </c>
       <c r="D194" s="26" t="inlineStr">
         <is>
-          <t>Asking rent less the amortized concession. Stated on every row — a concession-blind comp set is the most common way a rent assumption goes wrong.</t>
+          <t>Advertised asking rent.</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F194" s="26" t="inlineStr">
@@ -10834,7 +10917,7 @@
       </c>
       <c r="B195" s="5" t="inlineStr">
         <is>
-          <t>comp_asking_psf</t>
+          <t>comp_concession</t>
         </is>
       </c>
       <c r="C195" s="5" t="inlineStr">
@@ -10844,17 +10927,17 @@
       </c>
       <c r="D195" s="26" t="inlineStr">
         <is>
-          <t>Asking rent per square foot.</t>
+          <t>Monthly value of the advertised concession.</t>
         </is>
       </c>
       <c r="E195" s="5" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F195" s="26" t="inlineStr">
         <is>
-          <t>Comp set</t>
+          <t>Concession assumption</t>
         </is>
       </c>
       <c r="G195" s="26" t="inlineStr">
@@ -10864,7 +10947,7 @@
       </c>
       <c r="H195" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -10876,27 +10959,27 @@
       </c>
       <c r="B196" s="5" t="inlineStr">
         <is>
-          <t>comp_occupancy</t>
+          <t>comp_net_effective_rent</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D196" s="26" t="inlineStr">
         <is>
-          <t>Occupancy where the source published it.</t>
+          <t>Asking rent less the amortized concession. Stated on every row — a concession-blind comp set is the most common way a rent assumption goes wrong.</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F196" s="26" t="inlineStr">
         <is>
-          <t>Market context</t>
+          <t>Market rent evidence</t>
         </is>
       </c>
       <c r="G196" s="26" t="inlineStr">
@@ -10906,7 +10989,7 @@
       </c>
       <c r="H196" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$1,047</t>
         </is>
       </c>
     </row>
@@ -10918,27 +11001,27 @@
       </c>
       <c r="B197" s="5" t="inlineStr">
         <is>
-          <t>comp_as_of</t>
+          <t>comp_asking_psf</t>
         </is>
       </c>
       <c r="C197" s="5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D197" s="26" t="inlineStr">
         <is>
-          <t>When the row was scraped.</t>
+          <t>Asking rent per square foot.</t>
         </is>
       </c>
       <c r="E197" s="5" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F197" s="26" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G197" s="26" t="inlineStr">
@@ -10948,7 +11031,7 @@
       </c>
       <c r="H197" s="26" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10960,17 +11043,17 @@
       </c>
       <c r="B198" s="5" t="inlineStr">
         <is>
-          <t>comp_source</t>
+          <t>comp_occupancy</t>
         </is>
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D198" s="26" t="inlineStr">
         <is>
-          <t>Always the operator's own weekly scrape. Licensed comp feeds are excluded by design and cannot be represented in this schema.</t>
+          <t>Occupancy where the source published it.</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
@@ -10980,7 +11063,7 @@
       </c>
       <c r="F198" s="26" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Market context</t>
         </is>
       </c>
       <c r="G198" s="26" t="inlineStr">
@@ -10990,7 +11073,7 @@
       </c>
       <c r="H198" s="26" t="inlineStr">
         <is>
-          <t>own weekly scrape</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -11002,27 +11085,27 @@
       </c>
       <c r="B199" s="5" t="inlineStr">
         <is>
-          <t>compset_avg_asking</t>
+          <t>comp_as_of</t>
         </is>
       </c>
       <c r="C199" s="5" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D199" s="26" t="inlineStr">
         <is>
-          <t>Average asking rent across the comp set.</t>
+          <t>When the row was scraped.</t>
         </is>
       </c>
       <c r="E199" s="5" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F199" s="26" t="inlineStr">
         <is>
-          <t>Market rent benchmark</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G199" s="26" t="inlineStr">
@@ -11032,7 +11115,7 @@
       </c>
       <c r="H199" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
@@ -11044,27 +11127,27 @@
       </c>
       <c r="B200" s="5" t="inlineStr">
         <is>
-          <t>compset_avg_net_effective</t>
+          <t>comp_source</t>
         </is>
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D200" s="26" t="inlineStr">
         <is>
-          <t>Average net effective rent across the comp set.</t>
+          <t>Always the operator's own weekly scrape. Licensed comp feeds are excluded by design and cannot be represented in this schema.</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F200" s="26" t="inlineStr">
         <is>
-          <t>Market rent benchmark</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G200" s="26" t="inlineStr">
@@ -11074,7 +11157,7 @@
       </c>
       <c r="H200" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>own weekly scrape</t>
         </is>
       </c>
     </row>
@@ -11086,17 +11169,17 @@
       </c>
       <c r="B201" s="5" t="inlineStr">
         <is>
-          <t>subject_vs_compset_spread</t>
+          <t>compset_avg_asking</t>
         </is>
       </c>
       <c r="C201" s="5" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D201" s="26" t="inlineStr">
         <is>
-          <t>Subject market rent over comp-set net effective, less one.</t>
+          <t>Average asking rent across the comp set.</t>
         </is>
       </c>
       <c r="E201" s="5" t="inlineStr">
@@ -11106,7 +11189,7 @@
       </c>
       <c r="F201" s="26" t="inlineStr">
         <is>
-          <t>Rent positioning</t>
+          <t>Market rent benchmark</t>
         </is>
       </c>
       <c r="G201" s="26" t="inlineStr">
@@ -11121,102 +11204,102 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="4" t="inlineStr">
-        <is>
-          <t>Demand</t>
-        </is>
-      </c>
-      <c r="B202" s="4" t="n"/>
-      <c r="C202" s="4" t="n"/>
-      <c r="D202" s="4" t="n"/>
-      <c r="E202" s="4" t="n"/>
-      <c r="F202" s="4" t="n"/>
-      <c r="G202" s="4" t="n"/>
-      <c r="H202" s="4" t="n"/>
+      <c r="A202" s="5" t="inlineStr">
+        <is>
+          <t>Comps</t>
+        </is>
+      </c>
+      <c r="B202" s="5" t="inlineStr">
+        <is>
+          <t>compset_avg_net_effective</t>
+        </is>
+      </c>
+      <c r="C202" s="5" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D202" s="26" t="inlineStr">
+        <is>
+          <t>Average net effective rent across the comp set.</t>
+        </is>
+      </c>
+      <c r="E202" s="5" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F202" s="26" t="inlineStr">
+        <is>
+          <t>Market rent benchmark</t>
+        </is>
+      </c>
+      <c r="G202" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H202" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="5" t="inlineStr">
         <is>
+          <t>Comps</t>
+        </is>
+      </c>
+      <c r="B203" s="5" t="inlineStr">
+        <is>
+          <t>subject_vs_compset_spread</t>
+        </is>
+      </c>
+      <c r="C203" s="5" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D203" s="26" t="inlineStr">
+        <is>
+          <t>Subject market rent over comp-set net effective, less one.</t>
+        </is>
+      </c>
+      <c r="E203" s="5" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F203" s="26" t="inlineStr">
+        <is>
+          <t>Rent positioning</t>
+        </is>
+      </c>
+      <c r="G203" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H203" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="4" t="inlineStr">
+        <is>
           <t>Demand</t>
         </is>
       </c>
-      <c r="B203" s="5" t="inlineStr">
-        <is>
-          <t>demand_ring</t>
-        </is>
-      </c>
-      <c r="C203" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D203" s="26" t="inlineStr">
-        <is>
-          <t>Drive-ring the row describes: 1, 3, 5, or 10 miles, or the MSA.</t>
-        </is>
-      </c>
-      <c r="E203" s="5" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F203" s="26" t="inlineStr">
-        <is>
-          <t>Market summary</t>
-        </is>
-      </c>
-      <c r="G203" s="26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H203" s="26" t="inlineStr">
-        <is>
-          <t>1 mi</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="5" t="inlineStr">
-        <is>
-          <t>Demand</t>
-        </is>
-      </c>
-      <c r="B204" s="5" t="inlineStr">
-        <is>
-          <t>demand_population</t>
-        </is>
-      </c>
-      <c r="C204" s="5" t="inlineStr">
-        <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="D204" s="26" t="inlineStr">
-        <is>
-          <t>Population in the ring.</t>
-        </is>
-      </c>
-      <c r="E204" s="5" t="inlineStr">
-        <is>
-          <t>Public demographic data</t>
-        </is>
-      </c>
-      <c r="F204" s="26" t="inlineStr">
-        <is>
-          <t>Market summary</t>
-        </is>
-      </c>
-      <c r="G204" s="26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H204" s="26" t="inlineStr">
-        <is>
-          <t>20,297</t>
-        </is>
-      </c>
+      <c r="B204" s="4" t="n"/>
+      <c r="C204" s="4" t="n"/>
+      <c r="D204" s="4" t="n"/>
+      <c r="E204" s="4" t="n"/>
+      <c r="F204" s="4" t="n"/>
+      <c r="G204" s="4" t="n"/>
+      <c r="H204" s="4" t="n"/>
     </row>
     <row r="205">
       <c r="A205" s="5" t="inlineStr">
@@ -11226,22 +11309,22 @@
       </c>
       <c r="B205" s="5" t="inlineStr">
         <is>
-          <t>demand_households</t>
+          <t>demand_ring</t>
         </is>
       </c>
       <c r="C205" s="5" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D205" s="26" t="inlineStr">
         <is>
-          <t>Households in the ring.</t>
+          <t>Drive-ring the row describes: 1, 3, 5, or 10 miles, or the MSA.</t>
         </is>
       </c>
       <c r="E205" s="5" t="inlineStr">
         <is>
-          <t>Public demographic data</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F205" s="26" t="inlineStr">
@@ -11256,7 +11339,7 @@
       </c>
       <c r="H205" s="26" t="inlineStr">
         <is>
-          <t>7,711</t>
+          <t>1 mi</t>
         </is>
       </c>
     </row>
@@ -11268,17 +11351,17 @@
       </c>
       <c r="B206" s="5" t="inlineStr">
         <is>
-          <t>demand_median_income</t>
+          <t>demand_population</t>
         </is>
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D206" s="26" t="inlineStr">
         <is>
-          <t>Median household income in the ring.</t>
+          <t>Population in the ring.</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
@@ -11288,7 +11371,7 @@
       </c>
       <c r="F206" s="26" t="inlineStr">
         <is>
-          <t>Affordability check</t>
+          <t>Market summary</t>
         </is>
       </c>
       <c r="G206" s="26" t="inlineStr">
@@ -11298,7 +11381,7 @@
       </c>
       <c r="H206" s="26" t="inlineStr">
         <is>
-          <t>$79,735</t>
+          <t>20,297</t>
         </is>
       </c>
     </row>
@@ -11310,7 +11393,7 @@
       </c>
       <c r="B207" s="5" t="inlineStr">
         <is>
-          <t>demand_jobs</t>
+          <t>demand_households</t>
         </is>
       </c>
       <c r="C207" s="5" t="inlineStr">
@@ -11320,7 +11403,7 @@
       </c>
       <c r="D207" s="26" t="inlineStr">
         <is>
-          <t>Jobs located in the ring.</t>
+          <t>Households in the ring.</t>
         </is>
       </c>
       <c r="E207" s="5" t="inlineStr">
@@ -11340,7 +11423,7 @@
       </c>
       <c r="H207" s="26" t="inlineStr">
         <is>
-          <t>5,239</t>
+          <t>7,711</t>
         </is>
       </c>
     </row>
@@ -11352,17 +11435,17 @@
       </c>
       <c r="B208" s="5" t="inlineStr">
         <is>
-          <t>demand_pop_growth_5yr</t>
+          <t>demand_median_income</t>
         </is>
       </c>
       <c r="C208" s="5" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D208" s="26" t="inlineStr">
         <is>
-          <t>Five-year population growth in the ring.</t>
+          <t>Median household income in the ring.</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
@@ -11372,7 +11455,7 @@
       </c>
       <c r="F208" s="26" t="inlineStr">
         <is>
-          <t>Growth assumption evidence</t>
+          <t>Affordability check</t>
         </is>
       </c>
       <c r="G208" s="26" t="inlineStr">
@@ -11382,7 +11465,7 @@
       </c>
       <c r="H208" s="26" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>$79,735</t>
         </is>
       </c>
     </row>
@@ -11394,137 +11477,137 @@
       </c>
       <c r="B209" s="5" t="inlineStr">
         <is>
-          <t>demand_renter_share</t>
+          <t>demand_jobs</t>
         </is>
       </c>
       <c r="C209" s="5" t="inlineStr">
         <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D209" s="26" t="inlineStr">
+        <is>
+          <t>Jobs located in the ring.</t>
+        </is>
+      </c>
+      <c r="E209" s="5" t="inlineStr">
+        <is>
+          <t>Public demographic data</t>
+        </is>
+      </c>
+      <c r="F209" s="26" t="inlineStr">
+        <is>
+          <t>Market summary</t>
+        </is>
+      </c>
+      <c r="G209" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H209" s="26" t="inlineStr">
+        <is>
+          <t>5,239</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="5" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="B210" s="5" t="inlineStr">
+        <is>
+          <t>demand_pop_growth_5yr</t>
+        </is>
+      </c>
+      <c r="C210" s="5" t="inlineStr">
+        <is>
           <t>percent</t>
         </is>
       </c>
-      <c r="D209" s="26" t="inlineStr">
-        <is>
-          <t>Share of ring households that rent.</t>
-        </is>
-      </c>
-      <c r="E209" s="5" t="inlineStr">
+      <c r="D210" s="26" t="inlineStr">
+        <is>
+          <t>Five-year population growth in the ring.</t>
+        </is>
+      </c>
+      <c r="E210" s="5" t="inlineStr">
         <is>
           <t>Public demographic data</t>
         </is>
       </c>
-      <c r="F209" s="26" t="inlineStr">
-        <is>
-          <t>Demand context</t>
-        </is>
-      </c>
-      <c r="G209" s="26" t="inlineStr">
+      <c r="F210" s="26" t="inlineStr">
+        <is>
+          <t>Growth assumption evidence</t>
+        </is>
+      </c>
+      <c r="G210" s="26" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H209" s="26" t="inlineStr">
-        <is>
-          <t>43.4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="4" t="inlineStr">
-        <is>
-          <t>Supply</t>
-        </is>
-      </c>
-      <c r="B210" s="4" t="n"/>
-      <c r="C210" s="4" t="n"/>
-      <c r="D210" s="4" t="n"/>
-      <c r="E210" s="4" t="n"/>
-      <c r="F210" s="4" t="n"/>
-      <c r="G210" s="4" t="n"/>
-      <c r="H210" s="4" t="n"/>
+      <c r="H210" s="26" t="inlineStr">
+        <is>
+          <t>-2.0%</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="5" t="inlineStr">
         <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="B211" s="5" t="inlineStr">
+        <is>
+          <t>demand_renter_share</t>
+        </is>
+      </c>
+      <c r="C211" s="5" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D211" s="26" t="inlineStr">
+        <is>
+          <t>Share of ring households that rent.</t>
+        </is>
+      </c>
+      <c r="E211" s="5" t="inlineStr">
+        <is>
+          <t>Public demographic data</t>
+        </is>
+      </c>
+      <c r="F211" s="26" t="inlineStr">
+        <is>
+          <t>Demand context</t>
+        </is>
+      </c>
+      <c r="G211" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H211" s="26" t="inlineStr">
+        <is>
+          <t>43.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="4" t="inlineStr">
+        <is>
           <t>Supply</t>
         </is>
       </c>
-      <c r="B211" s="5" t="inlineStr">
-        <is>
-          <t>supply_ring</t>
-        </is>
-      </c>
-      <c r="C211" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D211" s="26" t="inlineStr">
-        <is>
-          <t>Ring the supply row describes.</t>
-        </is>
-      </c>
-      <c r="E211" s="5" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F211" s="26" t="inlineStr">
-        <is>
-          <t>Competing supply</t>
-        </is>
-      </c>
-      <c r="G211" s="26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H211" s="26" t="inlineStr">
-        <is>
-          <t>1 mi</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" s="5" t="inlineStr">
-        <is>
-          <t>Supply</t>
-        </is>
-      </c>
-      <c r="B212" s="5" t="inlineStr">
-        <is>
-          <t>supply_stage</t>
-        </is>
-      </c>
-      <c r="C212" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D212" s="26" t="inlineStr">
-        <is>
-          <t>Entitlement, permitted, under construction, or delivered in the last 24 months. Stage is stated because entitled units and delivered units are not the same risk.</t>
-        </is>
-      </c>
-      <c r="E212" s="5" t="inlineStr">
-        <is>
-          <t>Public permit / entitlement records</t>
-        </is>
-      </c>
-      <c r="F212" s="26" t="inlineStr">
-        <is>
-          <t>Competing supply</t>
-        </is>
-      </c>
-      <c r="G212" s="26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H212" s="26" t="inlineStr">
-        <is>
-          <t>Entitlement</t>
-        </is>
-      </c>
+      <c r="B212" s="4" t="n"/>
+      <c r="C212" s="4" t="n"/>
+      <c r="D212" s="4" t="n"/>
+      <c r="E212" s="4" t="n"/>
+      <c r="F212" s="4" t="n"/>
+      <c r="G212" s="4" t="n"/>
+      <c r="H212" s="4" t="n"/>
     </row>
     <row r="213">
       <c r="A213" s="5" t="inlineStr">
@@ -11534,22 +11617,22 @@
       </c>
       <c r="B213" s="5" t="inlineStr">
         <is>
-          <t>supply_projects</t>
+          <t>supply_ring</t>
         </is>
       </c>
       <c r="C213" s="5" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D213" s="26" t="inlineStr">
         <is>
-          <t>Projects at that ring and stage.</t>
+          <t>Ring the supply row describes.</t>
         </is>
       </c>
       <c r="E213" s="5" t="inlineStr">
         <is>
-          <t>Public permit / entitlement records</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F213" s="26" t="inlineStr">
@@ -11564,7 +11647,7 @@
       </c>
       <c r="H213" s="26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1 mi</t>
         </is>
       </c>
     </row>
@@ -11576,17 +11659,17 @@
       </c>
       <c r="B214" s="5" t="inlineStr">
         <is>
-          <t>supply_units</t>
+          <t>supply_stage</t>
         </is>
       </c>
       <c r="C214" s="5" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D214" s="26" t="inlineStr">
         <is>
-          <t>Units at that ring and stage.</t>
+          <t>Entitlement, permitted, under construction, or delivered in the last 24 months. Stage is stated because entitled units and delivered units are not the same risk.</t>
         </is>
       </c>
       <c r="E214" s="5" t="inlineStr">
@@ -11596,7 +11679,7 @@
       </c>
       <c r="F214" s="26" t="inlineStr">
         <is>
-          <t>Competing supply / absorption</t>
+          <t>Competing supply</t>
         </is>
       </c>
       <c r="G214" s="26" t="inlineStr">
@@ -11606,7 +11689,7 @@
       </c>
       <c r="H214" s="26" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>Entitlement</t>
         </is>
       </c>
     </row>
@@ -11618,7 +11701,7 @@
       </c>
       <c r="B215" s="5" t="inlineStr">
         <is>
-          <t>supply_ring_total_units</t>
+          <t>supply_projects</t>
         </is>
       </c>
       <c r="C215" s="5" t="inlineStr">
@@ -11628,12 +11711,12 @@
       </c>
       <c r="D215" s="26" t="inlineStr">
         <is>
-          <t>All pipeline units in the ring across stages.</t>
+          <t>Projects at that ring and stage.</t>
         </is>
       </c>
       <c r="E215" s="5" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Public permit / entitlement records</t>
         </is>
       </c>
       <c r="F215" s="26" t="inlineStr">
@@ -11648,7 +11731,7 @@
       </c>
       <c r="H215" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -11660,27 +11743,27 @@
       </c>
       <c r="B216" s="5" t="inlineStr">
         <is>
-          <t>supply_pct_of_ring_stock</t>
+          <t>supply_units</t>
         </is>
       </c>
       <c r="C216" s="5" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D216" s="26" t="inlineStr">
         <is>
-          <t>Pipeline units as a share of the ring's existing stock, where stock is known.</t>
+          <t>Units at that ring and stage.</t>
         </is>
       </c>
       <c r="E216" s="5" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Public permit / entitlement records</t>
         </is>
       </c>
       <c r="F216" s="26" t="inlineStr">
         <is>
-          <t>Supply pressure</t>
+          <t>Competing supply / absorption</t>
         </is>
       </c>
       <c r="G216" s="26" t="inlineStr">
@@ -11690,7 +11773,7 @@
       </c>
       <c r="H216" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>72</t>
         </is>
       </c>
     </row>
@@ -11702,22 +11785,22 @@
       </c>
       <c r="B217" s="5" t="inlineStr">
         <is>
-          <t>supply_project_name</t>
+          <t>supply_ring_total_units</t>
         </is>
       </c>
       <c r="C217" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D217" s="26" t="inlineStr">
         <is>
-          <t>One development inside three miles, named. The ring rows say how many projects were counted; these say which ones.</t>
+          <t>All pipeline units in the ring across stages.</t>
         </is>
       </c>
       <c r="E217" s="5" t="inlineStr">
         <is>
-          <t>Public permit / entitlement records</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F217" s="26" t="inlineStr">
@@ -11732,7 +11815,7 @@
       </c>
       <c r="H217" s="26" t="inlineStr">
         <is>
-          <t>Reed Park Residences</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -11744,17 +11827,17 @@
       </c>
       <c r="B218" s="5" t="inlineStr">
         <is>
-          <t>supply_project_miles</t>
+          <t>supply_pct_of_ring_stock</t>
         </is>
       </c>
       <c r="C218" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D218" s="26" t="inlineStr">
         <is>
-          <t>Distance from the subject, at the nearest record any lifecycle layer carried.</t>
+          <t>Pipeline units as a share of the ring's existing stock, where stock is known.</t>
         </is>
       </c>
       <c r="E218" s="5" t="inlineStr">
@@ -11764,7 +11847,7 @@
       </c>
       <c r="F218" s="26" t="inlineStr">
         <is>
-          <t>Competing supply</t>
+          <t>Supply pressure</t>
         </is>
       </c>
       <c r="G218" s="26" t="inlineStr">
@@ -11774,7 +11857,7 @@
       </c>
       <c r="H218" s="26" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -11786,7 +11869,7 @@
       </c>
       <c r="B219" s="5" t="inlineStr">
         <is>
-          <t>supply_project_stage</t>
+          <t>supply_project_name</t>
         </is>
       </c>
       <c r="C219" s="5" t="inlineStr">
@@ -11796,7 +11879,7 @@
       </c>
       <c r="D219" s="26" t="inlineStr">
         <is>
-          <t>The furthest tracked stage the pipeline shows for that development — the stage it was counted at.</t>
+          <t>One development inside three miles, named. The ring rows say how many projects were counted; these say which ones.</t>
         </is>
       </c>
       <c r="E219" s="5" t="inlineStr">
@@ -11816,7 +11899,7 @@
       </c>
       <c r="H219" s="26" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>Reed Park Residences</t>
         </is>
       </c>
     </row>
@@ -11828,27 +11911,27 @@
       </c>
       <c r="B220" s="5" t="inlineStr">
         <is>
-          <t>supply_project_units</t>
+          <t>supply_project_miles</t>
         </is>
       </c>
       <c r="C220" s="5" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D220" s="26" t="inlineStr">
         <is>
-          <t>Units where a layer stated them. Blank means the source did not state a count, never zero.</t>
+          <t>Distance from the subject, at the nearest record any lifecycle layer carried.</t>
         </is>
       </c>
       <c r="E220" s="5" t="inlineStr">
         <is>
-          <t>Public permit / entitlement records</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F220" s="26" t="inlineStr">
         <is>
-          <t>Competing supply / absorption</t>
+          <t>Competing supply</t>
         </is>
       </c>
       <c r="G220" s="26" t="inlineStr">
@@ -11858,7 +11941,7 @@
       </c>
       <c r="H220" s="26" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>0.9</t>
         </is>
       </c>
     </row>
@@ -11870,7 +11953,7 @@
       </c>
       <c r="B221" s="5" t="inlineStr">
         <is>
-          <t>supply_project_product</t>
+          <t>supply_project_stage</t>
         </is>
       </c>
       <c r="C221" s="5" t="inlineStr">
@@ -11880,7 +11963,7 @@
       </c>
       <c r="D221" s="26" t="inlineStr">
         <is>
-          <t>Product the pipeline records for the development.</t>
+          <t>The furthest tracked stage the pipeline shows for that development — the stage it was counted at.</t>
         </is>
       </c>
       <c r="E221" s="5" t="inlineStr">
@@ -11900,7 +11983,7 @@
       </c>
       <c r="H221" s="26" t="inlineStr">
         <is>
-          <t>multifamily</t>
+          <t>Entitlement</t>
         </is>
       </c>
     </row>
@@ -11912,17 +11995,17 @@
       </c>
       <c r="B222" s="5" t="inlineStr">
         <is>
-          <t>supply_project_address</t>
+          <t>supply_project_units</t>
         </is>
       </c>
       <c r="C222" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D222" s="26" t="inlineStr">
         <is>
-          <t>Street address where a layer carried one.</t>
+          <t>Units where a layer stated them. Blank means the source did not state a count, never zero.</t>
         </is>
       </c>
       <c r="E222" s="5" t="inlineStr">
@@ -11932,7 +12015,7 @@
       </c>
       <c r="F222" s="26" t="inlineStr">
         <is>
-          <t>Competing supply</t>
+          <t>Competing supply / absorption</t>
         </is>
       </c>
       <c r="G222" s="26" t="inlineStr">
@@ -11942,7 +12025,7 @@
       </c>
       <c r="H222" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>72</t>
         </is>
       </c>
     </row>
@@ -11954,7 +12037,7 @@
       </c>
       <c r="B223" s="5" t="inlineStr">
         <is>
-          <t>supply_project_city</t>
+          <t>supply_project_product</t>
         </is>
       </c>
       <c r="C223" s="5" t="inlineStr">
@@ -11964,7 +12047,7 @@
       </c>
       <c r="D223" s="26" t="inlineStr">
         <is>
-          <t>City where a layer carried one.</t>
+          <t>Product the pipeline records for the development.</t>
         </is>
       </c>
       <c r="E223" s="5" t="inlineStr">
@@ -11984,7 +12067,7 @@
       </c>
       <c r="H223" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>multifamily</t>
         </is>
       </c>
     </row>
@@ -11996,17 +12079,17 @@
       </c>
       <c r="B224" s="5" t="inlineStr">
         <is>
-          <t>supply_project_acres</t>
+          <t>supply_project_address</t>
         </is>
       </c>
       <c r="C224" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D224" s="26" t="inlineStr">
         <is>
-          <t>Site acreage where a layer carried one.</t>
+          <t>Street address where a layer carried one.</t>
         </is>
       </c>
       <c r="E224" s="5" t="inlineStr">
@@ -12026,7 +12109,7 @@
       </c>
       <c r="H224" s="26" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -12038,7 +12121,7 @@
       </c>
       <c r="B225" s="5" t="inlineStr">
         <is>
-          <t>supply_project_developer</t>
+          <t>supply_project_city</t>
         </is>
       </c>
       <c r="C225" s="5" t="inlineStr">
@@ -12048,7 +12131,7 @@
       </c>
       <c r="D225" s="26" t="inlineStr">
         <is>
-          <t>Developer where a layer named one.</t>
+          <t>City where a layer carried one.</t>
         </is>
       </c>
       <c r="E225" s="5" t="inlineStr">
@@ -12080,17 +12163,17 @@
       </c>
       <c r="B226" s="5" t="inlineStr">
         <is>
-          <t>supply_project_filed</t>
+          <t>supply_project_acres</t>
         </is>
       </c>
       <c r="C226" s="5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D226" s="26" t="inlineStr">
         <is>
-          <t>Earliest filing date across the layers the development appears on.</t>
+          <t>Site acreage where a layer carried one.</t>
         </is>
       </c>
       <c r="E226" s="5" t="inlineStr">
@@ -12110,7 +12193,7 @@
       </c>
       <c r="H226" s="26" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>3.2</t>
         </is>
       </c>
     </row>
@@ -12122,17 +12205,17 @@
       </c>
       <c r="B227" s="5" t="inlineStr">
         <is>
-          <t>supply_project_latest</t>
+          <t>supply_project_developer</t>
         </is>
       </c>
       <c r="C227" s="5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D227" s="26" t="inlineStr">
         <is>
-          <t>Latest activity date across those layers.</t>
+          <t>Developer where a layer named one.</t>
         </is>
       </c>
       <c r="E227" s="5" t="inlineStr">
@@ -12152,7 +12235,7 @@
       </c>
       <c r="H227" s="26" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -12164,17 +12247,17 @@
       </c>
       <c r="B228" s="5" t="inlineStr">
         <is>
-          <t>supply_project_layers</t>
+          <t>supply_project_filed</t>
         </is>
       </c>
       <c r="C228" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D228" s="26" t="inlineStr">
         <is>
-          <t>The pipeline layers the development appeared on. Layers are lifecycle views of the same market, so one development can appear on several and is counted once.</t>
+          <t>Earliest filing date across the layers the development appears on.</t>
         </is>
       </c>
       <c r="E228" s="5" t="inlineStr">
@@ -12184,7 +12267,7 @@
       </c>
       <c r="F228" s="26" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Competing supply</t>
         </is>
       </c>
       <c r="G228" s="26" t="inlineStr">
@@ -12194,107 +12277,107 @@
       </c>
       <c r="H228" s="26" t="inlineStr">
         <is>
-          <t>1 entries</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="4" t="inlineStr">
-        <is>
-          <t>OM comparables</t>
-        </is>
-      </c>
-      <c r="B229" s="4" t="n"/>
-      <c r="C229" s="4" t="n"/>
-      <c r="D229" s="4" t="n"/>
-      <c r="E229" s="4" t="n"/>
-      <c r="F229" s="4" t="n"/>
-      <c r="G229" s="4" t="n"/>
-      <c r="H229" s="4" t="n"/>
+      <c r="A229" s="5" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="B229" s="5" t="inlineStr">
+        <is>
+          <t>supply_project_latest</t>
+        </is>
+      </c>
+      <c r="C229" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D229" s="26" t="inlineStr">
+        <is>
+          <t>Latest activity date across those layers.</t>
+        </is>
+      </c>
+      <c r="E229" s="5" t="inlineStr">
+        <is>
+          <t>Public permit / entitlement records</t>
+        </is>
+      </c>
+      <c r="F229" s="26" t="inlineStr">
+        <is>
+          <t>Competing supply</t>
+        </is>
+      </c>
+      <c r="G229" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H229" s="26" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="5" t="inlineStr">
         <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="B230" s="5" t="inlineStr">
+        <is>
+          <t>supply_project_layers</t>
+        </is>
+      </c>
+      <c r="C230" s="5" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D230" s="26" t="inlineStr">
+        <is>
+          <t>The pipeline layers the development appeared on. Layers are lifecycle views of the same market, so one development can appear on several and is counted once.</t>
+        </is>
+      </c>
+      <c r="E230" s="5" t="inlineStr">
+        <is>
+          <t>Public permit / entitlement records</t>
+        </is>
+      </c>
+      <c r="F230" s="26" t="inlineStr">
+        <is>
+          <t>Reference only — not a model input</t>
+        </is>
+      </c>
+      <c r="G230" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H230" s="26" t="inlineStr">
+        <is>
+          <t>1 entries</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="4" t="inlineStr">
+        <is>
           <t>OM comparables</t>
         </is>
       </c>
-      <c r="B230" s="5" t="inlineStr">
-        <is>
-          <t>om_rent_comp_community</t>
-        </is>
-      </c>
-      <c r="C230" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D230" s="26" t="inlineStr">
-        <is>
-          <t>A rent comparable the memorandum states, by name; one row per comparable in the interchange.</t>
-        </is>
-      </c>
-      <c r="E230" s="5" t="inlineStr">
-        <is>
-          <t>Offering memorandum / marketing package</t>
-        </is>
-      </c>
-      <c r="F230" s="26" t="inlineStr">
-        <is>
-          <t>Rent comps (broker-stated)</t>
-        </is>
-      </c>
-      <c r="G230" s="26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H230" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" s="5" t="inlineStr">
-        <is>
-          <t>OM comparables</t>
-        </is>
-      </c>
-      <c r="B231" s="5" t="inlineStr">
-        <is>
-          <t>om_rent_comp_distance_mi</t>
-        </is>
-      </c>
-      <c r="C231" s="5" t="inlineStr">
-        <is>
-          <t>number</t>
-        </is>
-      </c>
-      <c r="D231" s="26" t="inlineStr">
-        <is>
-          <t>Distance from the subject as the memorandum states it.</t>
-        </is>
-      </c>
-      <c r="E231" s="5" t="inlineStr">
-        <is>
-          <t>Offering memorandum / marketing package</t>
-        </is>
-      </c>
-      <c r="F231" s="26" t="inlineStr">
-        <is>
-          <t>Rent comps (broker-stated)</t>
-        </is>
-      </c>
-      <c r="G231" s="26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H231" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="B231" s="4" t="n"/>
+      <c r="C231" s="4" t="n"/>
+      <c r="D231" s="4" t="n"/>
+      <c r="E231" s="4" t="n"/>
+      <c r="F231" s="4" t="n"/>
+      <c r="G231" s="4" t="n"/>
+      <c r="H231" s="4" t="n"/>
     </row>
     <row r="232">
       <c r="A232" s="5" t="inlineStr">
@@ -12304,17 +12387,17 @@
       </c>
       <c r="B232" s="5" t="inlineStr">
         <is>
-          <t>om_rent_comp_rent</t>
+          <t>om_rent_comp_community</t>
         </is>
       </c>
       <c r="C232" s="5" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D232" s="26" t="inlineStr">
         <is>
-          <t>The monthly rent figure the memorandum states for that comparable; its basis is on the row.</t>
+          <t>A rent comparable the memorandum states, by name; one row per comparable in the interchange.</t>
         </is>
       </c>
       <c r="E232" s="5" t="inlineStr">
@@ -12346,17 +12429,17 @@
       </c>
       <c r="B233" s="5" t="inlineStr">
         <is>
-          <t>om_sale_comp_property</t>
+          <t>om_rent_comp_distance_mi</t>
         </is>
       </c>
       <c r="C233" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D233" s="26" t="inlineStr">
         <is>
-          <t>A whole-community sale comparable the memorandum cites, by name.</t>
+          <t>Distance from the subject as the memorandum states it.</t>
         </is>
       </c>
       <c r="E233" s="5" t="inlineStr">
@@ -12366,7 +12449,7 @@
       </c>
       <c r="F233" s="26" t="inlineStr">
         <is>
-          <t>Sale comps (institutional)</t>
+          <t>Rent comps (broker-stated)</t>
         </is>
       </c>
       <c r="G233" s="26" t="inlineStr">
@@ -12388,7 +12471,7 @@
       </c>
       <c r="B234" s="5" t="inlineStr">
         <is>
-          <t>om_sale_comp_price</t>
+          <t>om_rent_comp_rent</t>
         </is>
       </c>
       <c r="C234" s="5" t="inlineStr">
@@ -12398,7 +12481,7 @@
       </c>
       <c r="D234" s="26" t="inlineStr">
         <is>
-          <t>The stated sale price.</t>
+          <t>The monthly rent figure the memorandum states for that comparable; its basis is on the row.</t>
         </is>
       </c>
       <c r="E234" s="5" t="inlineStr">
@@ -12408,7 +12491,7 @@
       </c>
       <c r="F234" s="26" t="inlineStr">
         <is>
-          <t>Sale comps (institutional)</t>
+          <t>Rent comps (broker-stated)</t>
         </is>
       </c>
       <c r="G234" s="26" t="inlineStr">
@@ -12430,17 +12513,17 @@
       </c>
       <c r="B235" s="5" t="inlineStr">
         <is>
-          <t>om_sale_comp_price_per_unit</t>
+          <t>om_sale_comp_property</t>
         </is>
       </c>
       <c r="C235" s="5" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D235" s="26" t="inlineStr">
         <is>
-          <t>The stated price per unit.</t>
+          <t>A whole-community sale comparable the memorandum cites, by name.</t>
         </is>
       </c>
       <c r="E235" s="5" t="inlineStr">
@@ -12472,17 +12555,17 @@
       </c>
       <c r="B236" s="5" t="inlineStr">
         <is>
-          <t>om_sale_comp_cap_rate</t>
+          <t>om_sale_comp_price</t>
         </is>
       </c>
       <c r="C236" s="5" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D236" s="26" t="inlineStr">
         <is>
-          <t>The stated cap rate, as a fraction.</t>
+          <t>The stated sale price.</t>
         </is>
       </c>
       <c r="E236" s="5" t="inlineStr">
@@ -12514,35 +12597,119 @@
       </c>
       <c r="B237" s="5" t="inlineStr">
         <is>
+          <t>om_sale_comp_price_per_unit</t>
+        </is>
+      </c>
+      <c r="C237" s="5" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D237" s="26" t="inlineStr">
+        <is>
+          <t>The stated price per unit.</t>
+        </is>
+      </c>
+      <c r="E237" s="5" t="inlineStr">
+        <is>
+          <t>Offering memorandum / marketing package</t>
+        </is>
+      </c>
+      <c r="F237" s="26" t="inlineStr">
+        <is>
+          <t>Sale comps (institutional)</t>
+        </is>
+      </c>
+      <c r="G237" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H237" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="5" t="inlineStr">
+        <is>
+          <t>OM comparables</t>
+        </is>
+      </c>
+      <c r="B238" s="5" t="inlineStr">
+        <is>
+          <t>om_sale_comp_cap_rate</t>
+        </is>
+      </c>
+      <c r="C238" s="5" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D238" s="26" t="inlineStr">
+        <is>
+          <t>The stated cap rate, as a fraction.</t>
+        </is>
+      </c>
+      <c r="E238" s="5" t="inlineStr">
+        <is>
+          <t>Offering memorandum / marketing package</t>
+        </is>
+      </c>
+      <c r="F238" s="26" t="inlineStr">
+        <is>
+          <t>Sale comps (institutional)</t>
+        </is>
+      </c>
+      <c r="G238" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H238" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="5" t="inlineStr">
+        <is>
+          <t>OM comparables</t>
+        </is>
+      </c>
+      <c r="B239" s="5" t="inlineStr">
+        <is>
           <t>om_sale_comp_date</t>
         </is>
       </c>
-      <c r="C237" s="5" t="inlineStr">
+      <c r="C239" s="5" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="D237" s="26" t="inlineStr">
+      <c r="D239" s="26" t="inlineStr">
         <is>
           <t>The sale date as written.</t>
         </is>
       </c>
-      <c r="E237" s="5" t="inlineStr">
+      <c r="E239" s="5" t="inlineStr">
         <is>
           <t>Offering memorandum / marketing package</t>
         </is>
       </c>
-      <c r="F237" s="26" t="inlineStr">
+      <c r="F239" s="26" t="inlineStr">
         <is>
           <t>Sale comps (institutional)</t>
         </is>
       </c>
-      <c r="G237" s="26" t="inlineStr">
+      <c r="G239" s="26" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H237" s="26" t="inlineStr">
+      <c r="H239" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/public/downloads/underwriting-demo/sample-underwriting-pack.xlsx
+++ b/public/downloads/underwriting-demo/sample-underwriting-pack.xlsx
@@ -4535,7 +4535,7 @@
       </c>
       <c r="H33" s="26" t="inlineStr">
         <is>
-          <t>1,981</t>
+          <t>1981</t>
         </is>
       </c>
     </row>
@@ -5767,7 +5767,7 @@
       </c>
       <c r="H65" s="26" t="inlineStr">
         <is>
-          <t>2,025</t>
+          <t>2025</t>
         </is>
       </c>
     </row>
@@ -10443,7 +10443,7 @@
       </c>
       <c r="H183" s="26" t="inlineStr">
         <is>
-          <t>1,984</t>
+          <t>1984</t>
         </is>
       </c>
     </row>
@@ -10633,7 +10633,7 @@
       </c>
       <c r="D188" s="26" t="inlineStr">
         <is>
-          <t>Unit count where the registry has one.</t>
+          <t>Unit count where the registry has one. The registry was seeded from licensed data exports, so the public demo withholds it.</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
@@ -10648,12 +10648,12 @@
       </c>
       <c r="G188" s="26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Internal pipeline only — Unit counts come from a licensed data export; the internal pipeline carries them.</t>
         </is>
       </c>
       <c r="H188" s="26" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>MISSING</t>
         </is>
       </c>
     </row>
@@ -12726,7 +12726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -12776,7 +12776,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
@@ -12934,22 +12934,22 @@
     <row r="12">
       <c r="A12" s="30" t="inlineStr">
         <is>
-          <t>comps.rows</t>
+          <t>comps.nearby[].units</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>19 entries</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape, via the market-report service</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>POST /report (format json)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12960,94 +12960,94 @@
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="26" t="inlineStr">
         <is>
-          <t>Own weekly scrape; asking and net effective stated separately.</t>
+          <t>Unit counts come from a licensed data export; the internal pipeline carries them.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="30" t="inlineStr">
         <is>
-          <t>comps.rows.tier</t>
+          <t>comps.rows</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19 entries</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Tracked-community registry, via the market-report service</t>
+          <t>Operator's own weekly rent scrape, via the market-report service</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>comp_tiers.assign</t>
+          <t>POST /report (format json)</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>comps.rows.distance_mi, comps.tiering.subject_product, comps.tiering.subject_year_built, comps.tiering.year_band, comps.tiering.top_n, comps.tiering.additional_n</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="n"/>
       <c r="G13" s="26" t="inlineStr">
         <is>
-          <t>Closest same-product communities first, within the vintage band where the registry carries a year built; an unknown year keeps the community and says so.</t>
+          <t>Own weekly scrape; asking and net effective stated separately.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="30" t="inlineStr">
         <is>
-          <t>demand.rings</t>
+          <t>comps.rows.tier</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>5 entries</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Public demographic data (the operator's ring engine), via the market-report service</t>
+          <t>Tracked-community registry, via the market-report service</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>POST /report (format json)</t>
+          <t>comp_tiers.assign</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F14" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>comps.rows.distance_mi, comps.tiering.subject_product, comps.tiering.subject_year_built, comps.tiering.year_band, comps.tiering.top_n, comps.tiering.additional_n</t>
+        </is>
+      </c>
       <c r="G14" s="26" t="inlineStr">
         <is>
-          <t>Ring demographics.</t>
+          <t>Closest same-product communities first, within the vintage band where the registry carries a year built; an unknown year keeps the community and says so.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="30" t="inlineStr">
         <is>
-          <t>demand.zip_home</t>
+          <t>demand.rings</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5 entries</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Zillow ZHVI home values (vendored static table, undated), via the market-report service</t>
+          <t>Public demographic data (the operator's ring engine), via the market-report service</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -13063,29 +13063,29 @@
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="26" t="inlineStr">
         <is>
-          <t>ZIP and metro home values from the vendored Zillow ZHVI table; static, undated.</t>
+          <t>Ring demographics.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>om_comps.rent</t>
+          <t>demand.zip_home</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>0 entries</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Zillow ZHVI home values (vendored static table, undated), via the market-report service</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>p.20</t>
+          <t>POST /report (format json)</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="26" t="inlineStr">
         <is>
-          <t>4 rent comparable(s) the memorandum states; every figure verified inside its own quote.</t>
+          <t>ZIP and metro home values from the vendored Zillow ZHVI table; static, undated.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="30" t="inlineStr">
         <is>
-          <t>pricing.price_per_unit</t>
+          <t>om_comps.rent</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>215,000</t>
+          <t>0 entries</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Illustrative price</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.20</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13129,24 +13129,24 @@
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="26" t="inlineStr">
         <is>
-          <t>Per-unit price chosen for the sample, inside the sale-price band; every cap rate and pricing ladder is computed from it.</t>
+          <t>4 rent comparable(s) the memorandum states; every figure verified inside its own quote.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="30" t="inlineStr">
         <is>
-          <t>pricing.unit_count</t>
+          <t>pricing.price_per_unit</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>215,000</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Sample Property RR 8.4.26.xlsx</t>
+          <t>Illustrative price</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -13156,29 +13156,25 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>summary.unit_count</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="n"/>
       <c r="G18" s="26" t="inlineStr">
         <is>
-          <t>The same count the summary carries, counted from the rows of the uploaded rent roll.</t>
+          <t>Per-unit price chosen for the sample, inside the sale-price band; every cap rate and pricing ladder is computed from it.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="30" t="inlineStr">
         <is>
-          <t>rent_roll.as_of</t>
+          <t>pricing.unit_count</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>334</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -13188,40 +13184,44 @@
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>as-of line</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F19" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>summary.unit_count</t>
+        </is>
+      </c>
       <c r="G19" s="26" t="inlineStr">
         <is>
-          <t>Read as the end of the period the roll's own header states.</t>
+          <t>The same count the summary carries, counted from the rows of the uploaded rent roll.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="30" t="inlineStr">
         <is>
-          <t>rent_roll.lookback_months</t>
+          <t>rent_roll.as_of</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>Not stated in the uploaded documents</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>as-of line</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -13232,19 +13232,19 @@
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="26" t="inlineStr">
         <is>
-          <t>This demo's default of 12 — the months of lease history the turnover figures look back over. No uploaded document or note set it.</t>
+          <t>Read as the end of the period the roll's own header states.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="30" t="inlineStr">
         <is>
-          <t>rent_roll.new_tenant_tolerance_days</t>
+          <t>rent_roll.lookback_months</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -13265,29 +13265,29 @@
       <c r="F21" s="12" t="n"/>
       <c r="G21" s="26" t="inlineStr">
         <is>
-          <t>This demo's default of 31 — the days a lease start may sit from a move-in and still count as the same event. No uploaded document or note set it.</t>
+          <t>This demo's default of 12 — the months of lease history the turnover figures look back over. No uploaded document or note set it.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="30" t="inlineStr">
         <is>
-          <t>rent_roll.units</t>
+          <t>rent_roll.new_tenant_tolerance_days</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>334 entries</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Sample Property RR 8.4.26.xlsx</t>
+          <t>Not stated in the uploaded documents</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>roll</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -13298,29 +13298,29 @@
       <c r="F22" s="12" t="n"/>
       <c r="G22" s="26" t="inlineStr">
         <is>
-          <t>Read from the uploaded rent roll.</t>
+          <t>This demo's default of 31 — the days a lease start may sit from a move-in and still count as the same event. No uploaded document or note set it.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="30" t="inlineStr">
         <is>
-          <t>summary.address_provenance</t>
+          <t>rent_roll.units</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for t…</t>
+          <t>334 entries</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>roll</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13331,24 +13331,24 @@
       <c r="F23" s="12" t="n"/>
       <c r="G23" s="26" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>Read from the uploaded rent roll.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="30" t="inlineStr">
         <is>
-          <t>summary.assessed_value_basis</t>
+          <t>summary.address_provenance</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for t…</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
@@ -13364,29 +13364,29 @@
       <c r="F24" s="12" t="n"/>
       <c r="G24" s="26" t="inlineStr">
         <is>
-          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="30" t="inlineStr">
         <is>
-          <t>summary.assessment_ratio</t>
+          <t>summary.assessed_value_basis</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Vendored county rate table</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>property_tax_table.STATE_RULES['AZ']</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -13397,29 +13397,29 @@
       <c r="F25" s="12" t="n"/>
       <c r="G25" s="26" t="inlineStr">
         <is>
-          <t>10% — legal class 4.2, residential rental. A.R.S. sec. 42-15003 (class four assessed at 10%); A.R.S. sec. 42-12004 (class four includes residential rental property).</t>
+          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="30" t="inlineStr">
         <is>
-          <t>summary.city</t>
+          <t>summary.assessment_ratio</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>property_tax_table.STATE_RULES['AZ']</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13430,24 +13430,24 @@
       <c r="F26" s="12" t="n"/>
       <c r="G26" s="26" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>10% — legal class 4.2, residential rental. A.R.S. sec. 42-15003 (class four assessed at 10%); A.R.S. sec. 42-12004 (class four includes residential rental property).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="30" t="inlineStr">
         <is>
-          <t>summary.construction_status</t>
+          <t>summary.city</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Mesa</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Not stated in the uploaded documents</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -13463,24 +13463,24 @@
       <c r="F27" s="12" t="n"/>
       <c r="G27" s="26" t="inlineStr">
         <is>
-          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="30" t="inlineStr">
         <is>
-          <t>summary.county</t>
+          <t>summary.construction_status</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>Maricopa</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Not stated in the uploaded documents</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -13496,24 +13496,24 @@
       <c r="F28" s="12" t="n"/>
       <c r="G28" s="26" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="30" t="inlineStr">
         <is>
-          <t>summary.deal_name</t>
+          <t>summary.county</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Sample Mesa Apt</t>
+          <t>Maricopa</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Illustrative name</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -13529,24 +13529,24 @@
       <c r="F29" s="12" t="n"/>
       <c r="G29" s="26" t="inlineStr">
         <is>
-          <t>An illustrative name for the public sample. The real asset's name is withheld; the memorandum's own name for it does not appear anywhere in this set.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="30" t="inlineStr">
         <is>
-          <t>summary.deal_status</t>
+          <t>summary.deal_name</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Sample Mesa Apt</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Not stated in the uploaded documents</t>
+          <t>Illustrative name</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -13562,14 +13562,14 @@
       <c r="F30" s="12" t="n"/>
       <c r="G30" s="26" t="inlineStr">
         <is>
-          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
+          <t>An illustrative name for the public sample. The real asset's name is withheld; the memorandum's own name for it does not appear anywhere in this set.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="30" t="inlineStr">
         <is>
-          <t>summary.delivery_date</t>
+          <t>summary.deal_status</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
@@ -13602,7 +13602,7 @@
     <row r="32">
       <c r="A32" s="30" t="inlineStr">
         <is>
-          <t>summary.fair_market_value</t>
+          <t>summary.delivery_date</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -13612,7 +13612,7 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Not stated in the uploaded documents</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -13628,24 +13628,24 @@
       <c r="F32" s="12" t="n"/>
       <c r="G32" s="26" t="inlineStr">
         <is>
-          <t>The internal pipeline pulls a market value by web lookup; the demo does not reach the web.</t>
+          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="30" t="inlineStr">
         <is>
-          <t>summary.in_place_rent_avg</t>
+          <t>summary.fair_market_value</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>1,456.99</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Sample Property RR 8.4.26.xlsx</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -13655,34 +13655,30 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>rent_roll.units</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F33" s="12" t="n"/>
       <c r="G33" s="26" t="inlineStr">
         <is>
-          <t>Unit-weighted across the uploaded roll.</t>
+          <t>The internal pipeline pulls a market value by web lookup; the demo does not reach the web.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="30" t="inlineStr">
         <is>
-          <t>summary.listing_brokerage</t>
+          <t>summary.in_place_rent_avg</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>Desert Ridge Capital Advisors</t>
+          <t>1,456.99</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Illustrative name</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -13692,30 +13688,34 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F34" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>rent_roll.units</t>
+        </is>
+      </c>
       <c r="G34" s="26" t="inlineStr">
         <is>
-          <t>An illustrative name. The real party is withheld from the public sample.</t>
+          <t>Unit-weighted across the uploaded roll.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="30" t="inlineStr">
         <is>
-          <t>summary.market_rent_for_model</t>
+          <t>summary.listing_brokerage</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>1,344.6</t>
+          <t>Desert Ridge Capital Advisors</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Sample Property RR 8.4.26.xlsx</t>
+          <t>Illustrative name</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -13725,34 +13725,30 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>rent_roll.units</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="n"/>
       <c r="G35" s="26" t="inlineStr">
         <is>
-          <t>Unit-weighted across the uploaded roll.</t>
+          <t>An illustrative name. The real party is withheld from the public sample.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="30" t="inlineStr">
         <is>
-          <t>summary.msa</t>
+          <t>summary.market_rent_for_model</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Phoenix MSA</t>
+          <t>1,344.6</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -13762,30 +13758,34 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F36" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>rent_roll.units</t>
+        </is>
+      </c>
       <c r="G36" s="26" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>Unit-weighted across the uploaded roll.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="30" t="inlineStr">
         <is>
-          <t>summary.pricing_guidance</t>
+          <t>summary.msa</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>$215,000 per unit (illustrative)</t>
+          <t>Phoenix MSA</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Illustrative price</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -13801,29 +13801,29 @@
       <c r="F37" s="12" t="n"/>
       <c r="G37" s="26" t="inlineStr">
         <is>
-          <t>Every price and cap rate below is illustrative. The per-unit price is a round number chosen for the sample inside the band a real per-unit sale price occupies; it is not a quote, an offer, or a broker's guidance.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="30" t="inlineStr">
         <is>
-          <t>summary.product_detail</t>
+          <t>summary.pricing_guidance</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Diversified mix of one-, two-, and three-bedroom residences averaging 856 square feet o…</t>
+          <t>$215,000 per unit (illustrative)</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Illustrative price</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>p.3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -13833,6 +13833,39 @@
       </c>
       <c r="F38" s="12" t="n"/>
       <c r="G38" s="26" t="inlineStr">
+        <is>
+          <t>Every price and cap rate below is illustrative. The per-unit price is a round number chosen for the sample inside the band a real per-unit sale price occupies; it is not a quote, an offer, or a broker's guidance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="30" t="inlineStr">
+        <is>
+          <t>summary.product_detail</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Diversified mix of one-, two-, and three-bedroom residences averaging 856 square feet o…</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Sample Property Offering Memorandum.pdf</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>p.3</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F39" s="12" t="n"/>
+      <c r="G39" s="26" t="inlineStr">
         <is>
           <t>the property offers a diversified mix of 
 one-, two-, and three-bedroom residences averaging 856 square 
@@ -13840,58 +13873,25 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="30" t="inlineStr">
-        <is>
-          <t>summary.product_type</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>Garden-style multifamily</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="inlineStr">
-        <is>
-          <t>p.3</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F39" s="12" t="n"/>
-      <c r="G39" s="26" t="inlineStr">
-        <is>
-          <t>Stated in the memorandum; withheld from the public sample because it identifies the real asset.</t>
-        </is>
-      </c>
-    </row>
     <row r="40">
       <c r="A40" s="30" t="inlineStr">
         <is>
-          <t>summary.school_elementary_name</t>
+          <t>summary.product_type</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Porter Elementary School</t>
+          <t>Garden-style multifamily</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Internal underwriting agent — attendance-zone school lookup</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>2151 E Southern Ave, Mesa, AZ 85204 on 2026-09-14</t>
+          <t>p.3</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -13902,19 +13902,19 @@
       <c r="F40" s="12" t="n"/>
       <c r="G40" s="26" t="inlineStr">
         <is>
-          <t>Looked up for the illustrative address by the internal underwriting agent; the public demo does not run this on an uploaded deal.</t>
+          <t>Stated in the memorandum; withheld from the public sample because it identifies the real asset.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="30" t="inlineStr">
         <is>
-          <t>summary.school_high_name</t>
+          <t>summary.school_elementary_name</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Mesa High School</t>
+          <t>Porter Elementary School</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -13942,12 +13942,12 @@
     <row r="42">
       <c r="A42" s="30" t="inlineStr">
         <is>
-          <t>summary.school_middle_name</t>
+          <t>summary.school_high_name</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Taylor Junior High School</t>
+          <t>Mesa High School</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -13975,22 +13975,22 @@
     <row r="43">
       <c r="A43" s="30" t="inlineStr">
         <is>
-          <t>summary.seller_entity</t>
+          <t>summary.school_middle_name</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Sonoran Residential Holdings LLC</t>
+          <t>Taylor Junior High School</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Illustrative name</t>
+          <t>Internal underwriting agent — attendance-zone school lookup</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2151 E Southern Ave, Mesa, AZ 85204 on 2026-09-14</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -14001,24 +14001,24 @@
       <c r="F43" s="12" t="n"/>
       <c r="G43" s="26" t="inlineStr">
         <is>
-          <t>An illustrative name. The real party is withheld from the public sample.</t>
+          <t>Looked up for the illustrative address by the internal underwriting agent; the public demo does not run this on an uploaded deal.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="30" t="inlineStr">
         <is>
-          <t>summary.state</t>
+          <t>summary.seller_entity</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Sonoran Residential Holdings LLC</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Illustrative name</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -14034,19 +14034,19 @@
       <c r="F44" s="12" t="n"/>
       <c r="G44" s="26" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>An illustrative name. The real party is withheld from the public sample.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="30" t="inlineStr">
         <is>
-          <t>summary.street_address</t>
+          <t>summary.state</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>2151 E Southern Ave</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -14074,22 +14074,22 @@
     <row r="46">
       <c r="A46" s="30" t="inlineStr">
         <is>
-          <t>summary.structure</t>
+          <t>summary.street_address</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>1 &amp; 2 stories</t>
+          <t>2151 E Southern Ave</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>p.10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -14100,29 +14100,29 @@
       <c r="F46" s="12" t="n"/>
       <c r="G46" s="26" t="inlineStr">
         <is>
-          <t>Number of Stories 1 &amp; 2</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="30" t="inlineStr">
         <is>
-          <t>summary.tax_area_code</t>
+          <t>summary.structure</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>1 &amp; 2 stories</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.10</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14133,29 +14133,29 @@
       <c r="F47" s="12" t="n"/>
       <c r="G47" s="26" t="inlineStr">
         <is>
-          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+          <t>Number of Stories 1 &amp; 2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="30" t="inlineStr">
         <is>
-          <t>summary.tax_basis_label</t>
+          <t>summary.tax_area_code</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>Limited property value (LPV), per the county assessor</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Vendored county rate table</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>property_tax_table.STATE_RULES['AZ']</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14166,19 +14166,19 @@
       <c r="F48" s="12" t="n"/>
       <c r="G48" s="26" t="inlineStr">
         <is>
-          <t>What the assessed basis is in this state.</t>
+          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="30" t="inlineStr">
         <is>
-          <t>summary.tax_basis_note</t>
+          <t>summary.tax_basis_label</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Arizona taxes the limited property value, not the price. Under Proposition 117 (Ariz. C…</t>
+          <t>Limited property value (LPV), per the county assessor</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
@@ -14199,29 +14199,29 @@
       <c r="F49" s="12" t="n"/>
       <c r="G49" s="26" t="inlineStr">
         <is>
-          <t>How the basis behaves on a sale, with the authority.</t>
+          <t>What the assessed basis is in this state.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="30" t="inlineStr">
         <is>
-          <t>summary.tax_billed_amount</t>
+          <t>summary.tax_basis_note</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>249,122</t>
+          <t>Arizona taxes the limited property value, not the price. Under Proposition 117 (Ariz. C…</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>p.10</t>
+          <t>property_tax_table.STATE_RULES['AZ']</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -14232,19 +14232,19 @@
       <c r="F50" s="12" t="n"/>
       <c r="G50" s="26" t="inlineStr">
         <is>
-          <t>2025 Property Tax $249,122</t>
+          <t>How the basis behaves on a sale, with the authority.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="30" t="inlineStr">
         <is>
-          <t>summary.tax_billed_year</t>
+          <t>summary.tax_billed_amount</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>2,025</t>
+          <t>249,122</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -14272,22 +14272,22 @@
     <row r="52">
       <c r="A52" s="30" t="inlineStr">
         <is>
-          <t>summary.tax_divisor</t>
+          <t>summary.tax_billed_year</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2,025</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>Vendored county rate table</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>property_tax_table.STATE_RULES['AZ']</t>
+          <t>p.10</t>
         </is>
       </c>
       <c r="E52" s="5" t="inlineStr">
@@ -14298,29 +14298,29 @@
       <c r="F52" s="12" t="n"/>
       <c r="G52" s="26" t="inlineStr">
         <is>
-          <t>The rate's unit in Arizona: per $100 of assessed value.</t>
+          <t>2025 Property Tax $249,122</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="30" t="inlineStr">
         <is>
-          <t>summary.tax_exemption</t>
+          <t>summary.tax_divisor</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>property_tax_table.STATE_RULES['AZ']</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14331,29 +14331,29 @@
       <c r="F53" s="12" t="n"/>
       <c r="G53" s="26" t="inlineStr">
         <is>
-          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+          <t>The rate's unit in Arizona: per $100 of assessed value.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="30" t="inlineStr">
         <is>
-          <t>summary.tax_parcel_id</t>
+          <t>summary.tax_exemption</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>301-04-002K</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>p.10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14364,56 +14364,52 @@
       <c r="F54" s="12" t="n"/>
       <c r="G54" s="26" t="inlineStr">
         <is>
-          <t>Tax Parcel Number 301-04-002K</t>
+          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="30" t="inlineStr">
         <is>
-          <t>summary.tax_per_unit_flag</t>
+          <t>summary.tax_parcel_id</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>In band (the statement's line per unit): $717 per unit a year is inside the AZ band of …</t>
+          <t>301-04-002K</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Vendored county rate table</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>property_tax_table.band_check</t>
+          <t>p.10</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>summary.tax_statement_amount, summary.unit_count, summary.state</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F55" s="12" t="n"/>
       <c r="G55" s="26" t="inlineStr">
         <is>
-          <t>A sanity check against the state's typical per-unit range. It flags; it never changes a figure.</t>
+          <t>Tax Parcel Number 301-04-002K</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="30" t="inlineStr">
         <is>
-          <t>summary.tax_rate_as_billed</t>
+          <t>summary.tax_per_unit_flag</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>In band (the statement's line per unit): $717 per unit a year is inside the AZ band of …</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
@@ -14423,30 +14419,34 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>property_tax_table.COUNTY_RATES[('AZ', 'maricopa')]</t>
+          <t>property_tax_table.band_check</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F56" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>summary.tax_statement_amount, summary.unit_count, summary.state</t>
+        </is>
+      </c>
       <c r="G56" s="26" t="inlineStr">
         <is>
-          <t>Tax area code 971300 — City of Phoenix / Deer Valley Unified School District #97, tax year 2025. Maricopa County, '2025 Tax Rates, Maricopa County, Arizona' (the treasurer's rate table by tax area code), row 971300: primary 6.7007, approx residential primary 5.1401, secondary 3.5566. Verified 2026-09-04.</t>
+          <t>A sanity check against the state's typical per-unit range. It flags; it never changes a figure.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="30" t="inlineStr">
         <is>
-          <t>summary.tax_rate_evidence</t>
+          <t>summary.tax_rate_as_billed</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>Vendored county rate table: 10.2573 per $100 of assessed value, tax year 2025 — Tax are…</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -14456,34 +14456,30 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>property_tax_table.evidence_text</t>
+          <t>property_tax_table.COUNTY_RATES[('AZ', 'maricopa')]</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>summary.state, summary.county, summary.tax_parcel_id, summary.tax_billed_amount, summary.tax_billed_year</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F57" s="12" t="n"/>
       <c r="G57" s="26" t="inlineStr">
         <is>
-          <t>The citation, tax year and jurisdiction stack behind the rate, or the honest note that none is on file. Also records what the uploaded document stated for the field(s) it cites.</t>
+          <t>Tax area code 971300 — City of Phoenix / Deer Valley Unified School District #97, tax year 2025. Maricopa County, '2025 Tax Rates, Maricopa County, Arizona' (the treasurer's rate table by tax area code), row 971300: primary 6.7007, approx residential primary 5.1401, secondary 3.5566. Verified 2026-09-04.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="30" t="inlineStr">
         <is>
-          <t>summary.tax_rate_year</t>
+          <t>summary.tax_rate_evidence</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>2,025</t>
+          <t>Vendored county rate table: 10.2573 per $100 of assessed value, tax year 2025 — Tax are…</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -14493,147 +14489,151 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>property_tax_table.COUNTY_RATES[('AZ', 'maricopa')]</t>
+          <t>property_tax_table.evidence_text</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F58" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>summary.state, summary.county, summary.tax_parcel_id, summary.tax_billed_amount, summary.tax_billed_year</t>
+        </is>
+      </c>
       <c r="G58" s="26" t="inlineStr">
         <is>
-          <t>The tax year of the rate on file. A bill from another year is displayed, not tied out.</t>
+          <t>The citation, tax year and jurisdiction stack behind the rate, or the honest note that none is on file. Also records what the uploaded document stated for the field(s) it cites.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="30" t="inlineStr">
         <is>
-          <t>summary.tax_statement_amount</t>
+          <t>summary.tax_rate_year</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>239,566.79</t>
+          <t>2,025</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>Sample Property T-12 June 26.xlsx</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Property Taxes lines</t>
+          <t>property_tax_table.COUNTY_RATES[('AZ', 'maricopa')]</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>computed</t>
-        </is>
-      </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>t12.rows</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F59" s="12" t="n"/>
       <c r="G59" s="26" t="inlineStr">
         <is>
-          <t>The statement's lines categorised as Property Taxes, summed over its twelve months. As billed in the statement, not the county's bill.</t>
+          <t>The tax year of the rate on file. A bill from another year is displayed, not tied out.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="30" t="inlineStr">
         <is>
-          <t>summary.unit_count</t>
+          <t>summary.tax_statement_amount</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>239,566.79</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Sample Property RR 8.4.26.xlsx</t>
+          <t>Sample Property T-12 June 26.xlsx</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Property Taxes lines</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>computed</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>rent_roll.units</t>
+          <t>t12.rows</t>
         </is>
       </c>
       <c r="G60" s="26" t="inlineStr">
         <is>
-          <t>Counted from the rows of the uploaded rent roll.</t>
+          <t>The statement's lines categorised as Property Taxes, summed over its twelve months. As billed in the statement, not the county's bill.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="30" t="inlineStr">
         <is>
-          <t>summary.year_built</t>
+          <t>summary.unit_count</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>1,981</t>
+          <t>334</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>p.10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F61" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>rent_roll.units</t>
+        </is>
+      </c>
       <c r="G61" s="26" t="inlineStr">
         <is>
-          <t>Y ear Built 1981</t>
+          <t>Counted from the rows of the uploaded rent roll.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="30" t="inlineStr">
         <is>
-          <t>summary.zip</t>
+          <t>summary.year_built</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>85204</t>
+          <t>1,981</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.10</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
@@ -14644,99 +14644,99 @@
       <c r="F62" s="12" t="n"/>
       <c r="G62" s="26" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>Y ear Built 1981</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="30" t="inlineStr">
         <is>
-          <t>supply.projects</t>
+          <t>summary.zip</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>32 entries</t>
+          <t>85204</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Public permit and entitlement records (the operator's supply pipeline), via the market-report service</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>POST /report (format json)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>supply.rings</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F63" s="12" t="n"/>
       <c r="G63" s="26" t="inlineStr">
         <is>
-          <t>The developments the counts are made of, within 3 mi: one row per development, reconciled across the pipeline's lifecycle layers and shown at the furthest stage any layer carries.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="30" t="inlineStr">
         <is>
+          <t>supply.projects</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>32 entries</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>Public permit and entitlement records (the operator's supply pipeline), via the market-report service</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr">
+        <is>
+          <t>POST /report (format json)</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
           <t>supply.rings</t>
         </is>
       </c>
-      <c r="B64" s="5" t="inlineStr">
-        <is>
-          <t>8 entries</t>
-        </is>
-      </c>
-      <c r="C64" s="5" t="inlineStr">
-        <is>
-          <t>Public permit and entitlement records (the operator's supply pipeline), via the market-report service</t>
-        </is>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>POST /report (format json)</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F64" s="12" t="n"/>
       <c r="G64" s="26" t="inlineStr">
         <is>
-          <t>Projects and units by cumulative ring and tracked stage, counted from the service's project rows.</t>
+          <t>The developments the counts are made of, within 3 mi: one row per development, reconciled across the pipeline's lifecycle layers and shown at the furthest stage any layer carries.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="30" t="inlineStr">
         <is>
-          <t>t12.month_labels</t>
+          <t>supply.rings</t>
         </is>
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>12 entries</t>
+          <t>8 entries</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Sample Property T-12 June 26.xlsx</t>
+          <t>Public permit and entitlement records (the operator's supply pipeline), via the market-report service</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>statement</t>
+          <t>POST /report (format json)</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
@@ -14747,19 +14747,19 @@
       <c r="F65" s="12" t="n"/>
       <c r="G65" s="26" t="inlineStr">
         <is>
-          <t>Read from the uploaded statement.</t>
+          <t>Projects and units by cumulative ring and tracked stage, counted from the service's project rows.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="30" t="inlineStr">
         <is>
-          <t>t12.source_subtotals</t>
+          <t>t12.month_labels</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>4 keys</t>
+          <t>12 entries</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
@@ -14769,7 +14769,7 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>header block</t>
+          <t>statement</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -14778,17 +14778,21 @@
         </is>
       </c>
       <c r="F66" s="12" t="n"/>
-      <c r="G66" s="31" t="n"/>
+      <c r="G66" s="26" t="inlineStr">
+        <is>
+          <t>Read from the uploaded statement.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="30" t="inlineStr">
         <is>
-          <t>t12.units</t>
+          <t>t12.source_subtotals</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>4 keys</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -14798,7 +14802,7 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>statement</t>
+          <t>header block</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -14807,31 +14811,27 @@
         </is>
       </c>
       <c r="F67" s="12" t="n"/>
-      <c r="G67" s="26" t="inlineStr">
-        <is>
-          <t>Read from the uploaded statement.</t>
-        </is>
-      </c>
+      <c r="G67" s="31" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="30" t="inlineStr">
         <is>
-          <t>trade_out.rows</t>
+          <t>t12.units</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>0 entries</t>
+          <t>334</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Sample Property T-12 June 26.xlsx</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>statement</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -14841,6 +14841,39 @@
       </c>
       <c r="F68" s="12" t="n"/>
       <c r="G68" s="26" t="inlineStr">
+        <is>
+          <t>Read from the uploaded statement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="30" t="inlineStr">
+        <is>
+          <t>trade_out.rows</t>
+        </is>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>0 entries</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
+          <t>Internal pipeline only</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F69" s="12" t="n"/>
+      <c r="G69" s="26" t="inlineStr">
         <is>
           <t>The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
         </is>
@@ -14857,7 +14890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I106"/>
+  <dimension ref="A1:I107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -15965,139 +15998,124 @@
         <v>-0.1242759499897198</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Home values: Zillow Home Value Index (ZHVI), Zillow Group</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>Labor market</t>
         </is>
       </c>
-      <c r="B57" s="4" t="n"/>
-      <c r="C57" s="4" t="n"/>
-      <c r="D57" s="4" t="n"/>
-      <c r="E57" s="4" t="n"/>
-      <c r="F57" s="4" t="n"/>
-      <c r="G57" s="4" t="n"/>
-      <c r="H57" s="4" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
+      <c r="B58" s="4" t="n"/>
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="n"/>
+      <c r="E58" s="4" t="n"/>
+      <c r="F58" s="4" t="n"/>
+      <c r="G58" s="4" t="n"/>
+      <c r="H58" s="4" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
         <is>
           <t>Ring job counts are WORKPLACE counts — jobs located inside the ring, not residents who hold jobs. The unemployment row above is the opposite: residents. The two answer different questions and are not interchangeable.</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="14" t="inlineStr"/>
-      <c r="B59" s="14" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="14" t="inlineStr"/>
+      <c r="B60" s="14" t="inlineStr">
         <is>
           <t>1 mi</t>
         </is>
       </c>
-      <c r="C59" s="14" t="inlineStr">
+      <c r="C60" s="14" t="inlineStr">
         <is>
           <t>3 mi</t>
         </is>
       </c>
-      <c r="D59" s="14" t="inlineStr">
+      <c r="D60" s="14" t="inlineStr">
         <is>
           <t>5 mi</t>
         </is>
       </c>
-      <c r="E59" s="14" t="inlineStr">
+      <c r="E60" s="14" t="inlineStr">
         <is>
           <t>10 mi</t>
         </is>
       </c>
-      <c r="F59" s="14" t="inlineStr">
+      <c r="F60" s="14" t="inlineStr">
         <is>
           <t>Phoenix MSA</t>
         </is>
       </c>
-      <c r="G59" s="14" t="inlineStr">
+      <c r="G60" s="14" t="inlineStr">
         <is>
           <t>Arizona</t>
         </is>
       </c>
-      <c r="H59" s="14" t="inlineStr">
+      <c r="H60" s="14" t="inlineStr">
         <is>
           <t>U.S.</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>Unemployment rate (residents, ACS)</t>
         </is>
       </c>
-      <c r="B60" s="11" t="n">
+      <c r="B61" s="11" t="n">
         <v>0.052</v>
       </c>
-      <c r="C60" s="11" t="n">
+      <c r="C61" s="11" t="n">
         <v>0.046</v>
       </c>
-      <c r="D60" s="11" t="n">
+      <c r="D61" s="11" t="n">
         <v>0.045</v>
       </c>
-      <c r="E60" s="11" t="n">
+      <c r="E61" s="11" t="n">
         <v>0.043</v>
       </c>
-      <c r="F60" s="11" t="n">
+      <c r="F61" s="11" t="n">
         <v>0.047</v>
       </c>
-      <c r="G60" s="11" t="n">
+      <c r="G61" s="11" t="n">
         <v>0.051</v>
       </c>
-      <c r="H60" s="11" t="n">
+      <c r="H61" s="11" t="n">
         <v>0.052</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="13" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="13" t="inlineStr">
         <is>
           <t>Jobs located inside the ring — LODES workplace counts</t>
         </is>
       </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    2019</t>
-        </is>
-      </c>
-      <c r="B62" s="7" t="n">
-        <v>4140</v>
-      </c>
-      <c r="C62" s="7" t="n">
-        <v>59139</v>
-      </c>
-      <c r="D62" s="7" t="n">
-        <v>150089</v>
-      </c>
-      <c r="E62" s="7" t="n">
-        <v>458614</v>
-      </c>
-      <c r="F62" s="12" t="n"/>
-      <c r="G62" s="12" t="n"/>
-      <c r="H62" s="12" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2020</t>
+          <t xml:space="preserve">    2019</t>
         </is>
       </c>
       <c r="B63" s="7" t="n">
-        <v>4549</v>
+        <v>4140</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>58261</v>
+        <v>59139</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>150082</v>
+        <v>150089</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>455835</v>
+        <v>458614</v>
       </c>
       <c r="F63" s="12" t="n"/>
       <c r="G63" s="12" t="n"/>
@@ -16106,20 +16124,20 @@
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2021</t>
+          <t xml:space="preserve">    2020</t>
         </is>
       </c>
       <c r="B64" s="7" t="n">
-        <v>4552</v>
+        <v>4549</v>
       </c>
       <c r="C64" s="7" t="n">
-        <v>59079</v>
+        <v>58261</v>
       </c>
       <c r="D64" s="7" t="n">
-        <v>152118</v>
+        <v>150082</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>466392</v>
+        <v>455835</v>
       </c>
       <c r="F64" s="12" t="n"/>
       <c r="G64" s="12" t="n"/>
@@ -16128,20 +16146,20 @@
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2022</t>
+          <t xml:space="preserve">    2021</t>
         </is>
       </c>
       <c r="B65" s="7" t="n">
-        <v>4741</v>
+        <v>4552</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>63403</v>
+        <v>59079</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>162056</v>
+        <v>152118</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>501214</v>
+        <v>466392</v>
       </c>
       <c r="F65" s="12" t="n"/>
       <c r="G65" s="12" t="n"/>
@@ -16150,20 +16168,20 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    2023  (latest)</t>
+          <t xml:space="preserve">    2022</t>
         </is>
       </c>
       <c r="B66" s="7" t="n">
-        <v>5239</v>
+        <v>4741</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>65083</v>
+        <v>63403</v>
       </c>
       <c r="D66" s="7" t="n">
-        <v>165142</v>
+        <v>162056</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>516916</v>
+        <v>501214</v>
       </c>
       <c r="F66" s="12" t="n"/>
       <c r="G66" s="12" t="n"/>
@@ -16172,947 +16190,969 @@
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Job growth 2019 to 2023</t>
-        </is>
-      </c>
-      <c r="B67" s="11" t="n">
-        <v>0.2654589371980676</v>
-      </c>
-      <c r="C67" s="11" t="n">
-        <v>0.1005089703917887</v>
-      </c>
-      <c r="D67" s="11" t="n">
-        <v>0.1002938256634396</v>
-      </c>
-      <c r="E67" s="11" t="n">
-        <v>0.1271265159807595</v>
+          <t xml:space="preserve">    2023  (latest)</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="n">
+        <v>5239</v>
+      </c>
+      <c r="C67" s="7" t="n">
+        <v>65083</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>165142</v>
+      </c>
+      <c r="E67" s="7" t="n">
+        <v>516916</v>
       </c>
       <c r="F67" s="12" t="n"/>
       <c r="G67" s="12" t="n"/>
       <c r="H67" s="12" t="n"/>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>Already a fraction in the engine's output, unlike the rates above.</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Job CAGR (4-yr)</t>
+          <t xml:space="preserve">    Job growth 2019 to 2023</t>
         </is>
       </c>
       <c r="B68" s="11" t="n">
-        <v>0.06062537773196808</v>
+        <v>0.2654589371980676</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>0.02423213297708893</v>
+        <v>0.1005089703917887</v>
       </c>
       <c r="D68" s="11" t="n">
-        <v>0.02418207107245318</v>
+        <v>0.1002938256634396</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.03036990821614882</v>
+        <v>0.1271265159807595</v>
       </c>
       <c r="F68" s="12" t="n"/>
       <c r="G68" s="12" t="n"/>
       <c r="H68" s="12" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="13" t="inlineStr">
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Already a fraction in the engine's output, unlike the rates above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Job CAGR (4-yr)</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="n">
+        <v>0.06062537773196808</v>
+      </c>
+      <c r="C69" s="11" t="n">
+        <v>0.02423213297708893</v>
+      </c>
+      <c r="D69" s="11" t="n">
+        <v>0.02418207107245318</v>
+      </c>
+      <c r="E69" s="11" t="n">
+        <v>0.03036990821614882</v>
+      </c>
+      <c r="F69" s="12" t="n"/>
+      <c r="G69" s="12" t="n"/>
+      <c r="H69" s="12" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="13" t="inlineStr">
         <is>
           <t>Metro nonfarm employment and unemployment — Maricopa County, Arizona</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="14" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="14" t="inlineStr">
         <is>
           <t>Year</t>
         </is>
       </c>
-      <c r="B71" s="14" t="inlineStr">
+      <c r="B72" s="14" t="inlineStr">
         <is>
           <t>Nonfarm jobs (000s)</t>
         </is>
       </c>
-      <c r="C71" s="14" t="inlineStr">
+      <c r="C72" s="14" t="inlineStr">
         <is>
           <t>Job growth</t>
         </is>
       </c>
-      <c r="D71" s="14" t="inlineStr">
+      <c r="D72" s="14" t="inlineStr">
         <is>
           <t>Unemployment</t>
         </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="12" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B72" s="10" t="n">
-        <v>2469.37</v>
-      </c>
-      <c r="C72" s="11" t="n">
-        <v>0.002793919975309533</v>
-      </c>
-      <c r="D72" s="11" t="n">
-        <v>0.0431</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="12" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B73" s="10" t="n">
-        <v>2462.49</v>
+        <v>2469.37</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>0.002626178726730766</v>
+        <v>0.002793919975309533</v>
       </c>
       <c r="D73" s="11" t="n">
-        <v>0.0381</v>
+        <v>0.0431</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="12" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B74" s="10" t="n">
-        <v>2456.04</v>
+        <v>2462.49</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>0.02243406947942472</v>
+        <v>0.002626178726730766</v>
       </c>
       <c r="D74" s="11" t="n">
-        <v>0.0328</v>
+        <v>0.0381</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="12" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B75" s="10" t="n">
-        <v>2402.15</v>
+        <v>2456.04</v>
       </c>
       <c r="C75" s="11" t="n">
-        <v>0.03166081866321946</v>
+        <v>0.02243406947942472</v>
       </c>
       <c r="D75" s="11" t="n">
-        <v>0.0326</v>
+        <v>0.0328</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="12" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B76" s="10" t="n">
-        <v>2328.43</v>
+        <v>2402.15</v>
       </c>
       <c r="C76" s="11" t="n">
-        <v>0.05041323059710923</v>
+        <v>0.03166081866321946</v>
       </c>
       <c r="D76" s="11" t="n">
-        <v>0.0332</v>
+        <v>0.0326</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="12" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B77" s="10" t="n">
-        <v>2216.68</v>
+        <v>2328.43</v>
       </c>
       <c r="C77" s="11" t="n">
-        <v>0.04558897751446889</v>
+        <v>0.05041323059710923</v>
       </c>
       <c r="D77" s="11" t="n">
-        <v>0.0462</v>
+        <v>0.0332</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="12" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B78" s="10" t="n">
-        <v>2120.03</v>
+        <v>2216.68</v>
       </c>
       <c r="C78" s="11" t="n">
-        <v>-0.02628980328576602</v>
+        <v>0.04558897751446889</v>
       </c>
       <c r="D78" s="11" t="n">
-        <v>0.0728</v>
+        <v>0.0462</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="12" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B79" s="10" t="n">
-        <v>2177.27</v>
+        <v>2120.03</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>0.03380213477170857</v>
+        <v>-0.02628980328576602</v>
       </c>
       <c r="D79" s="11" t="n">
-        <v>0.0413</v>
+        <v>0.0728</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="12" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B80" s="10" t="n">
-        <v>2106.08</v>
+        <v>2177.27</v>
       </c>
       <c r="C80" s="11" t="n">
-        <v>0.03344079531681654</v>
+        <v>0.03380213477170857</v>
       </c>
       <c r="D80" s="11" t="n">
-        <v>0.0415</v>
+        <v>0.0413</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="12" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B81" s="10" t="n">
-        <v>2037.93</v>
+        <v>2106.08</v>
       </c>
       <c r="C81" s="11" t="n">
-        <v>0.03009517840264042</v>
+        <v>0.03344079531681654</v>
       </c>
       <c r="D81" s="11" t="n">
-        <v>0.0428</v>
+        <v>0.0415</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="12" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B82" s="10" t="n">
+        <v>2037.93</v>
+      </c>
+      <c r="C82" s="11" t="n">
+        <v>0.03009517840264042</v>
+      </c>
+      <c r="D82" s="11" t="n">
+        <v>0.0428</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="12" t="n">
         <v>2016</v>
       </c>
-      <c r="B82" s="10" t="n">
+      <c r="B83" s="10" t="n">
         <v>1978.39</v>
       </c>
-      <c r="C82" s="12" t="n"/>
-      <c r="D82" s="11" t="n">
+      <c r="C83" s="12" t="n"/>
+      <c r="D83" s="11" t="n">
         <v>0.0471</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="4" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>Jobs by industry (2023)</t>
         </is>
       </c>
-      <c r="B84" s="4" t="n"/>
-      <c r="C84" s="4" t="n"/>
-      <c r="D84" s="4" t="n"/>
-      <c r="E84" s="4" t="n"/>
-      <c r="F84" s="4" t="n"/>
-      <c r="G84" s="4" t="n"/>
-      <c r="H84" s="4" t="n"/>
-    </row>
-    <row r="85">
-      <c r="A85" s="6" t="inlineStr">
+      <c r="B85" s="4" t="n"/>
+      <c r="C85" s="4" t="n"/>
+      <c r="D85" s="4" t="n"/>
+      <c r="E85" s="4" t="n"/>
+      <c r="F85" s="4" t="n"/>
+      <c r="G85" s="4" t="n"/>
+      <c r="H85" s="4" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
         <is>
           <t>Share of jobs by sector, sorted by the metro's own concentration. Ring, MSA and state shares come from LODES workplace counts; the U.S. column is QCEW — a different survey, so read it as a benchmark rather than the same measurement. The location quotient on each row is the metro share over the national share.</t>
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="14" t="inlineStr"/>
-      <c r="B86" s="14" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="14" t="inlineStr"/>
+      <c r="B87" s="14" t="inlineStr">
         <is>
           <t>1 mi</t>
         </is>
       </c>
-      <c r="C86" s="14" t="inlineStr">
+      <c r="C87" s="14" t="inlineStr">
         <is>
           <t>3 mi</t>
         </is>
       </c>
-      <c r="D86" s="14" t="inlineStr">
+      <c r="D87" s="14" t="inlineStr">
         <is>
           <t>5 mi</t>
         </is>
       </c>
-      <c r="E86" s="14" t="inlineStr">
+      <c r="E87" s="14" t="inlineStr">
         <is>
           <t>10 mi</t>
         </is>
       </c>
-      <c r="F86" s="14" t="inlineStr">
+      <c r="F87" s="14" t="inlineStr">
         <is>
           <t>Phoenix MSA</t>
         </is>
       </c>
-      <c r="G86" s="14" t="inlineStr">
+      <c r="G87" s="14" t="inlineStr">
         <is>
           <t>Arizona</t>
         </is>
       </c>
-      <c r="H86" s="14" t="inlineStr">
+      <c r="H87" s="14" t="inlineStr">
         <is>
           <t>U.S.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>Health Care/Social Asst</t>
-        </is>
-      </c>
-      <c r="B87" s="11" t="n">
-        <v>0.1675892345867532</v>
-      </c>
-      <c r="C87" s="11" t="n">
-        <v>0.1324022003011585</v>
-      </c>
-      <c r="D87" s="11" t="n">
-        <v>0.128294871717239</v>
-      </c>
-      <c r="E87" s="11" t="n">
-        <v>0.1575223875399726</v>
-      </c>
-      <c r="F87" s="11" t="n">
-        <v>0.1439230188830762</v>
-      </c>
-      <c r="G87" s="11" t="n">
-        <v>0.1480747084992491</v>
-      </c>
-      <c r="H87" s="11" t="n">
-        <v>0.1524112221376376</v>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>Location quotient vs U.S.: 0.94x — less concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>Retail Trade</t>
+          <t>Health Care/Social Asst</t>
         </is>
       </c>
       <c r="B88" s="11" t="n">
-        <v>0.1402939492269517</v>
+        <v>0.1675892345867532</v>
       </c>
       <c r="C88" s="11" t="n">
-        <v>0.1312959036292677</v>
+        <v>0.1324022003011585</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>0.1295604415567115</v>
+        <v>0.128294871717239</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>0.1260357078602561</v>
+        <v>0.1575223875399726</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>0.1090536545703669</v>
+        <v>0.1439230188830762</v>
       </c>
       <c r="G88" s="11" t="n">
-        <v>0.1100206596769526</v>
+        <v>0.1480747084992491</v>
       </c>
       <c r="H88" s="11" t="n">
-        <v>0.1019921721752688</v>
+        <v>0.1524112221376376</v>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 1.07x — more concentrated here.</t>
+          <t>Location quotient vs U.S.: 0.94x — less concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>Accommodation/Food Svcs</t>
+          <t>Retail Trade</t>
         </is>
       </c>
       <c r="B89" s="11" t="n">
-        <v>0.1093720175606032</v>
+        <v>0.1402939492269517</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>0.09160751052518361</v>
+        <v>0.1312959036292677</v>
       </c>
       <c r="D89" s="11" t="n">
-        <v>0.09612275421907074</v>
+        <v>0.1295604415567115</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>0.0974934080326242</v>
+        <v>0.1260357078602561</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>0.09153364975214603</v>
+        <v>0.1090536545703669</v>
       </c>
       <c r="G89" s="11" t="n">
-        <v>0.09799831322286184</v>
+        <v>0.1100206596769526</v>
       </c>
       <c r="H89" s="11" t="n">
-        <v>0.09210003364899073</v>
+        <v>0.1019921721752688</v>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 0.99x — less concentrated here.</t>
+          <t>Location quotient vs U.S.: 1.07x — more concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>Admin/Support/Waste</t>
+          <t>Accommodation/Food Svcs</t>
         </is>
       </c>
       <c r="B90" s="11" t="n">
-        <v>0.09200229051345676</v>
+        <v>0.1093720175606032</v>
       </c>
       <c r="C90" s="11" t="n">
-        <v>0.1102148059371255</v>
+        <v>0.09160751052518361</v>
       </c>
       <c r="D90" s="11" t="n">
-        <v>0.09007950685163767</v>
+        <v>0.09612275421907074</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>0.07061675278623067</v>
+        <v>0.0974934080326242</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>0.08654896600644772</v>
+        <v>0.09153364975214603</v>
       </c>
       <c r="G90" s="11" t="n">
-        <v>0.08053357937738248</v>
+        <v>0.09799831322286184</v>
       </c>
       <c r="H90" s="11" t="n">
-        <v>0.06170694540515537</v>
+        <v>0.09210003364899073</v>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 1.40x — more concentrated here.</t>
+          <t>Location quotient vs U.S.: 0.99x — less concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>Construction</t>
+          <t>Admin/Support/Waste</t>
         </is>
       </c>
       <c r="B91" s="11" t="n">
-        <v>0.03397594960870395</v>
+        <v>0.09200229051345676</v>
       </c>
       <c r="C91" s="11" t="n">
-        <v>0.1437571064195937</v>
+        <v>0.1102148059371255</v>
       </c>
       <c r="D91" s="11" t="n">
-        <v>0.1065198040486124</v>
+        <v>0.09007950685163767</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>0.07423822393150158</v>
+        <v>0.07061675278623067</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>0.07168567465967132</v>
+        <v>0.08654896600644772</v>
       </c>
       <c r="G91" s="11" t="n">
-        <v>0.0692629280579044</v>
+        <v>0.08053357937738248</v>
       </c>
       <c r="H91" s="11" t="n">
-        <v>0.0531750429082045</v>
+        <v>0.06170694540515537</v>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 1.35x — more concentrated here.</t>
+          <t>Location quotient vs U.S.: 1.40x — more concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>Educational Services</t>
+          <t>Construction</t>
         </is>
       </c>
       <c r="B92" s="11" t="n">
-        <v>0.05630845581217789</v>
+        <v>0.03397594960870395</v>
       </c>
       <c r="C92" s="11" t="n">
-        <v>0.09185335423004824</v>
+        <v>0.1437571064195937</v>
       </c>
       <c r="D92" s="11" t="n">
-        <v>0.1103528457155314</v>
+        <v>0.1065198040486124</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>0.09778359001541834</v>
+        <v>0.07423822393150158</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>0.0692937123890178</v>
+        <v>0.07168567465967132</v>
       </c>
       <c r="G92" s="11" t="n">
-        <v>0.07805244418719343</v>
+        <v>0.0692629280579044</v>
       </c>
       <c r="H92" s="11" t="n">
-        <v>0.08463384936674581</v>
+        <v>0.0531750429082045</v>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 0.82x — less concentrated here.</t>
+          <t>Location quotient vs U.S.: 1.35x — more concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>Finance/Insurance</t>
+          <t>Educational Services</t>
         </is>
       </c>
       <c r="B93" s="11" t="n">
-        <v>0.01355220461920214</v>
+        <v>0.05630845581217789</v>
       </c>
       <c r="C93" s="11" t="n">
-        <v>0.02564457146369196</v>
+        <v>0.09185335423004824</v>
       </c>
       <c r="D93" s="11" t="n">
-        <v>0.02846623835100489</v>
+        <v>0.1103528457155314</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>0.06430626193373404</v>
+        <v>0.09778359001541834</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>0.06699836548547758</v>
+        <v>0.0692937123890178</v>
       </c>
       <c r="G93" s="11" t="n">
-        <v>0.05584002806837911</v>
+        <v>0.07805244418719343</v>
       </c>
       <c r="H93" s="11" t="n">
-        <v>0.04139724841428747</v>
+        <v>0.08463384936674581</v>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 1.62x — more concentrated here.</t>
+          <t>Location quotient vs U.S.: 0.82x — less concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>Manufacturing</t>
+          <t>Finance/Insurance</t>
         </is>
       </c>
       <c r="B94" s="11" t="n">
-        <v>0.005344531399121969</v>
+        <v>0.01355220461920214</v>
       </c>
       <c r="C94" s="11" t="n">
-        <v>0.03838234842199072</v>
+        <v>0.02564457146369196</v>
       </c>
       <c r="D94" s="11" t="n">
-        <v>0.04546362849167086</v>
+        <v>0.02846623835100489</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>0.06499302595968018</v>
+        <v>0.06430626193373404</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>0.06180957654864814</v>
+        <v>0.06699836548547758</v>
       </c>
       <c r="G94" s="11" t="n">
-        <v>0.06178450068945185</v>
+        <v>0.05584002806837911</v>
       </c>
       <c r="H94" s="11" t="n">
-        <v>0.08451882031580928</v>
+        <v>0.04139724841428747</v>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 0.73x — less concentrated here.</t>
+          <t>Location quotient vs U.S.: 1.62x — more concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>Professional/Scientific/Tech</t>
+          <t>Manufacturing</t>
         </is>
       </c>
       <c r="B95" s="11" t="n">
-        <v>0.03531208245848445</v>
+        <v>0.005344531399121969</v>
       </c>
       <c r="C95" s="11" t="n">
-        <v>0.06550198211487047</v>
+        <v>0.03838234842199072</v>
       </c>
       <c r="D95" s="11" t="n">
-        <v>0.05942728423245309</v>
+        <v>0.04546362849167086</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>0.06130384568509065</v>
+        <v>0.06499302595968018</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>0.06005544300027939</v>
+        <v>0.06180957654864814</v>
       </c>
       <c r="G95" s="11" t="n">
-        <v>0.05671111569578283</v>
+        <v>0.06178450068945185</v>
       </c>
       <c r="H95" s="11" t="n">
-        <v>0.07101058481218332</v>
+        <v>0.08451882031580928</v>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 0.85x — less concentrated here.</t>
+          <t>Location quotient vs U.S.: 0.73x — less concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>Transportation/Warehousing</t>
+          <t>Professional/Scientific/Tech</t>
         </is>
       </c>
       <c r="B96" s="11" t="n">
-        <v>0.01068906279824394</v>
+        <v>0.03531208245848445</v>
       </c>
       <c r="C96" s="11" t="n">
-        <v>0.006038536000737531</v>
+        <v>0.06550198211487047</v>
       </c>
       <c r="D96" s="11" t="n">
-        <v>0.01906832260525726</v>
+        <v>0.05942728423245309</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>0.02301916942178338</v>
+        <v>0.06130384568509065</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>0.0473268911935302</v>
+        <v>0.06005544300027939</v>
       </c>
       <c r="G96" s="11" t="n">
-        <v>0.04326179016785311</v>
+        <v>0.05671111569578283</v>
       </c>
       <c r="H96" s="11" t="n">
-        <v>0.04840196213219566</v>
+        <v>0.07101058481218332</v>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 0.98x — less concentrated here.</t>
+          <t>Location quotient vs U.S.: 0.85x — less concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>Wholesale Trade</t>
+          <t>Transportation/Warehousing</t>
         </is>
       </c>
       <c r="B97" s="11" t="n">
-        <v>0.007825920977285742</v>
+        <v>0.01068906279824394</v>
       </c>
       <c r="C97" s="11" t="n">
-        <v>0.03606219845733075</v>
+        <v>0.006038536000737531</v>
       </c>
       <c r="D97" s="11" t="n">
-        <v>0.03811847913626373</v>
+        <v>0.01906832260525726</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>0.03247329842121656</v>
+        <v>0.02301916942178338</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>0.04109248140049621</v>
+        <v>0.0473268911935302</v>
       </c>
       <c r="G97" s="11" t="n">
-        <v>0.03708044284108286</v>
+        <v>0.04326179016785311</v>
       </c>
       <c r="H97" s="11" t="n">
-        <v>0.03992451539947575</v>
+        <v>0.04840196213219566</v>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 1.03x — more concentrated here.</t>
+          <t>Location quotient vs U.S.: 0.98x — less concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>Public Administration</t>
+          <t>Wholesale Trade</t>
         </is>
       </c>
       <c r="B98" s="11" t="n">
-        <v>0</v>
+        <v>0.007825920977285742</v>
       </c>
       <c r="C98" s="11" t="n">
-        <v>0.001859193018038782</v>
+        <v>0.03606219845733075</v>
       </c>
       <c r="D98" s="11" t="n">
-        <v>0.02761848821930085</v>
+        <v>0.03811847913626373</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>0.02183329238543132</v>
+        <v>0.03247329842121656</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>0.03285591679200175</v>
+        <v>0.04109248140049621</v>
       </c>
       <c r="G98" s="11" t="n">
-        <v>0.04120792091186574</v>
+        <v>0.03708044284108286</v>
       </c>
       <c r="H98" s="11" t="n">
-        <v>0.04966983338636385</v>
+        <v>0.03992451539947575</v>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 0.66x — less concentrated here.</t>
+          <t>Location quotient vs U.S.: 1.03x — more concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>Other Services</t>
+          <t>Public Administration</t>
         </is>
       </c>
       <c r="B99" s="11" t="n">
-        <v>0.01546096583317427</v>
+        <v>0</v>
       </c>
       <c r="C99" s="11" t="n">
-        <v>0.02945514888909376</v>
+        <v>0.001859193018038782</v>
       </c>
       <c r="D99" s="11" t="n">
-        <v>0.03031917792458657</v>
+        <v>0.02761848821930085</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>0.02663677147395037</v>
+        <v>0.02183329238543132</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>0.02745633069056147</v>
+        <v>0.03285591679200175</v>
       </c>
       <c r="G99" s="11" t="n">
-        <v>0.02813810432102126</v>
+        <v>0.04120792091186574</v>
       </c>
       <c r="H99" s="11" t="n">
-        <v>0.03015265325357227</v>
+        <v>0.04966983338636385</v>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 0.91x — less concentrated here.</t>
+          <t>Location quotient vs U.S.: 0.66x — less concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>Arts/Entertainment/Rec</t>
+          <t>Other Services</t>
         </is>
       </c>
       <c r="B100" s="11" t="n">
-        <v>0.2744798625691926</v>
+        <v>0.01546096583317427</v>
       </c>
       <c r="C100" s="11" t="n">
-        <v>0.03211333394794259</v>
+        <v>0.02945514888909376</v>
       </c>
       <c r="D100" s="11" t="n">
-        <v>0.0287326741066833</v>
+        <v>0.03031917792458657</v>
       </c>
       <c r="E100" s="11" t="n">
-        <v>0.02107301559051066</v>
+        <v>0.02663677147395037</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>0.02090656164729619</v>
+        <v>0.02745633069056147</v>
       </c>
       <c r="G100" s="11" t="n">
-        <v>0.02117990984115704</v>
+        <v>0.02813810432102126</v>
       </c>
       <c r="H100" s="11" t="n">
-        <v>0.01844252444674844</v>
+        <v>0.03015265325357227</v>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 1.13x — more concentrated here.</t>
+          <t>Location quotient vs U.S.: 0.91x — less concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>Real Estate/Rental</t>
+          <t>Arts/Entertainment/Rec</t>
         </is>
       </c>
       <c r="B101" s="11" t="n">
-        <v>0.03340332124451231</v>
+        <v>0.2744798625691926</v>
       </c>
       <c r="C101" s="11" t="n">
-        <v>0.03411081404996773</v>
+        <v>0.03211333394794259</v>
       </c>
       <c r="D101" s="11" t="n">
-        <v>0.02407610374039469</v>
+        <v>0.0287326741066833</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>0.02037464428525276</v>
+        <v>0.02107301559051066</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>0.02084382439592392</v>
+        <v>0.02090656164729619</v>
       </c>
       <c r="G101" s="11" t="n">
-        <v>0.01961125167587262</v>
+        <v>0.02117990984115704</v>
       </c>
       <c r="H101" s="11" t="n">
-        <v>0.01586685774361</v>
+        <v>0.01844252444674844</v>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 1.31x — more concentrated here.</t>
+          <t>Location quotient vs U.S.: 1.13x — more concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>Information</t>
+          <t>Real Estate/Rental</t>
         </is>
       </c>
       <c r="B102" s="11" t="n">
-        <v>0.002672265699560985</v>
+        <v>0.03340332124451231</v>
       </c>
       <c r="C102" s="11" t="n">
-        <v>0.01090931440336806</v>
+        <v>0.03411081404996773</v>
       </c>
       <c r="D102" s="11" t="n">
-        <v>0.01293424486657018</v>
+        <v>0.02407610374039469</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>0.01705883149519169</v>
+        <v>0.02037464428525276</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>0.01906250470529385</v>
+        <v>0.02084382439592392</v>
       </c>
       <c r="G102" s="11" t="n">
-        <v>0.01736157873170788</v>
+        <v>0.01961125167587262</v>
       </c>
       <c r="H102" s="11" t="n">
-        <v>0.02037764401856688</v>
+        <v>0.01586685774361</v>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 0.94x — less concentrated here.</t>
+          <t>Location quotient vs U.S.: 1.31x — more concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>Mgmt of Companies</t>
+          <t>Information</t>
         </is>
       </c>
       <c r="B103" s="11" t="n">
-        <v>0.0005726283641916397</v>
+        <v>0.002672265699560985</v>
       </c>
       <c r="C103" s="11" t="n">
-        <v>0.01676346762545712</v>
+        <v>0.01090931440336806</v>
       </c>
       <c r="D103" s="11" t="n">
-        <v>0.01896538151783606</v>
+        <v>0.01293424486657018</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>0.01917522542303697</v>
+        <v>0.01705883149519169</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>0.01809509628913341</v>
+        <v>0.01906250470529385</v>
       </c>
       <c r="G103" s="11" t="n">
-        <v>0.01520137056214125</v>
+        <v>0.01736157873170788</v>
       </c>
       <c r="H103" s="11" t="n">
-        <v>0.0166872404072684</v>
+        <v>0.02037764401856688</v>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 1.08x — more concentrated here.</t>
+          <t>Location quotient vs U.S.: 0.94x — less concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Mgmt of Companies</t>
         </is>
       </c>
       <c r="B104" s="11" t="n">
-        <v>0.001145256728383279</v>
+        <v>0.0005726283641916397</v>
       </c>
       <c r="C104" s="11" t="n">
-        <v>0.0007221658830398574</v>
+        <v>0.01676346762545712</v>
       </c>
       <c r="D104" s="11" t="n">
-        <v>0.003772488086082971</v>
+        <v>0.01896538151783606</v>
       </c>
       <c r="E104" s="11" t="n">
-        <v>0.002512975970997278</v>
+        <v>0.01917522542303697</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>0.006769767671410718</v>
+        <v>0.01809509628913341</v>
       </c>
       <c r="G104" s="11" t="n">
-        <v>0.006825111647899759</v>
+        <v>0.01520137056214125</v>
       </c>
       <c r="H104" s="11" t="n">
-        <v>0.0054838649167028</v>
+        <v>0.0166872404072684</v>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 1.23x — more concentrated here.</t>
+          <t>Location quotient vs U.S.: 1.08x — more concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>Agriculture/Forestry/Fishing</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="B105" s="11" t="n">
-        <v>0</v>
+        <v>0.001145256728383279</v>
       </c>
       <c r="C105" s="11" t="n">
-        <v>0.0006299744937156203</v>
+        <v>0.0007221658830398574</v>
       </c>
       <c r="D105" s="11" t="n">
-        <v>0.001725777053826078</v>
+        <v>0.003772488086082971</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>0.001151055198416767</v>
+        <v>0.002512975970997278</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>0.003239751660864168</v>
+        <v>0.006769767671410718</v>
       </c>
       <c r="G105" s="11" t="n">
-        <v>0.007704795534784445</v>
+        <v>0.006825111647899759</v>
       </c>
       <c r="H105" s="11" t="n">
-        <v>0.008224135502638645</v>
+        <v>0.0054838649167028</v>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>Location quotient vs U.S.: 0.39x — less concentrated here.</t>
+          <t>Location quotient vs U.S.: 1.23x — more concentrated here.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>Mining/Oil &amp; Gas</t>
+          <t>Agriculture/Forestry/Fishing</t>
         </is>
       </c>
       <c r="B106" s="11" t="n">
         <v>0</v>
       </c>
       <c r="C106" s="11" t="n">
+        <v>0.0006299744937156203</v>
+      </c>
+      <c r="D106" s="11" t="n">
+        <v>0.001725777053826078</v>
+      </c>
+      <c r="E106" s="11" t="n">
+        <v>0.001151055198416767</v>
+      </c>
+      <c r="F106" s="11" t="n">
+        <v>0.003239751660864168</v>
+      </c>
+      <c r="G106" s="11" t="n">
+        <v>0.007704795534784445</v>
+      </c>
+      <c r="H106" s="11" t="n">
+        <v>0.008224135502638645</v>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>Location quotient vs U.S.: 0.39x — less concentrated here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="5" t="inlineStr">
+        <is>
+          <t>Mining/Oil &amp; Gas</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="11" t="n">
         <v>0.0006760701883777388</v>
       </c>
-      <c r="D106" s="11" t="n">
+      <c r="D107" s="11" t="n">
         <v>0.0003814875592668172</v>
       </c>
-      <c r="E106" s="11" t="n">
+      <c r="E107" s="11" t="n">
         <v>0.0003985165897039564</v>
       </c>
-      <c r="F106" s="11" t="n">
+      <c r="F107" s="11" t="n">
         <v>0.00144881225835702</v>
       </c>
-      <c r="G106" s="11" t="n">
+      <c r="G107" s="11" t="n">
         <v>0.004149446289456433</v>
       </c>
-      <c r="H106" s="11" t="n">
+      <c r="H107" s="11" t="n">
         <v>0.003822849608574414</v>
       </c>
-      <c r="I106" s="2" t="inlineStr">
+      <c r="I107" s="2" t="inlineStr">
         <is>
           <t>Location quotient vs U.S.: 0.38x — less concentrated here.</t>
         </is>

--- a/public/downloads/underwriting-demo/sample-underwriting-pack.xlsx
+++ b/public/downloads/underwriting-demo/sample-underwriting-pack.xlsx
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-10-06.</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="H28" s="26" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-10-06.</t>
         </is>
       </c>
     </row>
@@ -10359,7 +10359,7 @@
       </c>
       <c r="H181" s="26" t="inlineStr">
         <is>
-          <t>1BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>1BR — lowest five of 5 available</t>
         </is>
       </c>
     </row>
@@ -10423,7 +10423,7 @@
       </c>
       <c r="D183" s="26" t="inlineStr">
         <is>
-          <t>Comp vintage where one is published. Blank means nobody published one — the tracker has no year-built column — never that the community is new.</t>
+          <t>Comp vintage where one is published: the public property record's year where it has one, else the community registry's. Blank means nobody published one, never that the community is new.</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
@@ -10465,7 +10465,7 @@
       </c>
       <c r="D184" s="26" t="inlineStr">
         <is>
-          <t>Where that year came from. Blank alongside a blank year; a year with no source is rejected at validation.</t>
+          <t>Where that year came from: the public record with its as-of, or the community registry (third-party market data). Blank alongside a blank year; a year with no source is rejected at validation.</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
@@ -10485,7 +10485,7 @@
       </c>
       <c r="H184" s="26" t="inlineStr">
         <is>
-          <t>vendor note on the tracked community record, via the market-report service</t>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
         </is>
       </c>
     </row>
@@ -10527,7 +10527,7 @@
       </c>
       <c r="H185" s="26" t="inlineStr">
         <is>
-          <t>Trails at Harris</t>
+          <t>The Village at Lindsay Park Apartments</t>
         </is>
       </c>
     </row>
@@ -10569,7 +10569,7 @@
       </c>
       <c r="H186" s="26" t="inlineStr">
         <is>
-          <t>1653 S Harris Dr, Mesa, AZ 85204</t>
+          <t>1441 S Lindsay Rd, Mesa, AZ 85204-6285</t>
         </is>
       </c>
     </row>
@@ -10633,7 +10633,7 @@
       </c>
       <c r="D188" s="26" t="inlineStr">
         <is>
-          <t>Unit count where the registry has one. The registry was seeded from licensed data exports, so the public demo withholds it.</t>
+          <t>Unit count. The registry's own count was seeded from licensed data exports, so the public demo withholds it and shows the public-record count instead where one exists (county property record, Florida DBPR apartment licence, City of Austin permit), with its source and as-of.</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
@@ -10648,12 +10648,12 @@
       </c>
       <c r="G188" s="26" t="inlineStr">
         <is>
-          <t>Internal pipeline only — Unit counts come from a licensed data export; the internal pipeline carries them.</t>
+          <t>Public record where one exists — A community's own unit count comes from a licensed data export, so the public demo holds it back; where a public record states a count (a county property record, a Florida DBPR apartment licence, a City of Austin permit), that count is shown with its source and as-of.</t>
         </is>
       </c>
       <c r="H188" s="26" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>256 — Maricopa County, AZ property record, as of 2026-10-05</t>
         </is>
       </c>
     </row>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="H189" s="26" t="inlineStr">
         <is>
-          <t>its 2 unit group(s) were withheld (flagged for review, no bedroom count or no rent), so nothing could be quoted</t>
+          <t>vintage 1997 is 16 years from the subject's 1981, outside the +/-10-year band</t>
         </is>
       </c>
     </row>
@@ -10905,7 +10905,7 @@
       </c>
       <c r="H194" s="26" t="inlineStr">
         <is>
-          <t>$1,047</t>
+          <t>$1,200</t>
         </is>
       </c>
     </row>
@@ -10989,7 +10989,7 @@
       </c>
       <c r="H196" s="26" t="inlineStr">
         <is>
-          <t>$1,047</t>
+          <t>$1,200</t>
         </is>
       </c>
     </row>
@@ -11115,7 +11115,7 @@
       </c>
       <c r="H199" s="26" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11381,7 @@
       </c>
       <c r="H206" s="26" t="inlineStr">
         <is>
-          <t>20,297</t>
+          <t>20,298</t>
         </is>
       </c>
     </row>
@@ -11465,7 +11465,7 @@
       </c>
       <c r="H208" s="26" t="inlineStr">
         <is>
-          <t>$79,735</t>
+          <t>$79,731</t>
         </is>
       </c>
     </row>
@@ -11507,7 +11507,7 @@
       </c>
       <c r="H209" s="26" t="inlineStr">
         <is>
-          <t>5,239</t>
+          <t>5,237</t>
         </is>
       </c>
     </row>
@@ -12726,7 +12726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -12776,7 +12776,7 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6">
@@ -12902,7 +12902,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>340 entries</t>
+          <t>343 entries</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -12960,7 +12960,7 @@
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="26" t="inlineStr">
         <is>
-          <t>Unit counts come from a licensed data export; the internal pipeline carries them.</t>
+          <t>A community's own unit count comes from a licensed data export, so the public demo holds it back; where a public record states a count (a county property record, a Florida DBPR apartment licence, a City of Austin permit), that count is shown with its source and as-of.</t>
         </is>
       </c>
     </row>
@@ -12972,7 +12972,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>19 entries</t>
+          <t>26 entries</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -13037,22 +13037,22 @@
     <row r="15">
       <c r="A15" s="30" t="inlineStr">
         <is>
-          <t>demand.rings</t>
+          <t>comps.rows[].units</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>5 entries</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Public demographic data (the operator's ring engine), via the market-report service</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>POST /report (format json)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -13063,24 +13063,24 @@
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="26" t="inlineStr">
         <is>
-          <t>Ring demographics.</t>
+          <t>A community's own unit count comes from a licensed data export, so the public demo holds it back; where a public record states a count (a county property record, a Florida DBPR apartment licence, a City of Austin permit), that count is shown with its source and as-of.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="30" t="inlineStr">
         <is>
-          <t>demand.zip_home</t>
+          <t>demand.rings</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5 entries</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Zillow ZHVI home values (vendored static table, undated), via the market-report service</t>
+          <t>Public demographic data (the operator's ring engine), via the market-report service</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -13096,29 +13096,29 @@
       <c r="F16" s="12" t="n"/>
       <c r="G16" s="26" t="inlineStr">
         <is>
-          <t>ZIP and metro home values from the vendored Zillow ZHVI table; static, undated.</t>
+          <t>Ring demographics.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="30" t="inlineStr">
         <is>
-          <t>om_comps.rent</t>
+          <t>demand.zip_home</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>0 entries</t>
+          <t>—</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Zillow ZHVI home values (vendored static table, undated), via the market-report service</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>p.20</t>
+          <t>POST /report (format json)</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -13129,29 +13129,29 @@
       <c r="F17" s="12" t="n"/>
       <c r="G17" s="26" t="inlineStr">
         <is>
-          <t>4 rent comparable(s) the memorandum states; every figure verified inside its own quote.</t>
+          <t>ZIP and metro home values from the vendored Zillow ZHVI table; static, undated.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="30" t="inlineStr">
         <is>
-          <t>pricing.price_per_unit</t>
+          <t>om_comps.rent</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>215,000</t>
+          <t>0 entries</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Illustrative price</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.20</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -13162,24 +13162,24 @@
       <c r="F18" s="12" t="n"/>
       <c r="G18" s="26" t="inlineStr">
         <is>
-          <t>Per-unit price chosen for the sample, inside the sale-price band; every cap rate and pricing ladder is computed from it.</t>
+          <t>4 rent comparable(s) the memorandum states; every figure verified inside its own quote.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="30" t="inlineStr">
         <is>
-          <t>pricing.unit_count</t>
+          <t>pricing.price_per_unit</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>215,000</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Sample Property RR 8.4.26.xlsx</t>
+          <t>Illustrative price</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -13189,29 +13189,25 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>summary.unit_count</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="n"/>
       <c r="G19" s="26" t="inlineStr">
         <is>
-          <t>The same count the summary carries, counted from the rows of the uploaded rent roll.</t>
+          <t>Per-unit price chosen for the sample, inside the sale-price band; every cap rate and pricing ladder is computed from it.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="30" t="inlineStr">
         <is>
-          <t>rent_roll.as_of</t>
+          <t>pricing.unit_count</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>334</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -13221,40 +13217,44 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>as-of line</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F20" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>summary.unit_count</t>
+        </is>
+      </c>
       <c r="G20" s="26" t="inlineStr">
         <is>
-          <t>Read as the end of the period the roll's own header states.</t>
+          <t>The same count the summary carries, counted from the rows of the uploaded rent roll.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="30" t="inlineStr">
         <is>
-          <t>rent_roll.lookback_months</t>
+          <t>rent_roll.as_of</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Not stated in the uploaded documents</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>as-of line</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -13265,19 +13265,19 @@
       <c r="F21" s="12" t="n"/>
       <c r="G21" s="26" t="inlineStr">
         <is>
-          <t>This demo's default of 12 — the months of lease history the turnover figures look back over. No uploaded document or note set it.</t>
+          <t>Read as the end of the period the roll's own header states.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="30" t="inlineStr">
         <is>
-          <t>rent_roll.new_tenant_tolerance_days</t>
+          <t>rent_roll.lookback_months</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -13298,29 +13298,29 @@
       <c r="F22" s="12" t="n"/>
       <c r="G22" s="26" t="inlineStr">
         <is>
-          <t>This demo's default of 31 — the days a lease start may sit from a move-in and still count as the same event. No uploaded document or note set it.</t>
+          <t>This demo's default of 12 — the months of lease history the turnover figures look back over. No uploaded document or note set it.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="30" t="inlineStr">
         <is>
-          <t>rent_roll.units</t>
+          <t>rent_roll.new_tenant_tolerance_days</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>334 entries</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Sample Property RR 8.4.26.xlsx</t>
+          <t>Not stated in the uploaded documents</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>roll</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -13331,29 +13331,29 @@
       <c r="F23" s="12" t="n"/>
       <c r="G23" s="26" t="inlineStr">
         <is>
-          <t>Read from the uploaded rent roll.</t>
+          <t>This demo's default of 31 — the days a lease start may sit from a move-in and still count as the same event. No uploaded document or note set it.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="30" t="inlineStr">
         <is>
-          <t>summary.address_provenance</t>
+          <t>rent_roll.units</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for t…</t>
+          <t>334 entries</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>roll</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -13364,24 +13364,24 @@
       <c r="F24" s="12" t="n"/>
       <c r="G24" s="26" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>Read from the uploaded rent roll.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="30" t="inlineStr">
         <is>
-          <t>summary.assessed_value_basis</t>
+          <t>summary.address_provenance</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for t…</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
@@ -13397,29 +13397,29 @@
       <c r="F25" s="12" t="n"/>
       <c r="G25" s="26" t="inlineStr">
         <is>
-          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-10-06.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="30" t="inlineStr">
         <is>
-          <t>summary.assessment_ratio</t>
+          <t>summary.assessed_value_basis</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Vendored county rate table</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>property_tax_table.STATE_RULES['AZ']</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -13430,29 +13430,29 @@
       <c r="F26" s="12" t="n"/>
       <c r="G26" s="26" t="inlineStr">
         <is>
-          <t>10% — legal class 4.2, residential rental. A.R.S. sec. 42-15003 (class four assessed at 10%); A.R.S. sec. 42-12004 (class four includes residential rental property).</t>
+          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="30" t="inlineStr">
         <is>
-          <t>summary.city</t>
+          <t>summary.assessment_ratio</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>property_tax_table.STATE_RULES['AZ']</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -13463,24 +13463,24 @@
       <c r="F27" s="12" t="n"/>
       <c r="G27" s="26" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>10% — legal class 4.2, residential rental. A.R.S. sec. 42-15003 (class four assessed at 10%); A.R.S. sec. 42-12004 (class four includes residential rental property).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="30" t="inlineStr">
         <is>
-          <t>summary.construction_status</t>
+          <t>summary.city</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Mesa</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Not stated in the uploaded documents</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
@@ -13496,24 +13496,24 @@
       <c r="F28" s="12" t="n"/>
       <c r="G28" s="26" t="inlineStr">
         <is>
-          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-10-06.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="30" t="inlineStr">
         <is>
-          <t>summary.county</t>
+          <t>summary.construction_status</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>Maricopa</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Not stated in the uploaded documents</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -13529,24 +13529,24 @@
       <c r="F29" s="12" t="n"/>
       <c r="G29" s="26" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="30" t="inlineStr">
         <is>
-          <t>summary.deal_name</t>
+          <t>summary.county</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>Sample Mesa Apt</t>
+          <t>Maricopa</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>Illustrative name</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
@@ -13562,24 +13562,24 @@
       <c r="F30" s="12" t="n"/>
       <c r="G30" s="26" t="inlineStr">
         <is>
-          <t>An illustrative name for the public sample. The real asset's name is withheld; the memorandum's own name for it does not appear anywhere in this set.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-10-06.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="30" t="inlineStr">
         <is>
-          <t>summary.deal_status</t>
+          <t>summary.deal_name</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>Sample Mesa Apt</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>Not stated in the uploaded documents</t>
+          <t>Illustrative name</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -13595,14 +13595,14 @@
       <c r="F31" s="12" t="n"/>
       <c r="G31" s="26" t="inlineStr">
         <is>
-          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
+          <t>An illustrative name for the public sample. The real asset's name is withheld; the memorandum's own name for it does not appear anywhere in this set.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="30" t="inlineStr">
         <is>
-          <t>summary.delivery_date</t>
+          <t>summary.deal_status</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
@@ -13635,7 +13635,7 @@
     <row r="33">
       <c r="A33" s="30" t="inlineStr">
         <is>
-          <t>summary.fair_market_value</t>
+          <t>summary.delivery_date</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
@@ -13645,7 +13645,7 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Not stated in the uploaded documents</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
@@ -13661,24 +13661,24 @@
       <c r="F33" s="12" t="n"/>
       <c r="G33" s="26" t="inlineStr">
         <is>
-          <t>The internal pipeline pulls a market value by web lookup; the demo does not reach the web.</t>
+          <t>No uploaded document stated this, so the value reads MISSING. Nothing was assumed to fill it.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="30" t="inlineStr">
         <is>
-          <t>summary.in_place_rent_avg</t>
+          <t>summary.fair_market_value</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>1,456.99</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Sample Property RR 8.4.26.xlsx</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
@@ -13688,34 +13688,30 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>rent_roll.units</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="n"/>
       <c r="G34" s="26" t="inlineStr">
         <is>
-          <t>Unit-weighted across the uploaded roll.</t>
+          <t>The internal pipeline pulls a market value by web lookup; the demo does not reach the web.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="30" t="inlineStr">
         <is>
-          <t>summary.listing_brokerage</t>
+          <t>summary.in_place_rent_avg</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Desert Ridge Capital Advisors</t>
+          <t>1,456.99</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Illustrative name</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -13725,30 +13721,34 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F35" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>rent_roll.units</t>
+        </is>
+      </c>
       <c r="G35" s="26" t="inlineStr">
         <is>
-          <t>An illustrative name. The real party is withheld from the public sample.</t>
+          <t>Unit-weighted across the uploaded roll.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="30" t="inlineStr">
         <is>
-          <t>summary.market_rent_for_model</t>
+          <t>summary.listing_brokerage</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>1,344.6</t>
+          <t>Desert Ridge Capital Advisors</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Sample Property RR 8.4.26.xlsx</t>
+          <t>Illustrative name</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -13758,34 +13758,30 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>rent_roll.units</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="n"/>
       <c r="G36" s="26" t="inlineStr">
         <is>
-          <t>Unit-weighted across the uploaded roll.</t>
+          <t>An illustrative name. The real party is withheld from the public sample.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="30" t="inlineStr">
         <is>
-          <t>summary.msa</t>
+          <t>summary.market_rent_for_model</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Phoenix MSA</t>
+          <t>1,344.6</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
@@ -13795,30 +13791,34 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F37" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>rent_roll.units</t>
+        </is>
+      </c>
       <c r="G37" s="26" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>Unit-weighted across the uploaded roll.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="30" t="inlineStr">
         <is>
-          <t>summary.pricing_guidance</t>
+          <t>summary.msa</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>$215,000 per unit (illustrative)</t>
+          <t>Phoenix MSA</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Illustrative price</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -13834,29 +13834,29 @@
       <c r="F38" s="12" t="n"/>
       <c r="G38" s="26" t="inlineStr">
         <is>
-          <t>Every price and cap rate below is illustrative. The per-unit price is a round number chosen for the sample inside the band a real per-unit sale price occupies; it is not a quote, an offer, or a broker's guidance.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-10-06.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="30" t="inlineStr">
         <is>
-          <t>summary.product_detail</t>
+          <t>summary.pricing_guidance</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Diversified mix of one-, two-, and three-bedroom residences averaging 856 square feet o…</t>
+          <t>$215,000 per unit (illustrative)</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Illustrative price</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>p.3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13866,6 +13866,39 @@
       </c>
       <c r="F39" s="12" t="n"/>
       <c r="G39" s="26" t="inlineStr">
+        <is>
+          <t>Every price and cap rate below is illustrative. The per-unit price is a round number chosen for the sample inside the band a real per-unit sale price occupies; it is not a quote, an offer, or a broker's guidance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="30" t="inlineStr">
+        <is>
+          <t>summary.product_detail</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Diversified mix of one-, two-, and three-bedroom residences averaging 856 square feet o…</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Sample Property Offering Memorandum.pdf</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>p.3</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F40" s="12" t="n"/>
+      <c r="G40" s="26" t="inlineStr">
         <is>
           <t>the property offers a diversified mix of 
 one-, two-, and three-bedroom residences averaging 856 square 
@@ -13873,58 +13906,25 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="30" t="inlineStr">
-        <is>
-          <t>summary.product_type</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>Garden-style multifamily</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>p.3</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F40" s="12" t="n"/>
-      <c r="G40" s="26" t="inlineStr">
-        <is>
-          <t>Stated in the memorandum; withheld from the public sample because it identifies the real asset.</t>
-        </is>
-      </c>
-    </row>
     <row r="41">
       <c r="A41" s="30" t="inlineStr">
         <is>
-          <t>summary.school_elementary_name</t>
+          <t>summary.product_type</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Porter Elementary School</t>
+          <t>Garden-style multifamily</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Internal underwriting agent — attendance-zone school lookup</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>2151 E Southern Ave, Mesa, AZ 85204 on 2026-09-14</t>
+          <t>p.3</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -13935,19 +13935,19 @@
       <c r="F41" s="12" t="n"/>
       <c r="G41" s="26" t="inlineStr">
         <is>
-          <t>Looked up for the illustrative address by the internal underwriting agent; the public demo does not run this on an uploaded deal.</t>
+          <t>Stated in the memorandum; withheld from the public sample because it identifies the real asset.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="30" t="inlineStr">
         <is>
-          <t>summary.school_high_name</t>
+          <t>summary.school_elementary_name</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Mesa High School</t>
+          <t>Porter Elementary School</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -13975,12 +13975,12 @@
     <row r="43">
       <c r="A43" s="30" t="inlineStr">
         <is>
-          <t>summary.school_middle_name</t>
+          <t>summary.school_high_name</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Taylor Junior High School</t>
+          <t>Mesa High School</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -14008,22 +14008,22 @@
     <row r="44">
       <c r="A44" s="30" t="inlineStr">
         <is>
-          <t>summary.seller_entity</t>
+          <t>summary.school_middle_name</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Sonoran Residential Holdings LLC</t>
+          <t>Taylor Junior High School</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>Illustrative name</t>
+          <t>Internal underwriting agent — attendance-zone school lookup</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2151 E Southern Ave, Mesa, AZ 85204 on 2026-09-14</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -14034,24 +14034,24 @@
       <c r="F44" s="12" t="n"/>
       <c r="G44" s="26" t="inlineStr">
         <is>
-          <t>An illustrative name. The real party is withheld from the public sample.</t>
+          <t>Looked up for the illustrative address by the internal underwriting agent; the public demo does not run this on an uploaded deal.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="30" t="inlineStr">
         <is>
-          <t>summary.state</t>
+          <t>summary.seller_entity</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>Sonoran Residential Holdings LLC</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Illustrative name</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -14067,19 +14067,19 @@
       <c r="F45" s="12" t="n"/>
       <c r="G45" s="26" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>An illustrative name. The real party is withheld from the public sample.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="30" t="inlineStr">
         <is>
-          <t>summary.street_address</t>
+          <t>summary.state</t>
         </is>
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>2151 E Southern Ave</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -14100,29 +14100,29 @@
       <c r="F46" s="12" t="n"/>
       <c r="G46" s="26" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-10-06.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="30" t="inlineStr">
         <is>
-          <t>summary.structure</t>
+          <t>summary.street_address</t>
         </is>
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>1 &amp; 2 stories</t>
+          <t>2151 E Southern Ave</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>p.10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -14133,29 +14133,29 @@
       <c r="F47" s="12" t="n"/>
       <c r="G47" s="26" t="inlineStr">
         <is>
-          <t>Number of Stories 1 &amp; 2</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-10-06.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="30" t="inlineStr">
         <is>
-          <t>summary.tax_area_code</t>
+          <t>summary.structure</t>
         </is>
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>1 &amp; 2 stories</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.10</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -14166,29 +14166,29 @@
       <c r="F48" s="12" t="n"/>
       <c r="G48" s="26" t="inlineStr">
         <is>
-          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+          <t>Number of Stories 1 &amp; 2</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="30" t="inlineStr">
         <is>
-          <t>summary.tax_basis_label</t>
+          <t>summary.tax_area_code</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Limited property value (LPV), per the county assessor</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>Vendored county rate table</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>property_tax_table.STATE_RULES['AZ']</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -14199,19 +14199,19 @@
       <c r="F49" s="12" t="n"/>
       <c r="G49" s="26" t="inlineStr">
         <is>
-          <t>What the assessed basis is in this state.</t>
+          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="30" t="inlineStr">
         <is>
-          <t>summary.tax_basis_note</t>
+          <t>summary.tax_basis_label</t>
         </is>
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>Arizona taxes the limited property value, not the price. Under Proposition 117 (Ariz. C…</t>
+          <t>Limited property value (LPV), per the county assessor</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
@@ -14232,29 +14232,29 @@
       <c r="F50" s="12" t="n"/>
       <c r="G50" s="26" t="inlineStr">
         <is>
-          <t>How the basis behaves on a sale, with the authority.</t>
+          <t>What the assessed basis is in this state.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="30" t="inlineStr">
         <is>
-          <t>summary.tax_billed_amount</t>
+          <t>summary.tax_basis_note</t>
         </is>
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>249,122</t>
+          <t>Arizona taxes the limited property value, not the price. Under Proposition 117 (Ariz. C…</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>p.10</t>
+          <t>property_tax_table.STATE_RULES['AZ']</t>
         </is>
       </c>
       <c r="E51" s="5" t="inlineStr">
@@ -14265,19 +14265,19 @@
       <c r="F51" s="12" t="n"/>
       <c r="G51" s="26" t="inlineStr">
         <is>
-          <t>2025 Property Tax $249,122</t>
+          <t>How the basis behaves on a sale, with the authority.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="30" t="inlineStr">
         <is>
-          <t>summary.tax_billed_year</t>
+          <t>summary.tax_billed_amount</t>
         </is>
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>2,025</t>
+          <t>249,122</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
@@ -14305,22 +14305,22 @@
     <row r="53">
       <c r="A53" s="30" t="inlineStr">
         <is>
-          <t>summary.tax_divisor</t>
+          <t>summary.tax_billed_year</t>
         </is>
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2,025</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Vendored county rate table</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>property_tax_table.STATE_RULES['AZ']</t>
+          <t>p.10</t>
         </is>
       </c>
       <c r="E53" s="5" t="inlineStr">
@@ -14331,29 +14331,29 @@
       <c r="F53" s="12" t="n"/>
       <c r="G53" s="26" t="inlineStr">
         <is>
-          <t>The rate's unit in Arizona: per $100 of assessed value.</t>
+          <t>2025 Property Tax $249,122</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="30" t="inlineStr">
         <is>
-          <t>summary.tax_exemption</t>
+          <t>summary.tax_divisor</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>property_tax_table.STATE_RULES['AZ']</t>
         </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
@@ -14364,29 +14364,29 @@
       <c r="F54" s="12" t="n"/>
       <c r="G54" s="26" t="inlineStr">
         <is>
-          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
+          <t>The rate's unit in Arizona: per $100 of assessed value.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="30" t="inlineStr">
         <is>
-          <t>summary.tax_parcel_id</t>
+          <t>summary.tax_exemption</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>301-04-002K</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Internal pipeline only</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>p.10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -14397,56 +14397,52 @@
       <c r="F55" s="12" t="n"/>
       <c r="G55" s="26" t="inlineStr">
         <is>
-          <t>Tax Parcel Number 301-04-002K</t>
+          <t>See parcel: read off the county assessor's portal by the internal pipeline only.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="30" t="inlineStr">
         <is>
-          <t>summary.tax_per_unit_flag</t>
+          <t>summary.tax_parcel_id</t>
         </is>
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>In band (the statement's line per unit): $717 per unit a year is inside the AZ band of …</t>
+          <t>301-04-002K</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Vendored county rate table</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>property_tax_table.band_check</t>
+          <t>p.10</t>
         </is>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>summary.tax_statement_amount, summary.unit_count, summary.state</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F56" s="12" t="n"/>
       <c r="G56" s="26" t="inlineStr">
         <is>
-          <t>A sanity check against the state's typical per-unit range. It flags; it never changes a figure.</t>
+          <t>Tax Parcel Number 301-04-002K</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="30" t="inlineStr">
         <is>
-          <t>summary.tax_rate_as_billed</t>
+          <t>summary.tax_per_unit_flag</t>
         </is>
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>In band (the statement's line per unit): $717 per unit a year is inside the AZ band of …</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -14456,30 +14452,34 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>property_tax_table.COUNTY_RATES[('AZ', 'maricopa')]</t>
+          <t>property_tax_table.band_check</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F57" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>summary.tax_statement_amount, summary.unit_count, summary.state</t>
+        </is>
+      </c>
       <c r="G57" s="26" t="inlineStr">
         <is>
-          <t>Tax area code 971300 — City of Phoenix / Deer Valley Unified School District #97, tax year 2025. Maricopa County, '2025 Tax Rates, Maricopa County, Arizona' (the treasurer's rate table by tax area code), row 971300: primary 6.7007, approx residential primary 5.1401, secondary 3.5566. Verified 2026-09-04.</t>
+          <t>A sanity check against the state's typical per-unit range. It flags; it never changes a figure.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="30" t="inlineStr">
         <is>
-          <t>summary.tax_rate_evidence</t>
+          <t>summary.tax_rate_as_billed</t>
         </is>
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>Vendored county rate table: 10.2573 per $100 of assessed value, tax year 2025 — Tax are…</t>
+          <t>10.26</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
@@ -14489,34 +14489,30 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>property_tax_table.evidence_text</t>
+          <t>property_tax_table.COUNTY_RATES[('AZ', 'maricopa')]</t>
         </is>
       </c>
       <c r="E58" s="5" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>summary.state, summary.county, summary.tax_parcel_id, summary.tax_billed_amount, summary.tax_billed_year</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F58" s="12" t="n"/>
       <c r="G58" s="26" t="inlineStr">
         <is>
-          <t>The citation, tax year and jurisdiction stack behind the rate, or the honest note that none is on file. Also records what the uploaded document stated for the field(s) it cites.</t>
+          <t>Tax area code 971300 — City of Phoenix / Deer Valley Unified School District #97, tax year 2025. Maricopa County, '2025 Tax Rates, Maricopa County, Arizona' (the treasurer's rate table by tax area code), row 971300: primary 6.7007, approx residential primary 5.1401, secondary 3.5566. Verified 2026-09-04.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="30" t="inlineStr">
         <is>
-          <t>summary.tax_rate_year</t>
+          <t>summary.tax_rate_evidence</t>
         </is>
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>2,025</t>
+          <t>Vendored county rate table: 10.2573 per $100 of assessed value, tax year 2025 — Tax are…</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -14526,147 +14522,151 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>property_tax_table.COUNTY_RATES[('AZ', 'maricopa')]</t>
+          <t>property_tax_table.evidence_text</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F59" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>summary.state, summary.county, summary.tax_parcel_id, summary.tax_billed_amount, summary.tax_billed_year</t>
+        </is>
+      </c>
       <c r="G59" s="26" t="inlineStr">
         <is>
-          <t>The tax year of the rate on file. A bill from another year is displayed, not tied out.</t>
+          <t>The citation, tax year and jurisdiction stack behind the rate, or the honest note that none is on file. Also records what the uploaded document stated for the field(s) it cites.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="30" t="inlineStr">
         <is>
-          <t>summary.tax_statement_amount</t>
+          <t>summary.tax_rate_year</t>
         </is>
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>239,566.79</t>
+          <t>2,025</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>Sample Property T-12 June 26.xlsx</t>
+          <t>Vendored county rate table</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Property Taxes lines</t>
+          <t>property_tax_table.COUNTY_RATES[('AZ', 'maricopa')]</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>computed</t>
-        </is>
-      </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>t12.rows</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F60" s="12" t="n"/>
       <c r="G60" s="26" t="inlineStr">
         <is>
-          <t>The statement's lines categorised as Property Taxes, summed over its twelve months. As billed in the statement, not the county's bill.</t>
+          <t>The tax year of the rate on file. A bill from another year is displayed, not tied out.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="30" t="inlineStr">
         <is>
-          <t>summary.unit_count</t>
+          <t>summary.tax_statement_amount</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>239,566.79</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>Sample Property RR 8.4.26.xlsx</t>
+          <t>Sample Property T-12 June 26.xlsx</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Property Taxes lines</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>derived</t>
+          <t>computed</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>rent_roll.units</t>
+          <t>t12.rows</t>
         </is>
       </c>
       <c r="G61" s="26" t="inlineStr">
         <is>
-          <t>Counted from the rows of the uploaded rent roll.</t>
+          <t>The statement's lines categorised as Property Taxes, summed over its twelve months. As billed in the statement, not the county's bill.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="30" t="inlineStr">
         <is>
-          <t>summary.year_built</t>
+          <t>summary.unit_count</t>
         </is>
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>1,981</t>
+          <t>334</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>Sample Property Offering Memorandum.pdf</t>
+          <t>Sample Property RR 8.4.26.xlsx</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>p.10</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E62" s="5" t="inlineStr">
         <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F62" s="12" t="n"/>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>rent_roll.units</t>
+        </is>
+      </c>
       <c r="G62" s="26" t="inlineStr">
         <is>
-          <t>Y ear Built 1981</t>
+          <t>Counted from the rows of the uploaded rent roll.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="30" t="inlineStr">
         <is>
-          <t>summary.zip</t>
+          <t>summary.year_built</t>
         </is>
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>85204</t>
+          <t>1,981</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Illustrative address</t>
+          <t>Sample Property Offering Memorandum.pdf</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>p.10</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
@@ -14677,99 +14677,99 @@
       <c r="F63" s="12" t="n"/>
       <c r="G63" s="26" t="inlineStr">
         <is>
-          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-09-14.</t>
+          <t>Y ear Built 1981</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="30" t="inlineStr">
         <is>
-          <t>supply.projects</t>
+          <t>summary.zip</t>
         </is>
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>32 entries</t>
+          <t>85204</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Public permit and entitlement records (the operator's supply pipeline), via the market-report service</t>
+          <t>Illustrative address</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>POST /report (format json)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>derived</t>
-        </is>
-      </c>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>supply.rings</t>
-        </is>
-      </c>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F64" s="12" t="n"/>
       <c r="G64" s="26" t="inlineStr">
         <is>
-          <t>The developments the counts are made of, within 3 mi: one row per development, reconciled across the pipeline's lifecycle layers and shown at the furthest stage any layer carries.</t>
+          <t>Illustrative address — not the asset's real location. The market tabs were pulled for this address on 2026-10-06.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="30" t="inlineStr">
         <is>
+          <t>supply.projects</t>
+        </is>
+      </c>
+      <c r="B65" s="5" t="inlineStr">
+        <is>
+          <t>33 entries</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
+        <is>
+          <t>Public permit and entitlement records (the operator's supply pipeline), via the market-report service</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="inlineStr">
+        <is>
+          <t>POST /report (format json)</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>derived</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
           <t>supply.rings</t>
         </is>
       </c>
-      <c r="B65" s="5" t="inlineStr">
-        <is>
-          <t>8 entries</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
-        <is>
-          <t>Public permit and entitlement records (the operator's supply pipeline), via the market-report service</t>
-        </is>
-      </c>
-      <c r="D65" s="5" t="inlineStr">
-        <is>
-          <t>POST /report (format json)</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>read</t>
-        </is>
-      </c>
-      <c r="F65" s="12" t="n"/>
       <c r="G65" s="26" t="inlineStr">
         <is>
-          <t>Projects and units by cumulative ring and tracked stage, counted from the service's project rows.</t>
+          <t>The developments the counts are made of, within 3 mi: one row per development, reconciled across the pipeline's lifecycle layers and shown at the furthest stage any layer carries.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="30" t="inlineStr">
         <is>
-          <t>t12.month_labels</t>
+          <t>supply.rings</t>
         </is>
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>12 entries</t>
+          <t>8 entries</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Sample Property T-12 June 26.xlsx</t>
+          <t>Public permit and entitlement records (the operator's supply pipeline), via the market-report service</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>statement</t>
+          <t>POST /report (format json)</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
@@ -14780,19 +14780,19 @@
       <c r="F66" s="12" t="n"/>
       <c r="G66" s="26" t="inlineStr">
         <is>
-          <t>Read from the uploaded statement.</t>
+          <t>Projects and units by cumulative ring and tracked stage, counted from the service's project rows.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="30" t="inlineStr">
         <is>
-          <t>t12.source_subtotals</t>
+          <t>t12.month_labels</t>
         </is>
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>4 keys</t>
+          <t>12 entries</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
@@ -14802,7 +14802,7 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>header block</t>
+          <t>statement</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -14811,17 +14811,21 @@
         </is>
       </c>
       <c r="F67" s="12" t="n"/>
-      <c r="G67" s="31" t="n"/>
+      <c r="G67" s="26" t="inlineStr">
+        <is>
+          <t>Read from the uploaded statement.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="30" t="inlineStr">
         <is>
-          <t>t12.units</t>
+          <t>t12.source_subtotals</t>
         </is>
       </c>
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>4 keys</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
@@ -14831,7 +14835,7 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>statement</t>
+          <t>header block</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
@@ -14840,31 +14844,27 @@
         </is>
       </c>
       <c r="F68" s="12" t="n"/>
-      <c r="G68" s="26" t="inlineStr">
-        <is>
-          <t>Read from the uploaded statement.</t>
-        </is>
-      </c>
+      <c r="G68" s="31" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="30" t="inlineStr">
         <is>
-          <t>trade_out.rows</t>
+          <t>t12.units</t>
         </is>
       </c>
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>0 entries</t>
+          <t>334</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Internal pipeline only</t>
+          <t>Sample Property T-12 June 26.xlsx</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>statement</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
@@ -14874,6 +14874,39 @@
       </c>
       <c r="F69" s="12" t="n"/>
       <c r="G69" s="26" t="inlineStr">
+        <is>
+          <t>Read from the uploaded statement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="30" t="inlineStr">
+        <is>
+          <t>trade_out.rows</t>
+        </is>
+      </c>
+      <c r="B70" s="5" t="inlineStr">
+        <is>
+          <t>0 entries</t>
+        </is>
+      </c>
+      <c r="C70" s="5" t="inlineStr">
+        <is>
+          <t>Internal pipeline only</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="F70" s="12" t="n"/>
+      <c r="G70" s="26" t="inlineStr">
         <is>
           <t>The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
         </is>
@@ -15008,16 +15041,16 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>7205.408782354566</v>
+        <v>7205.769022616706</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>56132.3904975113</v>
+        <v>56132.49059874286</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>146225.0843639599</v>
+        <v>146226.2857280746</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>419520.7372023506</v>
+        <v>419524.3564018827</v>
       </c>
       <c r="F10" s="7" t="n">
         <v>1790242</v>
@@ -15042,10 +15075,10 @@
         <v>58574</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>150543</v>
+        <v>150544</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>437696</v>
+        <v>437699</v>
       </c>
       <c r="F11" s="7" t="n">
         <v>1892613</v>
@@ -15064,16 +15097,16 @@
         </is>
       </c>
       <c r="B12" s="11" t="n">
-        <v>0.07016829064349328</v>
+        <v>0.07011478938577254</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>0.04349733693591684</v>
+        <v>0.0434954760641213</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>0.02952924017668956</v>
+        <v>0.02952762049878443</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>0.0433238721853284</v>
+        <v>0.04332202247801553</v>
       </c>
       <c r="F12" s="11" t="n">
         <v>0.05718277193809551</v>
@@ -15119,10 +15152,10 @@
         <v>61239.48308749999</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>157393.64739375</v>
+        <v>157394.6929</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>457613.9036</v>
+        <v>457617.04011875</v>
       </c>
       <c r="F14" s="7" t="n">
         <v>1978738.72033125</v>
@@ -15193,16 +15226,16 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>20710</v>
+        <v>20712</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>155942</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>393000</v>
+        <v>393001</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1100029</v>
+        <v>1100032</v>
       </c>
       <c r="F18" s="7" t="n">
         <v>4845832</v>
@@ -15221,7 +15254,7 @@
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>20297</v>
+        <v>20298</v>
       </c>
       <c r="C19" s="7" t="n">
         <v>159356</v>
@@ -15230,7 +15263,7 @@
         <v>394900</v>
       </c>
       <c r="E19" s="7" t="n">
-        <v>1119327</v>
+        <v>1119329</v>
       </c>
       <c r="F19" s="7" t="n">
         <v>5028754</v>
@@ -15249,16 +15282,16 @@
         </is>
       </c>
       <c r="B20" s="11" t="n">
-        <v>-0.01994205697730567</v>
+        <v>-0.01998841251448435</v>
       </c>
       <c r="C20" s="11" t="n">
         <v>0.0218927549986534</v>
       </c>
       <c r="D20" s="11" t="n">
-        <v>0.004834605597964448</v>
+        <v>0.004832048773412811</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>0.01754317386177995</v>
+        <v>0.01754221695368852</v>
       </c>
       <c r="F20" s="11" t="n">
         <v>0.03774831649136834</v>
@@ -15298,7 +15331,7 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>20745.989937</v>
+        <v>20747.012058</v>
       </c>
       <c r="C22" s="7" t="n">
         <v>162881.114076</v>
@@ -15307,7 +15340,7 @@
         <v>403635.5828999999</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>1144087.632567</v>
+        <v>1144089.676809</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>5139995.067233999</v>
@@ -15391,7 +15424,7 @@
         <v>6243</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>17153</v>
+        <v>17154</v>
       </c>
       <c r="E27" s="7" t="n">
         <v>47798</v>
@@ -15419,10 +15452,10 @@
         <v>10719</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>25455</v>
+        <v>25456</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>64599</v>
+        <v>64600</v>
       </c>
       <c r="F28" s="7" t="n">
         <v>288010</v>
@@ -15441,7 +15474,7 @@
         </is>
       </c>
       <c r="B29" s="7" t="n">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="C29" s="7" t="n">
         <v>10649</v>
@@ -15450,7 +15483,7 @@
         <v>25949</v>
       </c>
       <c r="E29" s="7" t="n">
-        <v>70655</v>
+        <v>70656</v>
       </c>
       <c r="F29" s="7" t="n">
         <v>302932</v>
@@ -15503,10 +15536,10 @@
         <v>7376</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>16579</v>
+        <v>16580</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>51719</v>
+        <v>51720</v>
       </c>
       <c r="F31" s="7" t="n">
         <v>217512</v>
@@ -15531,7 +15564,7 @@
         <v>4953</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>12640</v>
+        <v>12641</v>
       </c>
       <c r="E32" s="7" t="n">
         <v>38937</v>
@@ -15553,13 +15586,13 @@
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C33" s="7" t="n">
-        <v>5032</v>
+        <v>5031</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>14857</v>
+        <v>14856</v>
       </c>
       <c r="E33" s="7" t="n">
         <v>47604</v>
@@ -15612,13 +15645,13 @@
         <v>5566</v>
       </c>
       <c r="C35" s="7" t="n">
-        <v>41613</v>
+        <v>41612</v>
       </c>
       <c r="D35" s="7" t="n">
         <v>107934</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>325299</v>
+        <v>325301</v>
       </c>
       <c r="F35" s="7" t="n">
         <v>1393097</v>
@@ -15671,7 +15704,7 @@
         <v>22337</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>60138</v>
+        <v>60137</v>
       </c>
       <c r="E37" s="7" t="n">
         <v>193645</v>
@@ -15780,13 +15813,13 @@
         </is>
       </c>
       <c r="B43" s="7" t="n">
-        <v>94565</v>
+        <v>94562</v>
       </c>
       <c r="C43" s="7" t="n">
-        <v>98600</v>
+        <v>98599</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>105369</v>
+        <v>105367</v>
       </c>
       <c r="E43" s="7" t="n">
         <v>113475</v>
@@ -15808,16 +15841,16 @@
         </is>
       </c>
       <c r="B44" s="7" t="n">
-        <v>79735</v>
+        <v>79731</v>
       </c>
       <c r="C44" s="7" t="n">
-        <v>79858</v>
+        <v>79857</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>82683</v>
+        <v>82682</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>89671</v>
+        <v>89670</v>
       </c>
       <c r="F44" s="7" t="n">
         <v>88866</v>
@@ -15857,13 +15890,13 @@
         </is>
       </c>
       <c r="B46" s="7" t="n">
-        <v>106654.56786</v>
+        <v>106651.184328</v>
       </c>
       <c r="C46" s="7" t="n">
-        <v>111205.4184</v>
+        <v>111204.290556</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>118839.794436</v>
+        <v>118837.538748</v>
       </c>
       <c r="E46" s="7" t="n">
         <v>127982.0979</v>
@@ -15913,13 +15946,13 @@
         </is>
       </c>
       <c r="B48" s="11" t="n">
-        <v>0.1848874319251309</v>
+        <v>0.184893297519088</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>0.1773212981744422</v>
+        <v>0.1773230965831297</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>0.165930017367537</v>
+        <v>0.1659331669308227</v>
       </c>
       <c r="E48" s="11" t="n">
         <v>0.1540769332452082</v>
@@ -16106,16 +16139,16 @@
         </is>
       </c>
       <c r="B63" s="7" t="n">
-        <v>4140</v>
+        <v>4138</v>
       </c>
       <c r="C63" s="7" t="n">
-        <v>59139</v>
+        <v>59160</v>
       </c>
       <c r="D63" s="7" t="n">
         <v>150089</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>458614</v>
+        <v>458587</v>
       </c>
       <c r="F63" s="12" t="n"/>
       <c r="G63" s="12" t="n"/>
@@ -16128,16 +16161,16 @@
         </is>
       </c>
       <c r="B64" s="7" t="n">
-        <v>4549</v>
+        <v>4547</v>
       </c>
       <c r="C64" s="7" t="n">
-        <v>58261</v>
+        <v>58281</v>
       </c>
       <c r="D64" s="7" t="n">
-        <v>150082</v>
+        <v>150081</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>455835</v>
+        <v>455808</v>
       </c>
       <c r="F64" s="12" t="n"/>
       <c r="G64" s="12" t="n"/>
@@ -16150,16 +16183,16 @@
         </is>
       </c>
       <c r="B65" s="7" t="n">
-        <v>4552</v>
+        <v>4551</v>
       </c>
       <c r="C65" s="7" t="n">
-        <v>59079</v>
+        <v>59099</v>
       </c>
       <c r="D65" s="7" t="n">
         <v>152118</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>466392</v>
+        <v>466363</v>
       </c>
       <c r="F65" s="12" t="n"/>
       <c r="G65" s="12" t="n"/>
@@ -16172,16 +16205,16 @@
         </is>
       </c>
       <c r="B66" s="7" t="n">
-        <v>4741</v>
+        <v>4739</v>
       </c>
       <c r="C66" s="7" t="n">
-        <v>63403</v>
+        <v>63423</v>
       </c>
       <c r="D66" s="7" t="n">
         <v>162056</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>501214</v>
+        <v>501185</v>
       </c>
       <c r="F66" s="12" t="n"/>
       <c r="G66" s="12" t="n"/>
@@ -16194,16 +16227,16 @@
         </is>
       </c>
       <c r="B67" s="7" t="n">
-        <v>5239</v>
+        <v>5237</v>
       </c>
       <c r="C67" s="7" t="n">
-        <v>65083</v>
+        <v>65104</v>
       </c>
       <c r="D67" s="7" t="n">
         <v>165142</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>516916</v>
+        <v>516884</v>
       </c>
       <c r="F67" s="12" t="n"/>
       <c r="G67" s="12" t="n"/>
@@ -16216,16 +16249,16 @@
         </is>
       </c>
       <c r="B68" s="11" t="n">
-        <v>0.2654589371980676</v>
+        <v>0.2655872402126631</v>
       </c>
       <c r="C68" s="11" t="n">
-        <v>0.1005089703917887</v>
+        <v>0.100473292765382</v>
       </c>
       <c r="D68" s="11" t="n">
         <v>0.1002938256634396</v>
       </c>
       <c r="E68" s="11" t="n">
-        <v>0.1271265159807595</v>
+        <v>0.1271230976892062</v>
       </c>
       <c r="F68" s="12" t="n"/>
       <c r="G68" s="12" t="n"/>
@@ -16243,16 +16276,16 @@
         </is>
       </c>
       <c r="B69" s="11" t="n">
-        <v>0.06062537773196808</v>
+        <v>0.06065226052044004</v>
       </c>
       <c r="C69" s="11" t="n">
-        <v>0.02423213297708893</v>
+        <v>0.02422383167818176</v>
       </c>
       <c r="D69" s="11" t="n">
         <v>0.02418207107245318</v>
       </c>
       <c r="E69" s="11" t="n">
-        <v>0.03036990821614882</v>
+        <v>0.03036912700199279</v>
       </c>
       <c r="F69" s="12" t="n"/>
       <c r="G69" s="12" t="n"/>
@@ -16292,13 +16325,13 @@
         <v>2026</v>
       </c>
       <c r="B73" s="10" t="n">
-        <v>2469.37</v>
+        <v>2468.69</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>0.002793919975309533</v>
+        <v>0.002517776721935983</v>
       </c>
       <c r="D73" s="11" t="n">
-        <v>0.0431</v>
+        <v>0.04389999999999999</v>
       </c>
     </row>
     <row r="74">
@@ -16505,16 +16538,16 @@
         </is>
       </c>
       <c r="B88" s="11" t="n">
-        <v>0.1675892345867532</v>
+        <v>0.1676532365858316</v>
       </c>
       <c r="C88" s="11" t="n">
-        <v>0.1324022003011585</v>
+        <v>0.1323574588350946</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>0.128294871717239</v>
+        <v>0.1282956485933318</v>
       </c>
       <c r="E88" s="11" t="n">
-        <v>0.1575223875399726</v>
+        <v>0.1575340743105333</v>
       </c>
       <c r="F88" s="11" t="n">
         <v>0.1439230188830762</v>
@@ -16538,16 +16571,16 @@
         </is>
       </c>
       <c r="B89" s="11" t="n">
-        <v>0.1402939492269517</v>
+        <v>0.1403475272102349</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>0.1312959036292677</v>
+        <v>0.1312668960432539</v>
       </c>
       <c r="D89" s="11" t="n">
-        <v>0.1295604415567115</v>
+        <v>0.1295612260963292</v>
       </c>
       <c r="E89" s="11" t="n">
-        <v>0.1260357078602561</v>
+        <v>0.1260396413128646</v>
       </c>
       <c r="F89" s="11" t="n">
         <v>0.1090536545703669</v>
@@ -16571,16 +16604,16 @@
         </is>
       </c>
       <c r="B90" s="11" t="n">
-        <v>0.1093720175606032</v>
+        <v>0.1094137865189994</v>
       </c>
       <c r="C90" s="11" t="n">
-        <v>0.09160751052518361</v>
+        <v>0.09159191447530106</v>
       </c>
       <c r="D90" s="11" t="n">
-        <v>0.09612275421907074</v>
+        <v>0.09612333628029211</v>
       </c>
       <c r="E90" s="11" t="n">
-        <v>0.0974934080326242</v>
+        <v>0.09749944378343345</v>
       </c>
       <c r="F90" s="11" t="n">
         <v>0.09153364975214603</v>
@@ -16604,16 +16637,16 @@
         </is>
       </c>
       <c r="B91" s="11" t="n">
-        <v>0.09200229051345676</v>
+        <v>0.09203742600725606</v>
       </c>
       <c r="C91" s="11" t="n">
-        <v>0.1102148059371255</v>
+        <v>0.1101929220938806</v>
       </c>
       <c r="D91" s="11" t="n">
-        <v>0.09007950685163767</v>
+        <v>0.09008005231861065</v>
       </c>
       <c r="E91" s="11" t="n">
-        <v>0.07061675278623067</v>
+        <v>0.07061532062257563</v>
       </c>
       <c r="F91" s="11" t="n">
         <v>0.08654896600644772</v>
@@ -16637,16 +16670,16 @@
         </is>
       </c>
       <c r="B92" s="11" t="n">
-        <v>0.03397594960870395</v>
+        <v>0.03398892495703647</v>
       </c>
       <c r="C92" s="11" t="n">
-        <v>0.1437571064195937</v>
+        <v>0.1437238879331531</v>
       </c>
       <c r="D92" s="11" t="n">
-        <v>0.1065198040486124</v>
+        <v>0.1065265044628259</v>
       </c>
       <c r="E92" s="11" t="n">
-        <v>0.07423822393150158</v>
+        <v>0.07424281996962574</v>
       </c>
       <c r="F92" s="11" t="n">
         <v>0.07168567465967132</v>
@@ -16670,16 +16703,16 @@
         </is>
       </c>
       <c r="B93" s="11" t="n">
-        <v>0.05630845581217789</v>
+        <v>0.05632995990070651</v>
       </c>
       <c r="C93" s="11" t="n">
-        <v>0.09185335423004824</v>
+        <v>0.09206807569427378</v>
       </c>
       <c r="D93" s="11" t="n">
-        <v>0.1103528457155314</v>
+        <v>0.1103474585508229</v>
       </c>
       <c r="E93" s="11" t="n">
-        <v>0.09778359001541834</v>
+        <v>0.09778383973224218</v>
       </c>
       <c r="F93" s="11" t="n">
         <v>0.0692937123890178</v>
@@ -16703,16 +16736,16 @@
         </is>
       </c>
       <c r="B94" s="11" t="n">
-        <v>0.01355220461920214</v>
+        <v>0.01355738017949207</v>
       </c>
       <c r="C94" s="11" t="n">
-        <v>0.02564457146369196</v>
+        <v>0.02563590562791841</v>
       </c>
       <c r="D94" s="11" t="n">
-        <v>0.02846623835100489</v>
+        <v>0.02846641072531518</v>
       </c>
       <c r="E94" s="11" t="n">
-        <v>0.06430626193373404</v>
+        <v>0.06430443909186763</v>
       </c>
       <c r="F94" s="11" t="n">
         <v>0.06699836548547758</v>
@@ -16736,16 +16769,16 @@
         </is>
       </c>
       <c r="B95" s="11" t="n">
-        <v>0.005344531399121969</v>
+        <v>0.005346572465151804</v>
       </c>
       <c r="C95" s="11" t="n">
-        <v>0.03838234842199072</v>
+        <v>0.03838473826492996</v>
       </c>
       <c r="D95" s="11" t="n">
-        <v>0.04546362849167086</v>
+        <v>0.04546390379188819</v>
       </c>
       <c r="E95" s="11" t="n">
-        <v>0.06499302595968018</v>
+        <v>0.06499124563490911</v>
       </c>
       <c r="F95" s="11" t="n">
         <v>0.06180957654864814</v>
@@ -16769,16 +16802,16 @@
         </is>
       </c>
       <c r="B96" s="11" t="n">
-        <v>0.03531208245848445</v>
+        <v>0.03532556807332442</v>
       </c>
       <c r="C96" s="11" t="n">
-        <v>0.06550198211487047</v>
+        <v>0.06547984762840993</v>
       </c>
       <c r="D96" s="11" t="n">
-        <v>0.05942728423245309</v>
+        <v>0.0594276440881181</v>
       </c>
       <c r="E96" s="11" t="n">
-        <v>0.06130384568509065</v>
+        <v>0.06130183696566935</v>
       </c>
       <c r="F96" s="11" t="n">
         <v>0.06005544300027939</v>
@@ -16802,16 +16835,16 @@
         </is>
       </c>
       <c r="B97" s="11" t="n">
-        <v>0.01068906279824394</v>
+        <v>0.01069314493030361</v>
       </c>
       <c r="C97" s="11" t="n">
-        <v>0.006038536000737531</v>
+        <v>0.006036495453428361</v>
       </c>
       <c r="D97" s="11" t="n">
-        <v>0.01906832260525726</v>
+        <v>0.01906843807147788</v>
       </c>
       <c r="E97" s="11" t="n">
-        <v>0.02301916942178338</v>
+        <v>0.0230167251903228</v>
       </c>
       <c r="F97" s="11" t="n">
         <v>0.0473268911935302</v>
@@ -16835,16 +16868,16 @@
         </is>
       </c>
       <c r="B98" s="11" t="n">
-        <v>0.007825920977285742</v>
+        <v>0.007828909681115142</v>
       </c>
       <c r="C98" s="11" t="n">
-        <v>0.03606219845733075</v>
+        <v>0.03605001228803146</v>
       </c>
       <c r="D98" s="11" t="n">
-        <v>0.03811847913626373</v>
+        <v>0.03811870995870221</v>
       </c>
       <c r="E98" s="11" t="n">
-        <v>0.03247329842121656</v>
+        <v>0.03245015815897153</v>
       </c>
       <c r="F98" s="11" t="n">
         <v>0.04109248140049621</v>
@@ -16871,13 +16904,13 @@
         <v>0</v>
       </c>
       <c r="C99" s="11" t="n">
-        <v>0.001859193018038782</v>
+        <v>0.001873924797247481</v>
       </c>
       <c r="D99" s="11" t="n">
-        <v>0.02761848821930085</v>
+        <v>0.02761865546014945</v>
       </c>
       <c r="E99" s="11" t="n">
-        <v>0.02183329238543132</v>
+        <v>0.02183464406976407</v>
       </c>
       <c r="F99" s="11" t="n">
         <v>0.03285591679200175</v>
@@ -16901,16 +16934,16 @@
         </is>
       </c>
       <c r="B100" s="11" t="n">
-        <v>0.01546096583317427</v>
+        <v>0.01546687034561772</v>
       </c>
       <c r="C100" s="11" t="n">
-        <v>0.02945514888909376</v>
+        <v>0.02944519537970017</v>
       </c>
       <c r="D100" s="11" t="n">
-        <v>0.03031917792458657</v>
+        <v>0.03031936151917744</v>
       </c>
       <c r="E100" s="11" t="n">
-        <v>0.02663677147395037</v>
+        <v>0.02663842053841764</v>
       </c>
       <c r="F100" s="11" t="n">
         <v>0.02745633069056147</v>
@@ -16934,16 +16967,16 @@
         </is>
       </c>
       <c r="B101" s="11" t="n">
-        <v>0.2744798625691926</v>
+        <v>0.2742027878556426</v>
       </c>
       <c r="C101" s="11" t="n">
-        <v>0.03211333394794259</v>
+        <v>0.03210248218235439</v>
       </c>
       <c r="D101" s="11" t="n">
-        <v>0.0287326741066833</v>
+        <v>0.02873284809436727</v>
       </c>
       <c r="E101" s="11" t="n">
-        <v>0.02107301559051066</v>
+        <v>0.02107432020662236</v>
       </c>
       <c r="F101" s="11" t="n">
         <v>0.02090656164729619</v>
@@ -16967,16 +17000,16 @@
         </is>
       </c>
       <c r="B102" s="11" t="n">
-        <v>0.03340332124451231</v>
+        <v>0.03341607790719878</v>
       </c>
       <c r="C102" s="11" t="n">
-        <v>0.03411081404996773</v>
+        <v>0.03409928729417547</v>
       </c>
       <c r="D102" s="11" t="n">
-        <v>0.02407610374039469</v>
+        <v>0.02407019413595572</v>
       </c>
       <c r="E102" s="11" t="n">
-        <v>0.02037464428525276</v>
+        <v>0.02037590566567031</v>
       </c>
       <c r="F102" s="11" t="n">
         <v>0.02084382439592392</v>
@@ -17000,16 +17033,16 @@
         </is>
       </c>
       <c r="B103" s="11" t="n">
-        <v>0.002672265699560985</v>
+        <v>0.002673286232575902</v>
       </c>
       <c r="C103" s="11" t="n">
-        <v>0.01090931440336806</v>
+        <v>0.01090562791840747</v>
       </c>
       <c r="D103" s="11" t="n">
-        <v>0.01293424486657018</v>
+        <v>0.01293432318852866</v>
       </c>
       <c r="E103" s="11" t="n">
-        <v>0.01705883149519169</v>
+        <v>0.0170598875958869</v>
       </c>
       <c r="F103" s="11" t="n">
         <v>0.01906250470529385</v>
@@ -17033,16 +17066,16 @@
         </is>
       </c>
       <c r="B104" s="11" t="n">
-        <v>0.0005726283641916397</v>
+        <v>0.0005728470498376934</v>
       </c>
       <c r="C104" s="11" t="n">
-        <v>0.01676346762545712</v>
+        <v>0.01675780289997542</v>
       </c>
       <c r="D104" s="11" t="n">
-        <v>0.01896538151783606</v>
+        <v>0.01896549636070775</v>
       </c>
       <c r="E104" s="11" t="n">
-        <v>0.01917522542303697</v>
+        <v>0.01917447788192731</v>
       </c>
       <c r="F104" s="11" t="n">
         <v>0.01809509628913341</v>
@@ -17066,16 +17099,16 @@
         </is>
       </c>
       <c r="B105" s="11" t="n">
-        <v>0.001145256728383279</v>
+        <v>0.001145694099675387</v>
       </c>
       <c r="C105" s="11" t="n">
-        <v>0.0007221658830398574</v>
+        <v>0.0007219218481199312</v>
       </c>
       <c r="D105" s="11" t="n">
-        <v>0.003772488086082971</v>
+        <v>0.003772510929987526</v>
       </c>
       <c r="E105" s="11" t="n">
-        <v>0.002512975970997278</v>
+        <v>0.002513131547636321</v>
       </c>
       <c r="F105" s="11" t="n">
         <v>0.006769767671410718</v>
@@ -17102,13 +17135,13 @@
         <v>0</v>
       </c>
       <c r="C106" s="11" t="n">
-        <v>0.0006299744937156203</v>
+        <v>0.0006297616121897272</v>
       </c>
       <c r="D106" s="11" t="n">
-        <v>0.001725777053826078</v>
+        <v>0.001725787504087392</v>
       </c>
       <c r="E106" s="11" t="n">
-        <v>0.001151055198416767</v>
+        <v>0.001151126459463904</v>
       </c>
       <c r="F106" s="11" t="n">
         <v>0.003239751660864168</v>
@@ -17135,13 +17168,13 @@
         <v>0</v>
       </c>
       <c r="C107" s="11" t="n">
-        <v>0.0006760701883777388</v>
+        <v>0.0006758417301548292</v>
       </c>
       <c r="D107" s="11" t="n">
-        <v>0.0003814875592668172</v>
+        <v>0.0003814898693245813</v>
       </c>
       <c r="E107" s="11" t="n">
-        <v>0.0003985165897039564</v>
+        <v>0.0003985412615959063</v>
       </c>
       <c r="F107" s="11" t="n">
         <v>0.00144881225835702</v>
@@ -17169,7 +17202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:N81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -17177,7 +17210,7 @@
     <col width="42" customWidth="1" min="3" max="3"/>
     <col width="42" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
@@ -17198,7 +17231,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Mesa Apt — as of 2026-09-03</t>
+          <t>Sample Mesa Apt — as of 2026-09-30</t>
         </is>
       </c>
     </row>
@@ -17324,7 +17357,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>1BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>1BR — lowest five of 5 available</t>
         </is>
       </c>
       <c r="E8" s="15" t="n">
@@ -17335,13 +17368,13 @@
         <v>688</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>1047</v>
+        <v>1199.8</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J8" s="7" t="n">
-        <v>1047</v>
+        <v>1199.8</v>
       </c>
       <c r="K8" s="16">
         <f>IFERROR(H8/G8,"")</f>
@@ -17349,7 +17382,7 @@
       </c>
       <c r="L8" s="12" t="n"/>
       <c r="M8" s="17" t="n">
-        <v>46268</v>
+        <v>46295</v>
       </c>
       <c r="N8" s="5" t="inlineStr">
         <is>
@@ -17371,7 +17404,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>1BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>1BR — lowest five of 9 available</t>
         </is>
       </c>
       <c r="E9" s="15" t="n">
@@ -17382,13 +17415,13 @@
         <v>625</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>978</v>
+        <v>996</v>
       </c>
       <c r="I9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>978</v>
+        <v>996</v>
       </c>
       <c r="K9" s="16">
         <f>IFERROR(H9/G9,"")</f>
@@ -17396,7 +17429,7 @@
       </c>
       <c r="L9" s="12" t="n"/>
       <c r="M9" s="17" t="n">
-        <v>46267</v>
+        <v>46294</v>
       </c>
       <c r="N9" s="5" t="inlineStr">
         <is>
@@ -17418,7 +17451,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>2BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>2BR — lowest five of 9 available</t>
         </is>
       </c>
       <c r="E10" s="15" t="n">
@@ -17429,13 +17462,13 @@
         <v>725</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>1306</v>
+        <v>1186</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>1306</v>
+        <v>1186</v>
       </c>
       <c r="K10" s="16">
         <f>IFERROR(H10/G10,"")</f>
@@ -17443,7 +17476,7 @@
       </c>
       <c r="L10" s="12" t="n"/>
       <c r="M10" s="17" t="n">
-        <v>46267</v>
+        <v>46294</v>
       </c>
       <c r="N10" s="5" t="inlineStr">
         <is>
@@ -17465,7 +17498,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>1BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>1BR — lowest five of 6 available</t>
         </is>
       </c>
       <c r="E11" s="15" t="n">
@@ -17476,13 +17509,13 @@
         <v>579</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>1201</v>
+        <v>1243</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>139</v>
+        <v>95.14</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>1062</v>
+        <v>1147.86</v>
       </c>
       <c r="K11" s="16">
         <f>IFERROR(H11/G11,"")</f>
@@ -17490,7 +17523,7 @@
       </c>
       <c r="L11" s="12" t="n"/>
       <c r="M11" s="17" t="n">
-        <v>46268</v>
+        <v>46295</v>
       </c>
       <c r="N11" s="5" t="inlineStr">
         <is>
@@ -17508,11 +17541,11 @@
         <v>0.92</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>1BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>1BR — lowest five of 10 available</t>
         </is>
       </c>
       <c r="E12" s="15" t="n">
@@ -17523,13 +17556,13 @@
         <v>658</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>1044</v>
+        <v>1042.6</v>
       </c>
       <c r="I12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J12" s="7" t="n">
-        <v>1044</v>
+        <v>1042.6</v>
       </c>
       <c r="K12" s="16">
         <f>IFERROR(H12/G12,"")</f>
@@ -17537,7 +17570,7 @@
       </c>
       <c r="L12" s="12" t="n"/>
       <c r="M12" s="17" t="n">
-        <v>46267</v>
+        <v>46294</v>
       </c>
       <c r="N12" s="5" t="inlineStr">
         <is>
@@ -17548,18 +17581,18 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Gilbert Greens Apartments</t>
+          <t>Lucera Apartments</t>
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>1.63</v>
+        <v>1.46</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>1BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>1BR — lowest five of 2 available</t>
         </is>
       </c>
       <c r="E13" s="15" t="n">
@@ -17567,16 +17600,16 @@
       </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="7" t="n">
-        <v>605</v>
+        <v>530</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>1250</v>
+        <v>1109</v>
       </c>
       <c r="I13" s="7" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="J13" s="7" t="n">
-        <v>1202</v>
+        <v>1109</v>
       </c>
       <c r="K13" s="16">
         <f>IFERROR(H13/G13,"")</f>
@@ -17584,7 +17617,7 @@
       </c>
       <c r="L13" s="12" t="n"/>
       <c r="M13" s="17" t="n">
-        <v>46267</v>
+        <v>46295</v>
       </c>
       <c r="N13" s="5" t="inlineStr">
         <is>
@@ -17595,35 +17628,35 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Gilbert Greens Apartments</t>
+          <t>Lucera Apartments</t>
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>1.63</v>
+        <v>1.46</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>2BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>1BR — lowest five of 4 available</t>
         </is>
       </c>
       <c r="E14" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="7" t="n">
-        <v>808</v>
+        <v>700</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>1425</v>
+        <v>1244.25</v>
       </c>
       <c r="I14" s="7" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="J14" s="7" t="n">
-        <v>1370</v>
+        <v>1244.25</v>
       </c>
       <c r="K14" s="16">
         <f>IFERROR(H14/G14,"")</f>
@@ -17631,7 +17664,7 @@
       </c>
       <c r="L14" s="12" t="n"/>
       <c r="M14" s="17" t="n">
-        <v>46267</v>
+        <v>46295</v>
       </c>
       <c r="N14" s="5" t="inlineStr">
         <is>
@@ -17639,170 +17672,170 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Tier 2 — Additional comps: the next 5 communities matching the subject's product and vintage</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Lucera Apartments</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>2BR — lowest five of 6 available</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" s="12" t="n"/>
+      <c r="G15" s="7" t="n">
+        <v>892</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>1413</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>1413</v>
+      </c>
+      <c r="K15" s="16">
+        <f>IFERROR(H15/G15,"")</f>
+        <v/>
+      </c>
+      <c r="L15" s="12" t="n"/>
+      <c r="M15" s="17" t="n">
+        <v>46295</v>
+      </c>
+      <c r="N15" s="5" t="inlineStr">
+        <is>
+          <t>own weekly scrape</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Tier 2 — Additional comps: the next 8 communities matching the subject's product and vintage</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Community</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>Distance (mi)</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C18" s="14" t="inlineStr">
         <is>
           <t>Year built</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>Floor plan</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>Beds</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F18" s="14" t="inlineStr">
         <is>
           <t>Baths</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G18" s="14" t="inlineStr">
         <is>
           <t>SF</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr">
+      <c r="H18" s="14" t="inlineStr">
         <is>
           <t>Asking rent</t>
         </is>
       </c>
-      <c r="I17" s="14" t="inlineStr">
+      <c r="I18" s="14" t="inlineStr">
         <is>
           <t>Concession</t>
         </is>
       </c>
-      <c r="J17" s="14" t="inlineStr">
+      <c r="J18" s="14" t="inlineStr">
         <is>
           <t>Net effective rent</t>
         </is>
       </c>
-      <c r="K17" s="14" t="inlineStr">
+      <c r="K18" s="14" t="inlineStr">
         <is>
           <t>Asking $/SF</t>
         </is>
       </c>
-      <c r="L17" s="14" t="inlineStr">
+      <c r="L18" s="14" t="inlineStr">
         <is>
           <t>Occupancy</t>
         </is>
       </c>
-      <c r="M17" s="14" t="inlineStr">
+      <c r="M18" s="14" t="inlineStr">
         <is>
           <t>As-of date</t>
         </is>
       </c>
-      <c r="N17" s="14" t="inlineStr">
+      <c r="N18" s="14" t="inlineStr">
         <is>
           <t>Source</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Mesa Station</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>1984</v>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>1BR — group floor (lowest listing); the lowest-five measure was not provided</t>
-        </is>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="7" t="n">
-        <v>570</v>
-      </c>
-      <c r="H18" s="7" t="n">
-        <v>908</v>
-      </c>
-      <c r="I18" s="7" t="n">
-        <v>70</v>
-      </c>
-      <c r="J18" s="7" t="n">
-        <v>838</v>
-      </c>
-      <c r="K18" s="16">
-        <f>IFERROR(H18/G18,"")</f>
-        <v/>
-      </c>
-      <c r="L18" s="12" t="n"/>
-      <c r="M18" s="17" t="n">
-        <v>46267</v>
-      </c>
-      <c r="N18" s="5" t="inlineStr">
-        <is>
-          <t>own weekly scrape</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Mesa Station</t>
+          <t>Pebble Creek</t>
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="C19" s="8" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>2BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>1BR — lowest five of 1 available</t>
         </is>
       </c>
       <c r="E19" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="7" t="n">
-        <v>686</v>
+        <v>630</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>1000</v>
+        <v>1150</v>
       </c>
       <c r="I19" s="7" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="J19" s="7" t="n">
-        <v>923</v>
+        <v>1150</v>
       </c>
       <c r="K19" s="16">
         <f>IFERROR(H19/G19,"")</f>
@@ -17810,7 +17843,7 @@
       </c>
       <c r="L19" s="12" t="n"/>
       <c r="M19" s="17" t="n">
-        <v>46267</v>
+        <v>46295</v>
       </c>
       <c r="N19" s="5" t="inlineStr">
         <is>
@@ -17821,18 +17854,18 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Mesa Station</t>
+          <t>Pebble Creek</t>
         </is>
       </c>
       <c r="B20" s="10" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>2BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>2BR — lowest five of 1 available</t>
         </is>
       </c>
       <c r="E20" s="15" t="n">
@@ -17840,16 +17873,16 @@
       </c>
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="7" t="n">
-        <v>771</v>
+        <v>780</v>
       </c>
       <c r="H20" s="7" t="n">
-        <v>1186</v>
+        <v>1425</v>
       </c>
       <c r="I20" s="7" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="J20" s="7" t="n">
-        <v>1095</v>
+        <v>1425</v>
       </c>
       <c r="K20" s="16">
         <f>IFERROR(H20/G20,"")</f>
@@ -17857,7 +17890,7 @@
       </c>
       <c r="L20" s="12" t="n"/>
       <c r="M20" s="17" t="n">
-        <v>46267</v>
+        <v>46295</v>
       </c>
       <c r="N20" s="5" t="inlineStr">
         <is>
@@ -17868,18 +17901,18 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Dana Park Apartments</t>
+          <t>Gilbert Greens Apartments</t>
         </is>
       </c>
       <c r="B21" s="10" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="C21" s="8" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>1BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>1BR — lowest five of 5 available</t>
         </is>
       </c>
       <c r="E21" s="15" t="n">
@@ -17887,16 +17920,16 @@
       </c>
       <c r="F21" s="12" t="n"/>
       <c r="G21" s="7" t="n">
-        <v>722</v>
+        <v>605</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>1245</v>
+        <v>1230</v>
       </c>
       <c r="I21" s="7" t="n">
-        <v>239</v>
+        <v>94.3</v>
       </c>
       <c r="J21" s="7" t="n">
-        <v>1006</v>
+        <v>1135.7</v>
       </c>
       <c r="K21" s="16">
         <f>IFERROR(H21/G21,"")</f>
@@ -17904,7 +17937,7 @@
       </c>
       <c r="L21" s="12" t="n"/>
       <c r="M21" s="17" t="n">
-        <v>46268</v>
+        <v>46294</v>
       </c>
       <c r="N21" s="5" t="inlineStr">
         <is>
@@ -17915,18 +17948,18 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Dana Park Apartments</t>
+          <t>Gilbert Greens Apartments</t>
         </is>
       </c>
       <c r="B22" s="10" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="C22" s="8" t="n">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>2BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>2BR — lowest five of 1 available</t>
         </is>
       </c>
       <c r="E22" s="15" t="n">
@@ -17934,16 +17967,16 @@
       </c>
       <c r="F22" s="12" t="n"/>
       <c r="G22" s="7" t="n">
-        <v>1025</v>
+        <v>808</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>1499</v>
+        <v>1425</v>
       </c>
       <c r="I22" s="7" t="n">
-        <v>288</v>
+        <v>110</v>
       </c>
       <c r="J22" s="7" t="n">
-        <v>1211</v>
+        <v>1315</v>
       </c>
       <c r="K22" s="16">
         <f>IFERROR(H22/G22,"")</f>
@@ -17951,7 +17984,7 @@
       </c>
       <c r="L22" s="12" t="n"/>
       <c r="M22" s="17" t="n">
-        <v>46268</v>
+        <v>46294</v>
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
@@ -17962,35 +17995,35 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>Dana Park Apartments</t>
+          <t>Mesa Station</t>
         </is>
       </c>
       <c r="B23" s="10" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="C23" s="8" t="n">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>2BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>1BR — lowest five of 12 available</t>
         </is>
       </c>
       <c r="E23" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" s="12" t="n"/>
       <c r="G23" s="7" t="n">
-        <v>1067</v>
+        <v>570</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>1645</v>
+        <v>953.2</v>
       </c>
       <c r="I23" s="7" t="n">
-        <v>316</v>
+        <v>0</v>
       </c>
       <c r="J23" s="7" t="n">
-        <v>1329</v>
+        <v>953.2</v>
       </c>
       <c r="K23" s="16">
         <f>IFERROR(H23/G23,"")</f>
@@ -17998,7 +18031,7 @@
       </c>
       <c r="L23" s="12" t="n"/>
       <c r="M23" s="17" t="n">
-        <v>46268</v>
+        <v>46294</v>
       </c>
       <c r="N23" s="5" t="inlineStr">
         <is>
@@ -18009,35 +18042,35 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Astero Mesa East</t>
+          <t>Mesa Station</t>
         </is>
       </c>
       <c r="B24" s="10" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="C24" s="8" t="n">
-        <v>1987</v>
+        <v>1984</v>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>1BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>2BR — lowest five of 29 available</t>
         </is>
       </c>
       <c r="E24" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" s="12" t="n"/>
       <c r="G24" s="7" t="n">
-        <v>700</v>
+        <v>686</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>1249</v>
+        <v>990.2</v>
       </c>
       <c r="I24" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J24" s="7" t="n">
-        <v>1249</v>
+        <v>990.2</v>
       </c>
       <c r="K24" s="16">
         <f>IFERROR(H24/G24,"")</f>
@@ -18045,7 +18078,7 @@
       </c>
       <c r="L24" s="12" t="n"/>
       <c r="M24" s="17" t="n">
-        <v>46267</v>
+        <v>46294</v>
       </c>
       <c r="N24" s="5" t="inlineStr">
         <is>
@@ -18056,18 +18089,18 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Astero Mesa East</t>
+          <t>Mesa Station</t>
         </is>
       </c>
       <c r="B25" s="10" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="C25" s="8" t="n">
-        <v>1987</v>
+        <v>1984</v>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>2BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>2BR — lowest five of 8 available</t>
         </is>
       </c>
       <c r="E25" s="15" t="n">
@@ -18075,16 +18108,16 @@
       </c>
       <c r="F25" s="12" t="n"/>
       <c r="G25" s="7" t="n">
-        <v>900</v>
+        <v>771</v>
       </c>
       <c r="H25" s="7" t="n">
-        <v>1449</v>
+        <v>1130</v>
       </c>
       <c r="I25" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J25" s="7" t="n">
-        <v>1449</v>
+        <v>1130</v>
       </c>
       <c r="K25" s="16">
         <f>IFERROR(H25/G25,"")</f>
@@ -18092,7 +18125,7 @@
       </c>
       <c r="L25" s="12" t="n"/>
       <c r="M25" s="17" t="n">
-        <v>46267</v>
+        <v>46294</v>
       </c>
       <c r="N25" s="5" t="inlineStr">
         <is>
@@ -18103,35 +18136,35 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Astero Mesa East</t>
+          <t>Dana Park Apartments</t>
         </is>
       </c>
       <c r="B26" s="10" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="C26" s="8" t="n">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>2BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>1BR — lowest five of 1 available</t>
         </is>
       </c>
       <c r="E26" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" s="12" t="n"/>
       <c r="G26" s="7" t="n">
-        <v>1044</v>
+        <v>722</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>1499</v>
+        <v>1245</v>
       </c>
       <c r="I26" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J26" s="7" t="n">
-        <v>1499</v>
+        <v>1245</v>
       </c>
       <c r="K26" s="16">
         <f>IFERROR(H26/G26,"")</f>
@@ -18139,7 +18172,7 @@
       </c>
       <c r="L26" s="12" t="n"/>
       <c r="M26" s="17" t="n">
-        <v>46267</v>
+        <v>46295</v>
       </c>
       <c r="N26" s="5" t="inlineStr">
         <is>
@@ -18150,35 +18183,35 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>Astero Mesa West</t>
+          <t>Dana Park Apartments</t>
         </is>
       </c>
       <c r="B27" s="10" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="C27" s="8" t="n">
         <v>1986</v>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>1BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>2BR — lowest five of 1 available</t>
         </is>
       </c>
       <c r="E27" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="12" t="n"/>
       <c r="G27" s="7" t="n">
-        <v>576</v>
+        <v>1025</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>1049</v>
+        <v>1599</v>
       </c>
       <c r="I27" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="7" t="n">
-        <v>1049</v>
+        <v>1599</v>
       </c>
       <c r="K27" s="16">
         <f>IFERROR(H27/G27,"")</f>
@@ -18186,7 +18219,7 @@
       </c>
       <c r="L27" s="12" t="n"/>
       <c r="M27" s="17" t="n">
-        <v>46268</v>
+        <v>46295</v>
       </c>
       <c r="N27" s="5" t="inlineStr">
         <is>
@@ -18197,18 +18230,18 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Astero Mesa West</t>
+          <t>Dana Park Apartments</t>
         </is>
       </c>
       <c r="B28" s="10" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="C28" s="8" t="n">
         <v>1986</v>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>2BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>2BR — lowest five of 1 available</t>
         </is>
       </c>
       <c r="E28" s="15" t="n">
@@ -18216,16 +18249,16 @@
       </c>
       <c r="F28" s="12" t="n"/>
       <c r="G28" s="7" t="n">
-        <v>1035</v>
+        <v>1067</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>1349</v>
+        <v>1695</v>
       </c>
       <c r="I28" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J28" s="7" t="n">
-        <v>1349</v>
+        <v>1695</v>
       </c>
       <c r="K28" s="16">
         <f>IFERROR(H28/G28,"")</f>
@@ -18233,7 +18266,7 @@
       </c>
       <c r="L28" s="12" t="n"/>
       <c r="M28" s="17" t="n">
-        <v>46268</v>
+        <v>46295</v>
       </c>
       <c r="N28" s="5" t="inlineStr">
         <is>
@@ -18244,35 +18277,35 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>Gentrys Walk Apartments</t>
+          <t>Astero Mesa East</t>
         </is>
       </c>
       <c r="B29" s="10" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="C29" s="8" t="n">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>1BR — group floor (lowest listing); the lowest-five measure was not provided</t>
+          <t>2BR — lowest five of 1 available</t>
         </is>
       </c>
       <c r="E29" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" s="12" t="n"/>
       <c r="G29" s="7" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>1212</v>
+        <v>1399</v>
       </c>
       <c r="I29" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J29" s="7" t="n">
-        <v>1212</v>
+        <v>1399</v>
       </c>
       <c r="K29" s="16">
         <f>IFERROR(H29/G29,"")</f>
@@ -18280,7 +18313,7 @@
       </c>
       <c r="L29" s="12" t="n"/>
       <c r="M29" s="17" t="n">
-        <v>46268</v>
+        <v>46294</v>
       </c>
       <c r="N29" s="5" t="inlineStr">
         <is>
@@ -18288,358 +18321,1074 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Astero Mesa East</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C30" s="8" t="n">
+        <v>1987</v>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>2BR — lowest five of 1 available</t>
+        </is>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" s="12" t="n"/>
+      <c r="G30" s="7" t="n">
+        <v>1044</v>
+      </c>
+      <c r="H30" s="7" t="n">
+        <v>1449</v>
+      </c>
+      <c r="I30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="7" t="n">
+        <v>1449</v>
+      </c>
+      <c r="K30" s="16">
+        <f>IFERROR(H30/G30,"")</f>
+        <v/>
+      </c>
+      <c r="L30" s="12" t="n"/>
+      <c r="M30" s="17" t="n">
+        <v>46294</v>
+      </c>
+      <c r="N30" s="5" t="inlineStr">
+        <is>
+          <t>own weekly scrape</t>
+        </is>
+      </c>
+    </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>By bed count — like for like</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Astero Mesa West</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>1BR — lowest five of 1 available — STALE snapshot (older than the tracker's freshness threshold)</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="12" t="n"/>
+      <c r="G31" s="7" t="n">
+        <v>576</v>
+      </c>
+      <c r="H31" s="7" t="n">
+        <v>1049</v>
+      </c>
+      <c r="I31" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="7" t="n">
+        <v>1049</v>
+      </c>
+      <c r="K31" s="16">
+        <f>IFERROR(H31/G31,"")</f>
+        <v/>
+      </c>
+      <c r="L31" s="12" t="n"/>
+      <c r="M31" s="17" t="n">
+        <v>46281</v>
+      </c>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>own weekly scrape</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="14" t="inlineStr">
-        <is>
-          <t>Beds</t>
-        </is>
-      </c>
-      <c r="B32" s="14" t="inlineStr">
-        <is>
-          <t>Communities</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="inlineStr">
-        <is>
-          <t>Plans</t>
-        </is>
-      </c>
-      <c r="D32" s="14" t="inlineStr">
-        <is>
-          <t>Avg asking</t>
-        </is>
-      </c>
-      <c r="E32" s="14" t="inlineStr">
-        <is>
-          <t>Avg net effective</t>
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Gentrys Walk Apartments</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C32" s="8" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>1BR — lowest five of 6 available</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>1226.6</v>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="7" t="n">
+        <v>1226.6</v>
+      </c>
+      <c r="K32" s="16">
+        <f>IFERROR(H32/G32,"")</f>
+        <v/>
+      </c>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="17" t="n">
+        <v>46295</v>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>own weekly scrape</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>1 bed</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="C33" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="D33" s="7" t="n">
-        <v>1118.3</v>
-      </c>
-      <c r="E33" s="7" t="n">
-        <v>1068.7</v>
+          <t>Gentrys Walk Apartments</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>1BR — lowest five of 4 available</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="12" t="n"/>
+      <c r="G33" s="7" t="n">
+        <v>700</v>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>1344.5</v>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" s="7" t="n">
+        <v>1344.5</v>
+      </c>
+      <c r="K33" s="16">
+        <f>IFERROR(H33/G33,"")</f>
+        <v/>
+      </c>
+      <c r="L33" s="12" t="n"/>
+      <c r="M33" s="17" t="n">
+        <v>46295</v>
+      </c>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>own weekly scrape</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>2 bed</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="C34" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>1373.111111111111</v>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>1281.222222222222</v>
-      </c>
-    </row>
-    <row r="35"/>
+          <t>Gentrys Walk Apartments</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C34" s="8" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>2BR — lowest five of 8 available</t>
+        </is>
+      </c>
+      <c r="E34" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" s="12" t="n"/>
+      <c r="G34" s="7" t="n">
+        <v>920</v>
+      </c>
+      <c r="H34" s="7" t="n">
+        <v>1432.4</v>
+      </c>
+      <c r="I34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="7" t="n">
+        <v>1432.4</v>
+      </c>
+      <c r="K34" s="16">
+        <f>IFERROR(H34/G34,"")</f>
+        <v/>
+      </c>
+      <c r="L34" s="12" t="n"/>
+      <c r="M34" s="17" t="n">
+        <v>46295</v>
+      </c>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>own weekly scrape</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>The Orchard on Gilbert</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="C35" s="8" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>1BR — lowest five of 14 available</t>
+        </is>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="12" t="n"/>
+      <c r="G35" s="7" t="n">
+        <v>483</v>
+      </c>
+      <c r="H35" s="7" t="n">
+        <v>1209.4</v>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="J35" s="7" t="n">
+        <v>1116.6</v>
+      </c>
+      <c r="K35" s="16">
+        <f>IFERROR(H35/G35,"")</f>
+        <v/>
+      </c>
+      <c r="L35" s="12" t="n"/>
+      <c r="M35" s="17" t="n">
+        <v>46295</v>
+      </c>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>own weekly scrape</t>
+        </is>
+      </c>
+    </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>Subject versus comp set — detailed tiers only</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>Subject market rent</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="n">
-        <v>1344.6</v>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>Unit-weighted market rent for model, whole property.</t>
-        </is>
-      </c>
-    </row>
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>The Orchard on Gilbert</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="C36" s="8" t="n">
+        <v>1986</v>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>2BR — lowest five of 3 available</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" s="12" t="n"/>
+      <c r="G36" s="7" t="n">
+        <v>865</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>1585</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>121.84</v>
+      </c>
+      <c r="J36" s="7" t="n">
+        <v>1463.16</v>
+      </c>
+      <c r="K36" s="16">
+        <f>IFERROR(H36/G36,"")</f>
+        <v/>
+      </c>
+      <c r="L36" s="12" t="n"/>
+      <c r="M36" s="17" t="n">
+        <v>46295</v>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>own weekly scrape</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>Comp-set average asking</t>
-        </is>
-      </c>
-      <c r="B38" s="7">
-        <f>IFERROR(AVERAGE(H8:H14,H18:H29),"")</f>
-        <v/>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>Over 10 communities in the detailed tiers (top 5 plus next 15) — never the whole radius.</t>
-        </is>
-      </c>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Unit count and year built, by community — each with its source</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>Comp-set average net effective</t>
-        </is>
-      </c>
-      <c r="B39" s="7">
-        <f>IFERROR(AVERAGE(J8:J14,J18:J29),"")</f>
-        <v/>
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>Community</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="C39" s="14" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="D39" s="14" t="inlineStr">
+        <is>
+          <t>Units from</t>
+        </is>
+      </c>
+      <c r="E39" s="14" t="inlineStr">
+        <is>
+          <t>Year built</t>
+        </is>
+      </c>
+      <c r="F39" s="14" t="inlineStr">
+        <is>
+          <t>Year built from</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Comp set, mix-matched</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="n">
-        <v>1172.943495077356</v>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Each bed count's comp net-effective weighted by the subject's own unit mix, so both sides describe the same product.</t>
+          <t>Saltera Apartments</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>306</v>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>1984</v>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>Subject rent, same bed counts</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="n">
-        <v>1314.301989343287</v>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Restricted to the bed counts the comp set covers: [1, 2].</t>
+          <t>The Hamptons</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>249</v>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>1981</v>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Mix coverage</t>
-        </is>
-      </c>
-      <c r="B42" s="11" t="n">
-        <v>0.9461077844311377</v>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>Share of the subject's units actually compared, by bed count and priced plan.</t>
+          <t>Cielo on Gilbert</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>432</v>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>1985</v>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Subject vs comp set (mix-matched)</t>
-        </is>
-      </c>
-      <c r="B43" s="11">
-        <f>IFERROR(B41/B40-1,"")</f>
-        <v/>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>Negative means the subject is underwritten BELOW the market — mark-to-market room rather than a stretch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44"/>
+          <t>The Vance</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="7" t="n">
+        <v>464</v>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>1986</v>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Lucera Apartments</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>192</v>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>1986</v>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
+    </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>Two comp sets, selected identically except for the vintage test</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="n"/>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="n"/>
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Pebble Creek</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>122</v>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>1985</v>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>Held fixed in both: candidate pool, product test, tracker comp exclusions, radius, closest-20 cap, per-community rent rules, mix weighting. Varied: the +/-10-year vintage test only.</t>
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Gilbert Greens Apartments</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>164</v>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>1985</v>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="14" t="inlineStr">
-        <is>
-          <t>Comp set</t>
-        </is>
-      </c>
-      <c r="B47" s="14" t="inlineStr">
-        <is>
-          <t>Communities</t>
-        </is>
-      </c>
-      <c r="C47" s="14" t="inlineStr">
-        <is>
-          <t>Vintages</t>
-        </is>
-      </c>
-      <c r="D47" s="14" t="inlineStr">
-        <is>
-          <t>Comp net effective</t>
-        </is>
-      </c>
-      <c r="E47" s="14" t="inlineStr">
-        <is>
-          <t>Subject reads</t>
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Mesa Station</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>397</v>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>1984</v>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>A — vintage test ON</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>1981–1987</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="n">
-        <v>1172.943495077356</v>
-      </c>
-      <c r="E48" s="11" t="n">
-        <v>0.1205160307032596</v>
+          <t>Dana Park Apartments</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>222</v>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>1986</v>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>B — vintage test OFF</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="n">
-        <v>13</v>
+          <t>Astero Mesa East</t>
+        </is>
+      </c>
+      <c r="B49" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>1981–2018</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="n">
-        <v>1217.446518987342</v>
-      </c>
-      <c r="E49" s="11" t="n">
-        <v>0.07955624238550407</v>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>No public record; the licensed count is held back</t>
+        </is>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>1987</v>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>community registry (third-party market data)</t>
+        </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="inlineStr">
-        <is>
-          <t>Difference between the two sets</t>
-        </is>
-      </c>
-      <c r="B50" s="19" t="n"/>
-      <c r="C50" s="19" t="n"/>
-      <c r="D50" s="20" t="n">
-        <v>44.50302390998604</v>
-      </c>
-      <c r="E50" s="21" t="n">
-        <v>0.04095978831775549</v>
-      </c>
-    </row>
-    <row r="51"/>
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>Astero Mesa West</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>No public record; the licensed count is held back</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>1986</v>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>community registry (third-party market data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>Gentrys Walk Apartments</t>
+        </is>
+      </c>
+      <c r="B51" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" s="7" t="n">
+        <v>176</v>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>1986</v>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
+    </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
+          <t>The Orchard on Gilbert</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C52" s="7" t="n">
+        <v>130</v>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>1986</v>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="53"/>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>By bed count — like for like</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n"/>
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="n"/>
+      <c r="E54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="14" t="inlineStr">
+        <is>
+          <t>Beds</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>Communities</t>
+        </is>
+      </c>
+      <c r="C55" s="14" t="inlineStr">
+        <is>
+          <t>Plans</t>
+        </is>
+      </c>
+      <c r="D55" s="14" t="inlineStr">
+        <is>
+          <t>Avg asking</t>
+        </is>
+      </c>
+      <c r="E55" s="14" t="inlineStr">
+        <is>
+          <t>Avg net effective</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>1 bed</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>1160.167857142857</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>1140.007857142857</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>2 bed</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>1394.05</v>
+      </c>
+      <c r="E57" s="7" t="n">
+        <v>1374.73</v>
+      </c>
+    </row>
+    <row r="58"/>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>Subject versus comp set — detailed tiers only</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="n"/>
+      <c r="C59" s="4" t="n"/>
+      <c r="D59" s="4" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>Subject market rent</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="n">
+        <v>1344.6</v>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>Unit-weighted market rent for model, whole property.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>Comp-set average asking</t>
+        </is>
+      </c>
+      <c r="B61" s="7">
+        <f>IFERROR(AVERAGE(H8:H15,H19:H36),"")</f>
+        <v/>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>Over 13 communities in the detailed tiers (top 5 plus next 15) — never the whole radius.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>Comp-set average net effective</t>
+        </is>
+      </c>
+      <c r="B62" s="7">
+        <f>IFERROR(AVERAGE(J8:J15,J19:J36),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>Comp set, mix-matched</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="n">
+        <v>1255.140553797469</v>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>Each bed count's comp net-effective weighted by the subject's own unit mix, so both sides describe the same product.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>Subject rent, same bed counts</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="n">
+        <v>1314.301989343287</v>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>Restricted to the bed counts the comp set covers: [1, 2].</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>Mix coverage</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="n">
+        <v>0.9461077844311377</v>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>Share of the subject's units actually compared, by bed count and priced plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Subject vs comp set (mix-matched)</t>
+        </is>
+      </c>
+      <c r="B66" s="11">
+        <f>IFERROR(B64/B63-1,"")</f>
+        <v/>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>Negative means the subject is underwritten BELOW the market — mark-to-market room rather than a stretch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67"/>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>Two comp sets, selected identically except for the vintage test</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="n"/>
+      <c r="C68" s="4" t="n"/>
+      <c r="D68" s="4" t="n"/>
+      <c r="E68" s="4" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>Held fixed in both: candidate pool, product test, tracker comp exclusions, radius, closest-20 cap, per-community rent rules, mix weighting. Varied: the +/-10-year vintage test only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="14" t="inlineStr">
+        <is>
+          <t>Comp set</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>Communities</t>
+        </is>
+      </c>
+      <c r="C70" s="14" t="inlineStr">
+        <is>
+          <t>Vintages</t>
+        </is>
+      </c>
+      <c r="D70" s="14" t="inlineStr">
+        <is>
+          <t>Comp net effective</t>
+        </is>
+      </c>
+      <c r="E70" s="14" t="inlineStr">
+        <is>
+          <t>Subject reads</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>A — vintage test ON</t>
+        </is>
+      </c>
+      <c r="B71" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>1981–1987</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="n">
+        <v>1255.140553797469</v>
+      </c>
+      <c r="E71" s="11" t="n">
+        <v>0.04713530717083714</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="5" t="inlineStr">
+        <is>
+          <t>B — vintage test OFF</t>
+        </is>
+      </c>
+      <c r="B72" s="7" t="n">
+        <v>17</v>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>1981–2018</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>1303.423449367089</v>
+      </c>
+      <c r="E72" s="11" t="n">
+        <v>0.008346128789903817</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="18" t="inlineStr">
+        <is>
+          <t>Difference between the two sets</t>
+        </is>
+      </c>
+      <c r="B73" s="19" t="n"/>
+      <c r="C73" s="19" t="n"/>
+      <c r="D73" s="20" t="n">
+        <v>48.28289556962</v>
+      </c>
+      <c r="E73" s="21" t="n">
+        <v>0.03878917838093332</v>
+      </c>
+    </row>
+    <row r="74"/>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
           <t>In B but not A</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>Lindsay Palms Apartments, The Premiere at Dana Park, Vista Grove</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>Craft at Gilbert and Baseline, The Premiere at Dana Park, The Village at Lindsay Park Apartments, Vista Grove</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
         <is>
           <t>In A but not B</t>
         </is>
       </c>
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="6" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
         <is>
           <t>Both figures are weighted by this property's own unit mix and computed over the same bed counts, so the two rows describe the same product. This is what these two sets measured on this date; it is not an estimate of what vintage is worth in this market.</t>
         </is>
       </c>
     </row>
-    <row r="55"/>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+    <row r="78"/>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>Stated in the offering memorandum</t>
         </is>
       </c>
-      <c r="B56" s="4" t="n"/>
-      <c r="C56" s="4" t="n"/>
-      <c r="D56" s="4" t="n"/>
-      <c r="E56" s="4" t="n"/>
-      <c r="F56" s="4" t="n"/>
-      <c r="G56" s="4" t="n"/>
-      <c r="H56" s="4" t="n"/>
-      <c r="I56" s="4" t="n"/>
-      <c r="J56" s="4" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+      <c r="B79" s="4" t="n"/>
+      <c r="C79" s="4" t="n"/>
+      <c r="D79" s="4" t="n"/>
+      <c r="E79" s="4" t="n"/>
+      <c r="F79" s="4" t="n"/>
+      <c r="G79" s="4" t="n"/>
+      <c r="H79" s="4" t="n"/>
+      <c r="I79" s="4" t="n"/>
+      <c r="J79" s="4" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>The memorandum's stated comparables are withheld: they would place the real asset.</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>Retail for-sale comps are not part of this demo. Sale comparables shown here are the whole-community trades the memorandum itself cites.</t>
         </is>
@@ -19144,7 +19893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L58"/>
+  <dimension ref="A1:L59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -19288,7 +20037,7 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" s="7" t="n">
         <v>558</v>
@@ -19324,7 +20073,7 @@
         </is>
       </c>
       <c r="C13" s="7" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D13" s="7" t="n">
         <v>3355</v>
@@ -19342,10 +20091,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>38442</v>
+        <v>39029</v>
       </c>
     </row>
     <row r="15">
@@ -19360,10 +20109,10 @@
         </is>
       </c>
       <c r="C15" s="7" t="n">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>15187</v>
+        <v>16643</v>
       </c>
     </row>
     <row r="16"/>
@@ -19620,7 +20369,7 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>539 S WILLIAMS</t>
+          <t>Williams Place</t>
         </is>
       </c>
       <c r="B28" s="10" t="n">
@@ -19740,7 +20489,7 @@
         </is>
       </c>
       <c r="B30" s="10" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
@@ -19966,93 +20715,97 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>La Jolla Villas</t>
+          <t>The Bungalows on Ash</t>
         </is>
       </c>
       <c r="B34" s="10" t="n">
-        <v>1.59</v>
+        <v>1.34</v>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
-        </is>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>15</v>
+          <t>Permitted</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>multifamily</t>
+          <t>other_mf</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
+          <t>1381 N GILBERT RD</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>GILBERT</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H34" s="10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2020-06-25</t>
         </is>
       </c>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2021-06-16</t>
         </is>
       </c>
       <c r="L34" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>County permits</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>1424 E DANA AVE</t>
+          <t>La Jolla Villas</t>
         </is>
       </c>
       <c r="B35" s="10" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>Permitted</t>
+          <t>Entitlement</t>
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>apartment_rental</t>
+          <t>multifamily</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>1424 E DANA AVE</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H35" s="10" t="n">
-        <v>0.076</v>
+        <v>1.07</v>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
@@ -20061,115 +20814,111 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L35" s="5" t="inlineStr">
         <is>
-          <t>County permits</t>
+          <t>Entitlement</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Dana Park Village Square</t>
+          <t>1424 E DANA AVE</t>
         </is>
       </c>
       <c r="B36" s="10" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>Permitted</t>
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>multifamily</t>
+          <t>apartment_rental</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
+          <t>1424 E DANA AVE</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="H36" s="10" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G36" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H36" s="10" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="K36" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="L36" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>County permits</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>214 N GILBERT RD 111</t>
+          <t>Dana Park Village Square</t>
         </is>
       </c>
       <c r="B37" s="10" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>Permitted</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
+          <t>Entitlement</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>multifamily</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>apartment_rental</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>214 N GILBERT RD 111</t>
-        </is>
-      </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Mesa</t>
-        </is>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
           <t>—</t>
         </is>
       </c>
+      <c r="H37" s="10" t="n">
+        <v>4.25</v>
+      </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
           <t>—</t>
@@ -20177,17 +20926,17 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>2023-02-23</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="K37" s="5" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L37" s="5" t="inlineStr">
         <is>
-          <t>County permits</t>
+          <t>Entitlement</t>
         </is>
       </c>
     </row>
@@ -20250,98 +20999,98 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>Tangerine</t>
+          <t>214 N GILBERT RD 111</t>
         </is>
       </c>
       <c r="B39" s="10" t="n">
-        <v>2.09</v>
+        <v>1.8</v>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
-        </is>
-      </c>
-      <c r="D39" s="7" t="n">
-        <v>29</v>
+          <t>Permitted</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>multifamily</t>
+          <t>apartment_rental</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
+          <t>214 N GILBERT RD 111</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G39" s="5" t="inlineStr">
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H39" s="10" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="I39" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2023-02-23</t>
         </is>
       </c>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2023-03-01</t>
         </is>
       </c>
       <c r="L39" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>County permits</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>3020 E MAIN ST</t>
+          <t>Tangerine</t>
         </is>
       </c>
       <c r="B40" s="10" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>Permitted</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
+          <t>Entitlement</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>multifamily</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>apartment_rental</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>3020 E MAIN ST</t>
-        </is>
-      </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Mesa</t>
-        </is>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
           <t>—</t>
         </is>
       </c>
+      <c r="H40" s="10" t="n">
+        <v>2.06</v>
+      </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
           <t>—</t>
@@ -20349,32 +21098,32 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>2023-07-27</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="K40" s="5" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L40" s="5" t="inlineStr">
         <is>
-          <t>County permits</t>
+          <t>Entitlement</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>La Mesa Village Apartments</t>
+          <t>3020 E MAIN ST</t>
         </is>
       </c>
       <c r="B41" s="10" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>Permitted</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -20384,57 +21133,57 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>multifamily</t>
+          <t>apartment_rental</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
+          <t>3020 E MAIN ST</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>MESA</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr">
+      <c r="I41" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>2024-10-29</t>
+          <t>2023-07-27</t>
         </is>
       </c>
       <c r="K41" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="L41" s="5" t="inlineStr">
         <is>
-          <t>NOI radar (Arizona DEQ)</t>
+          <t>County permits</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>505 S LESUEUR C</t>
+          <t>La Mesa Village Apartments</t>
         </is>
       </c>
       <c r="B42" s="10" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>Permitted</t>
+          <t>Entitlement</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -20444,17 +21193,17 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>apartment_rental</t>
+          <t>multifamily</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>505 S LESUEUR C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>MESA</t>
         </is>
       </c>
       <c r="H42" s="5" t="inlineStr">
@@ -20469,84 +21218,88 @@
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>2020-07-01</t>
+          <t>2024-10-29</t>
         </is>
       </c>
       <c r="K42" s="5" t="inlineStr">
         <is>
-          <t>2020-07-23</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L42" s="5" t="inlineStr">
         <is>
-          <t>County permits</t>
+          <t>NOI radar (Arizona DEQ)</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>Pioneer Place</t>
+          <t>505 S LESUEUR C</t>
         </is>
       </c>
       <c r="B43" s="10" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="n">
-        <v>9</v>
+          <t>Permitted</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>apartment_rental</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
+          <t>505 S LESUEUR C</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="I43" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H43" s="10" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2020-07-01</t>
         </is>
       </c>
       <c r="K43" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2020-07-23</t>
         </is>
       </c>
       <c r="L43" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>County permits</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>PS16-006 A New Leaf Apartment Bldg</t>
+          <t>Pioneer Place</t>
         </is>
       </c>
       <c r="B44" s="10" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
@@ -20554,11 +21307,11 @@
         </is>
       </c>
       <c r="D44" s="7" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>multifamily</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
@@ -20572,7 +21325,7 @@
         </is>
       </c>
       <c r="H44" s="10" t="n">
-        <v>1.74</v>
+        <v>0.83</v>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
@@ -20598,40 +21351,38 @@
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>3426 E UNIVERSITY DR</t>
+          <t>PS16-006 A New Leaf Apartment Bldg</t>
         </is>
       </c>
       <c r="B45" s="10" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Permitted</t>
+          <t>Entitlement</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>apartment_rental</t>
+          <t>multifamily</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>3426 E UNIVERSITY DR</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Mesa</t>
-        </is>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
           <t>—</t>
         </is>
       </c>
+      <c r="H45" s="10" t="n">
+        <v>1.74</v>
+      </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
           <t>—</t>
@@ -20639,72 +21390,70 @@
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>2021-02-15</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L45" s="5" t="inlineStr">
         <is>
-          <t>County permits</t>
+          <t>Entitlement</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>455 E MAIN ST</t>
+          <t>3426 E UNIVERSITY DR</t>
         </is>
       </c>
       <c r="B46" s="10" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
           <t>Permitted</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
+      <c r="D46" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>apartment_rental</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>3426 E UNIVERSITY DR</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>apartment_rental</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>455 E MAIN ST</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>Mesa</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="inlineStr">
+      <c r="I46" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>2019-03-07</t>
+          <t>2021-02-15</t>
         </is>
       </c>
       <c r="K46" s="5" t="inlineStr">
         <is>
-          <t>2020-12-08</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="L46" s="5" t="inlineStr">
@@ -20716,75 +21465,81 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>Van Damme Residence</t>
+          <t>455 E MAIN ST</t>
         </is>
       </c>
       <c r="B47" s="10" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="n">
-        <v>2</v>
+          <t>Permitted</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>multifamily</t>
+          <t>apartment_rental</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
+          <t>455 E MAIN ST</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G47" s="5" t="inlineStr">
+      <c r="I47" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H47" s="10" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2019-03-07</t>
         </is>
       </c>
       <c r="K47" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2020-12-08</t>
         </is>
       </c>
       <c r="L47" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>County permits</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>LEGACY SQUARE</t>
+          <t>ASPIRE HERITAGE</t>
         </is>
       </c>
       <c r="B48" s="10" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>Permitted</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="n">
-        <v>110</v>
+          <t>Entitlement</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
         <is>
@@ -20793,12 +21548,12 @@
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>140 S POMEROY</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>MESA</t>
+          <t>GILBERT</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
@@ -20808,33 +21563,33 @@
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Willow Bridge Property Company</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>2025-02-06</t>
+          <t>2019-04-24</t>
         </is>
       </c>
       <c r="K48" s="5" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L48" s="5" t="inlineStr">
         <is>
-          <t>County permits, NOI radar (Arizona DEQ)</t>
+          <t>NOI radar (Arizona DEQ)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
         <is>
-          <t>Cadillac Aparments</t>
+          <t>Van Damme Residence</t>
         </is>
       </c>
       <c r="B49" s="10" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
@@ -20842,7 +21597,7 @@
         </is>
       </c>
       <c r="D49" s="7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
@@ -20860,7 +21615,7 @@
         </is>
       </c>
       <c r="H49" s="10" t="n">
-        <v>0.85</v>
+        <v>0.16</v>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
@@ -20886,115 +21641,109 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Clare House Social</t>
+          <t>LEGACY SQUARE</t>
         </is>
       </c>
       <c r="B50" s="10" t="n">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
+          <t>Permitted</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>110</v>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>multifamily</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>140 S POMEROY</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>MESA</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>mixed</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G50" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Willow Bridge Property Company</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="L50" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>County permits, NOI radar (Arizona DEQ)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>The Lumberyard</t>
+          <t>Cadillac Aparments</t>
         </is>
       </c>
       <c r="B51" s="10" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
           <t>Entitlement</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
+      <c r="D51" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>multifamily</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>multifamily</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
+      <c r="G51" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="H51" s="10" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I51" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L51" s="5" t="inlineStr">
@@ -21006,11 +21755,11 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>The Brundrett Building</t>
+          <t>Clare House Social</t>
         </is>
       </c>
       <c r="B52" s="10" t="n">
-        <v>2.72</v>
+        <v>2.65</v>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
@@ -21049,7 +21798,7 @@
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="K52" s="5" t="inlineStr">
@@ -21066,15 +21815,15 @@
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>233 E MAIN ST</t>
+          <t>The Brundrett Building</t>
         </is>
       </c>
       <c r="B53" s="10" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>Permitted</t>
+          <t>Entitlement</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
@@ -21084,17 +21833,17 @@
       </c>
       <c r="E53" s="5" t="inlineStr">
         <is>
-          <t>apartment_rental</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>233 E MAIN ST</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Mesa</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H53" s="5" t="inlineStr">
@@ -21109,84 +21858,88 @@
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>2020-01-27</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="K53" s="5" t="inlineStr">
         <is>
-          <t>2022-02-16</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L53" s="5" t="inlineStr">
         <is>
-          <t>County permits</t>
+          <t>Entitlement</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>NEC Neely St and Aviary Way</t>
+          <t>233 E MAIN ST</t>
         </is>
       </c>
       <c r="B54" s="10" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="n">
-        <v>99</v>
+          <t>Permitted</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>multifamily</t>
+          <t>apartment_rental</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
+          <t>233 E MAIN ST</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr">
+      <c r="I54" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H54" s="10" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2020-01-27</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2022-02-16</t>
         </is>
       </c>
       <c r="L54" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>County permits</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Mesa Main Street Apartments</t>
+          <t>NEC Neely St and Aviary Way</t>
         </is>
       </c>
       <c r="B55" s="10" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
@@ -21194,7 +21947,7 @@
         </is>
       </c>
       <c r="D55" s="7" t="n">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
@@ -21212,7 +21965,7 @@
         </is>
       </c>
       <c r="H55" s="10" t="n">
-        <v>4.33</v>
+        <v>11.75</v>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
@@ -21238,40 +21991,38 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>145 E MAIN ST 1</t>
+          <t>Mesa Main Street Apartments</t>
         </is>
       </c>
       <c r="B56" s="10" t="n">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>Permitted</t>
+          <t>Entitlement</t>
         </is>
       </c>
       <c r="D56" s="7" t="n">
-        <v>335</v>
+        <v>36</v>
       </c>
       <c r="E56" s="5" t="inlineStr">
         <is>
-          <t>apartment_rental</t>
+          <t>multifamily</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>145 E MAIN ST 1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>Mesa</t>
-        </is>
-      </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
           <t>—</t>
         </is>
       </c>
+      <c r="H56" s="10" t="n">
+        <v>4.33</v>
+      </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
           <t>—</t>
@@ -21279,127 +22030,185 @@
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>2021-04-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="K56" s="5" t="inlineStr">
         <is>
-          <t>2021-12-06</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="L56" s="5" t="inlineStr">
         <is>
-          <t>County permits</t>
+          <t>Entitlement</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>Fiesta Rose Garden</t>
+          <t>145 E MAIN ST 1</t>
         </is>
       </c>
       <c r="B57" s="10" t="n">
-        <v>2.93</v>
+        <v>2.89</v>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>Permitted</t>
         </is>
       </c>
       <c r="D57" s="7" t="n">
-        <v>12</v>
+        <v>335</v>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>multifamily</t>
+          <t>apartment_rental</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
+          <t>145 E MAIN ST 1</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>Mesa</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G57" s="5" t="inlineStr">
+      <c r="I57" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H57" s="10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="I57" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2021-04-01</t>
         </is>
       </c>
       <c r="K57" s="5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2021-12-06</t>
         </is>
       </c>
       <c r="L57" s="5" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>County permits</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
+          <t>Fiesta Rose Garden</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>Entitlement</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>multifamily</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H58" s="10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="L58" s="5" t="inlineStr">
+        <is>
+          <t>Entitlement</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
           <t>NWC Gilbert Rd and Elliot Rd</t>
         </is>
       </c>
-      <c r="B58" s="10" t="n">
+      <c r="B59" s="10" t="n">
         <v>2.99</v>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>Entitlement</t>
         </is>
       </c>
-      <c r="D58" s="7" t="n">
+      <c r="D59" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="E58" s="5" t="inlineStr">
+      <c r="E59" s="5" t="inlineStr">
         <is>
           <t>mixed</t>
         </is>
       </c>
-      <c r="F58" s="5" t="inlineStr">
+      <c r="F59" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G58" s="5" t="inlineStr">
+      <c r="G59" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H58" s="10" t="n">
+      <c r="H59" s="10" t="n">
         <v>2.19</v>
       </c>
-      <c r="I58" s="5" t="inlineStr">
+      <c r="I59" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J58" s="5" t="inlineStr">
+      <c r="J59" s="5" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="K58" s="5" t="inlineStr">
+      <c r="K59" s="5" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="L58" s="5" t="inlineStr">
+      <c r="L59" s="5" t="inlineStr">
         <is>
           <t>Entitlement</t>
         </is>

--- a/public/downloads/underwriting-demo/sample-underwriting-pack.xlsx
+++ b/public/downloads/underwriting-demo/sample-underwriting-pack.xlsx
@@ -3530,7 +3530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H239"/>
+  <dimension ref="A1:H240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="D162" s="26" t="inlineStr">
         <is>
-          <t>Unit-weighted in-place rent across the property.</t>
+          <t>Mean contract rent over the occupied units with a stated contract rent (vacant units carry no in-place rent; an occupied unit with no stated rent is left out, not counted as zero).</t>
         </is>
       </c>
       <c r="E162" s="5" t="inlineStr">
@@ -10105,32 +10105,32 @@
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>cohort_gross_change_pct</t>
+          <t>cohort_prior_rent_effective</t>
         </is>
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D175" s="26" t="inlineStr">
         <is>
-          <t>Gross change over prior rent.</t>
+          <t>Average prior rent after the prior lease's concession. Optional: absent when the report states no prior concession, and the prior gross stands in.</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Lease trade-out report</t>
         </is>
       </c>
       <c r="F175" s="26" t="inlineStr">
         <is>
-          <t>Rent growth evidence</t>
+          <t>Prior effective rent</t>
         </is>
       </c>
       <c r="G175" s="26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
         </is>
       </c>
       <c r="H175" s="26" t="inlineStr">
@@ -10147,7 +10147,7 @@
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>cohort_effective_change_pct</t>
+          <t>cohort_gross_change_pct</t>
         </is>
       </c>
       <c r="C176" s="5" t="inlineStr">
@@ -10157,7 +10157,7 @@
       </c>
       <c r="D176" s="26" t="inlineStr">
         <is>
-          <t>Effective change over prior rent.</t>
+          <t>Gross change over prior rent.</t>
         </is>
       </c>
       <c r="E176" s="5" t="inlineStr">
@@ -10172,7 +10172,7 @@
       </c>
       <c r="G176" s="26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
         </is>
       </c>
       <c r="H176" s="26" t="inlineStr">
@@ -10189,95 +10189,95 @@
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
+          <t>cohort_effective_change_pct</t>
+        </is>
+      </c>
+      <c r="C177" s="5" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D177" s="26" t="inlineStr">
+        <is>
+          <t>Effective change over prior effective rent (the prior gross when no prior concession is stated).</t>
+        </is>
+      </c>
+      <c r="E177" s="5" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F177" s="26" t="inlineStr">
+        <is>
+          <t>Rent growth evidence</t>
+        </is>
+      </c>
+      <c r="G177" s="26" t="inlineStr">
+        <is>
+          <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
+        </is>
+      </c>
+      <c r="H177" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="5" t="inlineStr">
+        <is>
+          <t>Trade-out</t>
+        </is>
+      </c>
+      <c r="B178" s="5" t="inlineStr">
+        <is>
           <t>absent_reason</t>
         </is>
       </c>
-      <c r="C177" s="5" t="inlineStr">
+      <c r="C178" s="5" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="D177" s="26" t="inlineStr">
+      <c r="D178" s="26" t="inlineStr">
         <is>
           <t>Why the block is empty, when no trade-out report exists. An empty block that says why is a deliverable; a block of plausible numbers is not.</t>
         </is>
       </c>
-      <c r="E177" s="5" t="inlineStr">
+      <c r="E178" s="5" t="inlineStr">
         <is>
           <t>Derived by the pipeline</t>
         </is>
       </c>
-      <c r="F177" s="26" t="inlineStr">
+      <c r="F178" s="26" t="inlineStr">
         <is>
           <t>Reference only — not a model input</t>
         </is>
       </c>
-      <c r="G177" s="26" t="inlineStr">
+      <c r="G178" s="26" t="inlineStr">
         <is>
           <t>Internal pipeline only — The internal pipeline reads a lease trade-out report (new versus renewal rents); the demo does not ask for one.</t>
         </is>
       </c>
-      <c r="H177" s="26" t="inlineStr">
+      <c r="H178" s="26" t="inlineStr">
         <is>
           <t>Lease trade-out is an internal-pipeline input: the demo does not ask for a trade-out report, on the sample or on an upload.</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="4" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="4" t="inlineStr">
         <is>
           <t>Comps</t>
         </is>
       </c>
-      <c r="B178" s="4" t="n"/>
-      <c r="C178" s="4" t="n"/>
-      <c r="D178" s="4" t="n"/>
-      <c r="E178" s="4" t="n"/>
-      <c r="F178" s="4" t="n"/>
-      <c r="G178" s="4" t="n"/>
-      <c r="H178" s="4" t="n"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="5" t="inlineStr">
-        <is>
-          <t>Comps</t>
-        </is>
-      </c>
-      <c r="B179" s="5" t="inlineStr">
-        <is>
-          <t>comp_community</t>
-        </is>
-      </c>
-      <c r="C179" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D179" s="26" t="inlineStr">
-        <is>
-          <t>Comparable community name.</t>
-        </is>
-      </c>
-      <c r="E179" s="5" t="inlineStr">
-        <is>
-          <t>Operator's own weekly rent scrape</t>
-        </is>
-      </c>
-      <c r="F179" s="26" t="inlineStr">
-        <is>
-          <t>Comp set</t>
-        </is>
-      </c>
-      <c r="G179" s="26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H179" s="26" t="inlineStr">
-        <is>
-          <t>Saltera Apartments</t>
-        </is>
-      </c>
+      <c r="B179" s="4" t="n"/>
+      <c r="C179" s="4" t="n"/>
+      <c r="D179" s="4" t="n"/>
+      <c r="E179" s="4" t="n"/>
+      <c r="F179" s="4" t="n"/>
+      <c r="G179" s="4" t="n"/>
+      <c r="H179" s="4" t="n"/>
     </row>
     <row r="180">
       <c r="A180" s="5" t="inlineStr">
@@ -10287,22 +10287,22 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>comp_distance_mi</t>
+          <t>comp_community</t>
         </is>
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D180" s="26" t="inlineStr">
         <is>
-          <t>Straight-line distance from the subject.</t>
+          <t>Comparable community name.</t>
         </is>
       </c>
       <c r="E180" s="5" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F180" s="26" t="inlineStr">
@@ -10317,7 +10317,7 @@
       </c>
       <c r="H180" s="26" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>Saltera Apartments</t>
         </is>
       </c>
     </row>
@@ -10329,22 +10329,22 @@
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>comp_floor_plan</t>
+          <t>comp_distance_mi</t>
         </is>
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D181" s="26" t="inlineStr">
         <is>
-          <t>Comp floor plan the row describes. Comps are stated per plan, not as one blended community number.</t>
+          <t>Straight-line distance from the subject.</t>
         </is>
       </c>
       <c r="E181" s="5" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F181" s="26" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="H181" s="26" t="inlineStr">
         <is>
-          <t>1BR — lowest five of 5 available</t>
+          <t>0.1</t>
         </is>
       </c>
     </row>
@@ -10371,22 +10371,22 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>comp_tier</t>
+          <t>comp_floor_plan</t>
         </is>
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D182" s="26" t="inlineStr">
         <is>
-          <t>1 = top comps (the closest five matching the subject's product and vintage), 2 = additional comps (the next fifteen). The identity-only third group carries no rent; since 2026-09-28 it is carried in the interchange file only and is not shown as a table.</t>
+          <t>Comp floor plan the row describes. Comps are stated per plan, not as one blended community number.</t>
         </is>
       </c>
       <c r="E182" s="5" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F182" s="26" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="H182" s="26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>1BR — lowest five of 5 available</t>
         </is>
       </c>
     </row>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>comp_year_built</t>
+          <t>comp_tier</t>
         </is>
       </c>
       <c r="C183" s="5" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="D183" s="26" t="inlineStr">
         <is>
-          <t>Comp vintage where one is published: the public property record's year where it has one, else the community registry's. Blank means nobody published one, never that the community is new.</t>
+          <t>1 = top comps (the closest five matching the subject's product and vintage), 2 = additional comps (the next fifteen). The identity-only third group carries no rent; since 2026-09-28 it is carried in the interchange file only and is not shown as a table.</t>
         </is>
       </c>
       <c r="E183" s="5" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F183" s="26" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="H183" s="26" t="inlineStr">
         <is>
-          <t>1984</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -10455,17 +10455,17 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>comp_year_built_source</t>
+          <t>comp_year_built</t>
         </is>
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D184" s="26" t="inlineStr">
         <is>
-          <t>Where that year came from: the public record with its as-of, or the community registry (third-party market data). Blank alongside a blank year; a year with no source is rejected at validation.</t>
+          <t>Comp vintage where one is published: the public property record's year where it has one, else the community registry's. Blank means nobody published one, never that the community is new.</t>
         </is>
       </c>
       <c r="E184" s="5" t="inlineStr">
@@ -10475,7 +10475,7 @@
       </c>
       <c r="F184" s="26" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G184" s="26" t="inlineStr">
@@ -10485,7 +10485,7 @@
       </c>
       <c r="H184" s="26" t="inlineStr">
         <is>
-          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
+          <t>1984</t>
         </is>
       </c>
     </row>
@@ -10497,7 +10497,7 @@
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>nearby_community</t>
+          <t>comp_year_built_source</t>
         </is>
       </c>
       <c r="C185" s="5" t="inlineStr">
@@ -10507,7 +10507,7 @@
       </c>
       <c r="D185" s="26" t="inlineStr">
         <is>
-          <t>A tracked community inside the radius that is NOT a comp. Carried in the interchange file; the ~340-row table was taken off the page on 2026-09-28.</t>
+          <t>Where that year came from: the public record with its as-of, or the community registry (third-party market data). Blank alongside a blank year; a year with no source is rejected at validation.</t>
         </is>
       </c>
       <c r="E185" s="5" t="inlineStr">
@@ -10517,7 +10517,7 @@
       </c>
       <c r="F185" s="26" t="inlineStr">
         <is>
-          <t>Market context</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G185" s="26" t="inlineStr">
@@ -10527,7 +10527,7 @@
       </c>
       <c r="H185" s="26" t="inlineStr">
         <is>
-          <t>The Village at Lindsay Park Apartments</t>
+          <t>Maricopa County, AZ property record, as of 2026-10-05</t>
         </is>
       </c>
     </row>
@@ -10539,7 +10539,7 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>nearby_address</t>
+          <t>nearby_community</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
@@ -10549,7 +10549,7 @@
       </c>
       <c r="D186" s="26" t="inlineStr">
         <is>
-          <t>Its address, so the reader can place it.</t>
+          <t>A tracked community inside the radius that is NOT a comp. Carried in the interchange file; the ~340-row table was taken off the page on 2026-09-28.</t>
         </is>
       </c>
       <c r="E186" s="5" t="inlineStr">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="H186" s="26" t="inlineStr">
         <is>
-          <t>1441 S Lindsay Rd, Mesa, AZ 85204-6285</t>
+          <t>The Village at Lindsay Park Apartments</t>
         </is>
       </c>
     </row>
@@ -10581,22 +10581,22 @@
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>nearby_distance_mi</t>
+          <t>nearby_address</t>
         </is>
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D187" s="26" t="inlineStr">
         <is>
-          <t>Distance from the subject.</t>
+          <t>Its address, so the reader can place it.</t>
         </is>
       </c>
       <c r="E187" s="5" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F187" s="26" t="inlineStr">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="H187" s="26" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1441 S Lindsay Rd, Mesa, AZ 85204-6285</t>
         </is>
       </c>
     </row>
@@ -10623,22 +10623,22 @@
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>nearby_units</t>
+          <t>nearby_distance_mi</t>
         </is>
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D188" s="26" t="inlineStr">
         <is>
-          <t>Unit count. The registry's own count was seeded from licensed data exports, so the public demo withholds it and shows the public-record count instead where one exists (county property record, Florida DBPR apartment licence, City of Austin permit), with its source and as-of.</t>
+          <t>Distance from the subject.</t>
         </is>
       </c>
       <c r="E188" s="5" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F188" s="26" t="inlineStr">
@@ -10648,12 +10648,12 @@
       </c>
       <c r="G188" s="26" t="inlineStr">
         <is>
-          <t>Public record where one exists — A community's own unit count comes from a licensed data export, so the public demo holds it back; where a public record states a count (a county property record, a Florida DBPR apartment licence, a City of Austin permit), that count is shown with its source and as-of.</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H188" s="26" t="inlineStr">
         <is>
-          <t>256 — Maricopa County, AZ property record, as of 2026-10-05</t>
+          <t>0.9</t>
         </is>
       </c>
     </row>
@@ -10665,22 +10665,22 @@
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
-          <t>nearby_reason</t>
+          <t>nearby_units</t>
         </is>
       </c>
       <c r="C189" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D189" s="26" t="inlineStr">
         <is>
-          <t>Why it is not a comp: wrong product, vintage outside the band, no quoted rent, excluded by the tracker, or simply beyond the closest twenty. The field that answers 'why isn't the property across the street in your comp set?' for every community in the radius.</t>
+          <t>Unit count. The registry's own count was seeded from licensed data exports, so the public demo withholds it and shows the public-record count instead where one exists (county property record, Florida DBPR apartment licence, City of Austin permit), with its source and as-of.</t>
         </is>
       </c>
       <c r="E189" s="5" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F189" s="26" t="inlineStr">
@@ -10690,12 +10690,12 @@
       </c>
       <c r="G189" s="26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>Public record where one exists — A community's own unit count comes from a licensed data export, so the public demo holds it back; where a public record states a count (a county property record, a Florida DBPR apartment licence, a City of Austin permit), that count is shown with its source and as-of.</t>
         </is>
       </c>
       <c r="H189" s="26" t="inlineStr">
         <is>
-          <t>vintage 1997 is 16 years from the subject's 1981, outside the +/-10-year band</t>
+          <t>256 — Maricopa County, AZ property record, as of 2026-10-05</t>
         </is>
       </c>
     </row>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
-          <t>compset_vintage_footnote</t>
+          <t>nearby_reason</t>
         </is>
       </c>
       <c r="C190" s="5" t="inlineStr">
@@ -10717,7 +10717,7 @@
       </c>
       <c r="D190" s="26" t="inlineStr">
         <is>
-          <t>The disclosure on the detailed tiers: the band applied, and whether some communities carried no year and so could not be tested.</t>
+          <t>Why it is not a comp: wrong product, vintage outside the band, no quoted rent, excluded by the tracker, or simply beyond the closest twenty. The field that answers 'why isn't the property across the street in your comp set?' for every community in the radius.</t>
         </is>
       </c>
       <c r="E190" s="5" t="inlineStr">
@@ -10727,7 +10727,7 @@
       </c>
       <c r="F190" s="26" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Market context</t>
         </is>
       </c>
       <c r="G190" s="26" t="inlineStr">
@@ -10737,7 +10737,7 @@
       </c>
       <c r="H190" s="26" t="inlineStr">
         <is>
-          <t>Vintage filter: +/-10 years of the subject's year built.</t>
+          <t>vintage 1997 is 16 years from the subject's 1981, outside the +/-10-year band</t>
         </is>
       </c>
     </row>
@@ -10749,27 +10749,27 @@
       </c>
       <c r="B191" s="5" t="inlineStr">
         <is>
-          <t>comp_beds</t>
+          <t>compset_vintage_footnote</t>
         </is>
       </c>
       <c r="C191" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D191" s="26" t="inlineStr">
         <is>
-          <t>Bedrooms in the comp plan.</t>
+          <t>The disclosure on the detailed tiers: the band applied, and whether some communities carried no year and so could not be tested.</t>
         </is>
       </c>
       <c r="E191" s="5" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F191" s="26" t="inlineStr">
         <is>
-          <t>Comp set</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G191" s="26" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="H191" s="26" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>Vintage filter: +/-10 years of the subject's year built.</t>
         </is>
       </c>
     </row>
@@ -10791,7 +10791,7 @@
       </c>
       <c r="B192" s="5" t="inlineStr">
         <is>
-          <t>comp_baths</t>
+          <t>comp_beds</t>
         </is>
       </c>
       <c r="C192" s="5" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="D192" s="26" t="inlineStr">
         <is>
-          <t>Bathrooms in the comp plan.</t>
+          <t>Bedrooms in the comp plan.</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr">
@@ -10821,7 +10821,7 @@
       </c>
       <c r="H192" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1.0</t>
         </is>
       </c>
     </row>
@@ -10833,7 +10833,7 @@
       </c>
       <c r="B193" s="5" t="inlineStr">
         <is>
-          <t>comp_sqft</t>
+          <t>comp_baths</t>
         </is>
       </c>
       <c r="C193" s="5" t="inlineStr">
@@ -10843,7 +10843,7 @@
       </c>
       <c r="D193" s="26" t="inlineStr">
         <is>
-          <t>Square footage of the comp plan.</t>
+          <t>Bathrooms in the comp plan.</t>
         </is>
       </c>
       <c r="E193" s="5" t="inlineStr">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="H193" s="26" t="inlineStr">
         <is>
-          <t>688.0</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -10875,17 +10875,17 @@
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>comp_asking_rent</t>
+          <t>comp_sqft</t>
         </is>
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D194" s="26" t="inlineStr">
         <is>
-          <t>Advertised asking rent.</t>
+          <t>Square footage of the comp plan.</t>
         </is>
       </c>
       <c r="E194" s="5" t="inlineStr">
@@ -10895,7 +10895,7 @@
       </c>
       <c r="F194" s="26" t="inlineStr">
         <is>
-          <t>Market rent evidence</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G194" s="26" t="inlineStr">
@@ -10905,7 +10905,7 @@
       </c>
       <c r="H194" s="26" t="inlineStr">
         <is>
-          <t>$1,200</t>
+          <t>688.0</t>
         </is>
       </c>
     </row>
@@ -10917,7 +10917,7 @@
       </c>
       <c r="B195" s="5" t="inlineStr">
         <is>
-          <t>comp_concession</t>
+          <t>comp_asking_rent</t>
         </is>
       </c>
       <c r="C195" s="5" t="inlineStr">
@@ -10927,7 +10927,7 @@
       </c>
       <c r="D195" s="26" t="inlineStr">
         <is>
-          <t>Monthly value of the advertised concession.</t>
+          <t>Advertised asking rent.</t>
         </is>
       </c>
       <c r="E195" s="5" t="inlineStr">
@@ -10937,7 +10937,7 @@
       </c>
       <c r="F195" s="26" t="inlineStr">
         <is>
-          <t>Concession assumption</t>
+          <t>Market rent evidence</t>
         </is>
       </c>
       <c r="G195" s="26" t="inlineStr">
@@ -10947,7 +10947,7 @@
       </c>
       <c r="H195" s="26" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$1,200</t>
         </is>
       </c>
     </row>
@@ -10959,7 +10959,7 @@
       </c>
       <c r="B196" s="5" t="inlineStr">
         <is>
-          <t>comp_net_effective_rent</t>
+          <t>comp_concession</t>
         </is>
       </c>
       <c r="C196" s="5" t="inlineStr">
@@ -10969,17 +10969,17 @@
       </c>
       <c r="D196" s="26" t="inlineStr">
         <is>
-          <t>Asking rent less the amortized concession. Stated on every row — a concession-blind comp set is the most common way a rent assumption goes wrong.</t>
+          <t>Monthly value of the advertised concession.</t>
         </is>
       </c>
       <c r="E196" s="5" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F196" s="26" t="inlineStr">
         <is>
-          <t>Market rent evidence</t>
+          <t>Concession assumption</t>
         </is>
       </c>
       <c r="G196" s="26" t="inlineStr">
@@ -10989,7 +10989,7 @@
       </c>
       <c r="H196" s="26" t="inlineStr">
         <is>
-          <t>$1,200</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -11001,7 +11001,7 @@
       </c>
       <c r="B197" s="5" t="inlineStr">
         <is>
-          <t>comp_asking_psf</t>
+          <t>comp_net_effective_rent</t>
         </is>
       </c>
       <c r="C197" s="5" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="D197" s="26" t="inlineStr">
         <is>
-          <t>Asking rent per square foot.</t>
+          <t>Asking rent less the amortized concession. Stated on every row — a concession-blind comp set is the most common way a rent assumption goes wrong.</t>
         </is>
       </c>
       <c r="E197" s="5" t="inlineStr">
@@ -11021,7 +11021,7 @@
       </c>
       <c r="F197" s="26" t="inlineStr">
         <is>
-          <t>Comp set</t>
+          <t>Market rent evidence</t>
         </is>
       </c>
       <c r="G197" s="26" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="H197" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>$1,200</t>
         </is>
       </c>
     </row>
@@ -11043,27 +11043,27 @@
       </c>
       <c r="B198" s="5" t="inlineStr">
         <is>
-          <t>comp_occupancy</t>
+          <t>comp_asking_psf</t>
         </is>
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D198" s="26" t="inlineStr">
         <is>
-          <t>Occupancy where the source published it.</t>
+          <t>Asking rent per square foot.</t>
         </is>
       </c>
       <c r="E198" s="5" t="inlineStr">
         <is>
-          <t>Operator's own weekly rent scrape</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F198" s="26" t="inlineStr">
         <is>
-          <t>Market context</t>
+          <t>Comp set</t>
         </is>
       </c>
       <c r="G198" s="26" t="inlineStr">
@@ -11085,17 +11085,17 @@
       </c>
       <c r="B199" s="5" t="inlineStr">
         <is>
-          <t>comp_as_of</t>
+          <t>comp_occupancy</t>
         </is>
       </c>
       <c r="C199" s="5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D199" s="26" t="inlineStr">
         <is>
-          <t>When the row was scraped.</t>
+          <t>Occupancy where the source published it.</t>
         </is>
       </c>
       <c r="E199" s="5" t="inlineStr">
@@ -11105,7 +11105,7 @@
       </c>
       <c r="F199" s="26" t="inlineStr">
         <is>
-          <t>Reference only — not a model input</t>
+          <t>Market context</t>
         </is>
       </c>
       <c r="G199" s="26" t="inlineStr">
@@ -11115,7 +11115,7 @@
       </c>
       <c r="H199" s="26" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -11127,17 +11127,17 @@
       </c>
       <c r="B200" s="5" t="inlineStr">
         <is>
-          <t>comp_source</t>
+          <t>comp_as_of</t>
         </is>
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="D200" s="26" t="inlineStr">
         <is>
-          <t>Always the operator's own weekly scrape. Licensed comp feeds are excluded by design and cannot be represented in this schema.</t>
+          <t>When the row was scraped.</t>
         </is>
       </c>
       <c r="E200" s="5" t="inlineStr">
@@ -11157,7 +11157,7 @@
       </c>
       <c r="H200" s="26" t="inlineStr">
         <is>
-          <t>own weekly scrape</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -11169,27 +11169,27 @@
       </c>
       <c r="B201" s="5" t="inlineStr">
         <is>
-          <t>compset_avg_asking</t>
+          <t>comp_source</t>
         </is>
       </c>
       <c r="C201" s="5" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D201" s="26" t="inlineStr">
         <is>
-          <t>Average asking rent across the comp set.</t>
+          <t>Always the operator's own weekly scrape. Licensed comp feeds are excluded by design and cannot be represented in this schema.</t>
         </is>
       </c>
       <c r="E201" s="5" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Operator's own weekly rent scrape</t>
         </is>
       </c>
       <c r="F201" s="26" t="inlineStr">
         <is>
-          <t>Market rent benchmark</t>
+          <t>Reference only — not a model input</t>
         </is>
       </c>
       <c r="G201" s="26" t="inlineStr">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="H201" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>own weekly scrape</t>
         </is>
       </c>
     </row>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="B202" s="5" t="inlineStr">
         <is>
-          <t>compset_avg_net_effective</t>
+          <t>compset_avg_asking</t>
         </is>
       </c>
       <c r="C202" s="5" t="inlineStr">
@@ -11221,7 +11221,7 @@
       </c>
       <c r="D202" s="26" t="inlineStr">
         <is>
-          <t>Average net effective rent across the comp set.</t>
+          <t>Average asking rent across the comp set.</t>
         </is>
       </c>
       <c r="E202" s="5" t="inlineStr">
@@ -11253,95 +11253,95 @@
       </c>
       <c r="B203" s="5" t="inlineStr">
         <is>
+          <t>compset_avg_net_effective</t>
+        </is>
+      </c>
+      <c r="C203" s="5" t="inlineStr">
+        <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="D203" s="26" t="inlineStr">
+        <is>
+          <t>Average net effective rent across the comp set.</t>
+        </is>
+      </c>
+      <c r="E203" s="5" t="inlineStr">
+        <is>
+          <t>Derived by the pipeline</t>
+        </is>
+      </c>
+      <c r="F203" s="26" t="inlineStr">
+        <is>
+          <t>Market rent benchmark</t>
+        </is>
+      </c>
+      <c r="G203" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H203" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="5" t="inlineStr">
+        <is>
+          <t>Comps</t>
+        </is>
+      </c>
+      <c r="B204" s="5" t="inlineStr">
+        <is>
           <t>subject_vs_compset_spread</t>
         </is>
       </c>
-      <c r="C203" s="5" t="inlineStr">
+      <c r="C204" s="5" t="inlineStr">
         <is>
           <t>percent</t>
         </is>
       </c>
-      <c r="D203" s="26" t="inlineStr">
+      <c r="D204" s="26" t="inlineStr">
         <is>
           <t>Subject market rent over comp-set net effective, less one.</t>
         </is>
       </c>
-      <c r="E203" s="5" t="inlineStr">
+      <c r="E204" s="5" t="inlineStr">
         <is>
           <t>Derived by the pipeline</t>
         </is>
       </c>
-      <c r="F203" s="26" t="inlineStr">
+      <c r="F204" s="26" t="inlineStr">
         <is>
           <t>Rent positioning</t>
         </is>
       </c>
-      <c r="G203" s="26" t="inlineStr">
+      <c r="G204" s="26" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H203" s="26" t="inlineStr">
+      <c r="H204" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="4" t="inlineStr">
+    <row r="205">
+      <c r="A205" s="4" t="inlineStr">
         <is>
           <t>Demand</t>
         </is>
       </c>
-      <c r="B204" s="4" t="n"/>
-      <c r="C204" s="4" t="n"/>
-      <c r="D204" s="4" t="n"/>
-      <c r="E204" s="4" t="n"/>
-      <c r="F204" s="4" t="n"/>
-      <c r="G204" s="4" t="n"/>
-      <c r="H204" s="4" t="n"/>
-    </row>
-    <row r="205">
-      <c r="A205" s="5" t="inlineStr">
-        <is>
-          <t>Demand</t>
-        </is>
-      </c>
-      <c r="B205" s="5" t="inlineStr">
-        <is>
-          <t>demand_ring</t>
-        </is>
-      </c>
-      <c r="C205" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D205" s="26" t="inlineStr">
-        <is>
-          <t>Drive-ring the row describes: 1, 3, 5, or 10 miles, or the MSA.</t>
-        </is>
-      </c>
-      <c r="E205" s="5" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F205" s="26" t="inlineStr">
-        <is>
-          <t>Market summary</t>
-        </is>
-      </c>
-      <c r="G205" s="26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H205" s="26" t="inlineStr">
-        <is>
-          <t>1 mi</t>
-        </is>
-      </c>
+      <c r="B205" s="4" t="n"/>
+      <c r="C205" s="4" t="n"/>
+      <c r="D205" s="4" t="n"/>
+      <c r="E205" s="4" t="n"/>
+      <c r="F205" s="4" t="n"/>
+      <c r="G205" s="4" t="n"/>
+      <c r="H205" s="4" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="5" t="inlineStr">
@@ -11351,22 +11351,22 @@
       </c>
       <c r="B206" s="5" t="inlineStr">
         <is>
-          <t>demand_population</t>
+          <t>demand_ring</t>
         </is>
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D206" s="26" t="inlineStr">
         <is>
-          <t>Population in the ring.</t>
+          <t>Drive-ring the row describes: 1, 3, 5, or 10 miles, or the MSA.</t>
         </is>
       </c>
       <c r="E206" s="5" t="inlineStr">
         <is>
-          <t>Public demographic data</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F206" s="26" t="inlineStr">
@@ -11381,7 +11381,7 @@
       </c>
       <c r="H206" s="26" t="inlineStr">
         <is>
-          <t>20,298</t>
+          <t>1 mi</t>
         </is>
       </c>
     </row>
@@ -11393,7 +11393,7 @@
       </c>
       <c r="B207" s="5" t="inlineStr">
         <is>
-          <t>demand_households</t>
+          <t>demand_population</t>
         </is>
       </c>
       <c r="C207" s="5" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="D207" s="26" t="inlineStr">
         <is>
-          <t>Households in the ring.</t>
+          <t>Population in the ring.</t>
         </is>
       </c>
       <c r="E207" s="5" t="inlineStr">
@@ -11423,7 +11423,7 @@
       </c>
       <c r="H207" s="26" t="inlineStr">
         <is>
-          <t>7,711</t>
+          <t>20,298</t>
         </is>
       </c>
     </row>
@@ -11435,17 +11435,17 @@
       </c>
       <c r="B208" s="5" t="inlineStr">
         <is>
-          <t>demand_median_income</t>
+          <t>demand_households</t>
         </is>
       </c>
       <c r="C208" s="5" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D208" s="26" t="inlineStr">
         <is>
-          <t>Median household income in the ring.</t>
+          <t>Households in the ring.</t>
         </is>
       </c>
       <c r="E208" s="5" t="inlineStr">
@@ -11455,7 +11455,7 @@
       </c>
       <c r="F208" s="26" t="inlineStr">
         <is>
-          <t>Affordability check</t>
+          <t>Market summary</t>
         </is>
       </c>
       <c r="G208" s="26" t="inlineStr">
@@ -11465,7 +11465,7 @@
       </c>
       <c r="H208" s="26" t="inlineStr">
         <is>
-          <t>$79,731</t>
+          <t>7,711</t>
         </is>
       </c>
     </row>
@@ -11477,17 +11477,17 @@
       </c>
       <c r="B209" s="5" t="inlineStr">
         <is>
-          <t>demand_jobs</t>
+          <t>demand_median_income</t>
         </is>
       </c>
       <c r="C209" s="5" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D209" s="26" t="inlineStr">
         <is>
-          <t>Jobs located in the ring.</t>
+          <t>Median household income in the ring.</t>
         </is>
       </c>
       <c r="E209" s="5" t="inlineStr">
@@ -11497,7 +11497,7 @@
       </c>
       <c r="F209" s="26" t="inlineStr">
         <is>
-          <t>Market summary</t>
+          <t>Affordability check</t>
         </is>
       </c>
       <c r="G209" s="26" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="H209" s="26" t="inlineStr">
         <is>
-          <t>5,237</t>
+          <t>$79,731</t>
         </is>
       </c>
     </row>
@@ -11519,17 +11519,17 @@
       </c>
       <c r="B210" s="5" t="inlineStr">
         <is>
-          <t>demand_pop_growth_5yr</t>
+          <t>demand_jobs</t>
         </is>
       </c>
       <c r="C210" s="5" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D210" s="26" t="inlineStr">
         <is>
-          <t>Five-year population growth in the ring.</t>
+          <t>Jobs located in the ring.</t>
         </is>
       </c>
       <c r="E210" s="5" t="inlineStr">
@@ -11539,7 +11539,7 @@
       </c>
       <c r="F210" s="26" t="inlineStr">
         <is>
-          <t>Growth assumption evidence</t>
+          <t>Market summary</t>
         </is>
       </c>
       <c r="G210" s="26" t="inlineStr">
@@ -11549,7 +11549,7 @@
       </c>
       <c r="H210" s="26" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>5,237</t>
         </is>
       </c>
     </row>
@@ -11561,95 +11561,95 @@
       </c>
       <c r="B211" s="5" t="inlineStr">
         <is>
+          <t>demand_pop_growth_5yr</t>
+        </is>
+      </c>
+      <c r="C211" s="5" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D211" s="26" t="inlineStr">
+        <is>
+          <t>Five-year population growth in the ring.</t>
+        </is>
+      </c>
+      <c r="E211" s="5" t="inlineStr">
+        <is>
+          <t>Public demographic data</t>
+        </is>
+      </c>
+      <c r="F211" s="26" t="inlineStr">
+        <is>
+          <t>Growth assumption evidence</t>
+        </is>
+      </c>
+      <c r="G211" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H211" s="26" t="inlineStr">
+        <is>
+          <t>-2.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="5" t="inlineStr">
+        <is>
+          <t>Demand</t>
+        </is>
+      </c>
+      <c r="B212" s="5" t="inlineStr">
+        <is>
           <t>demand_renter_share</t>
         </is>
       </c>
-      <c r="C211" s="5" t="inlineStr">
+      <c r="C212" s="5" t="inlineStr">
         <is>
           <t>percent</t>
         </is>
       </c>
-      <c r="D211" s="26" t="inlineStr">
+      <c r="D212" s="26" t="inlineStr">
         <is>
           <t>Share of ring households that rent.</t>
         </is>
       </c>
-      <c r="E211" s="5" t="inlineStr">
+      <c r="E212" s="5" t="inlineStr">
         <is>
           <t>Public demographic data</t>
         </is>
       </c>
-      <c r="F211" s="26" t="inlineStr">
+      <c r="F212" s="26" t="inlineStr">
         <is>
           <t>Demand context</t>
         </is>
       </c>
-      <c r="G211" s="26" t="inlineStr">
+      <c r="G212" s="26" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H211" s="26" t="inlineStr">
+      <c r="H212" s="26" t="inlineStr">
         <is>
           <t>43.4%</t>
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="4" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="4" t="inlineStr">
         <is>
           <t>Supply</t>
         </is>
       </c>
-      <c r="B212" s="4" t="n"/>
-      <c r="C212" s="4" t="n"/>
-      <c r="D212" s="4" t="n"/>
-      <c r="E212" s="4" t="n"/>
-      <c r="F212" s="4" t="n"/>
-      <c r="G212" s="4" t="n"/>
-      <c r="H212" s="4" t="n"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="5" t="inlineStr">
-        <is>
-          <t>Supply</t>
-        </is>
-      </c>
-      <c r="B213" s="5" t="inlineStr">
-        <is>
-          <t>supply_ring</t>
-        </is>
-      </c>
-      <c r="C213" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D213" s="26" t="inlineStr">
-        <is>
-          <t>Ring the supply row describes.</t>
-        </is>
-      </c>
-      <c r="E213" s="5" t="inlineStr">
-        <is>
-          <t>Derived by the pipeline</t>
-        </is>
-      </c>
-      <c r="F213" s="26" t="inlineStr">
-        <is>
-          <t>Competing supply</t>
-        </is>
-      </c>
-      <c r="G213" s="26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H213" s="26" t="inlineStr">
-        <is>
-          <t>1 mi</t>
-        </is>
-      </c>
+      <c r="B213" s="4" t="n"/>
+      <c r="C213" s="4" t="n"/>
+      <c r="D213" s="4" t="n"/>
+      <c r="E213" s="4" t="n"/>
+      <c r="F213" s="4" t="n"/>
+      <c r="G213" s="4" t="n"/>
+      <c r="H213" s="4" t="n"/>
     </row>
     <row r="214">
       <c r="A214" s="5" t="inlineStr">
@@ -11659,7 +11659,7 @@
       </c>
       <c r="B214" s="5" t="inlineStr">
         <is>
-          <t>supply_stage</t>
+          <t>supply_ring</t>
         </is>
       </c>
       <c r="C214" s="5" t="inlineStr">
@@ -11669,12 +11669,12 @@
       </c>
       <c r="D214" s="26" t="inlineStr">
         <is>
-          <t>Entitlement, permitted, under construction, or delivered in the last 24 months. Stage is stated because entitled units and delivered units are not the same risk.</t>
+          <t>Ring the supply row describes.</t>
         </is>
       </c>
       <c r="E214" s="5" t="inlineStr">
         <is>
-          <t>Public permit / entitlement records</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F214" s="26" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="H214" s="26" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>1 mi</t>
         </is>
       </c>
     </row>
@@ -11701,17 +11701,17 @@
       </c>
       <c r="B215" s="5" t="inlineStr">
         <is>
-          <t>supply_projects</t>
+          <t>supply_stage</t>
         </is>
       </c>
       <c r="C215" s="5" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D215" s="26" t="inlineStr">
         <is>
-          <t>Projects at that ring and stage.</t>
+          <t>Entitlement, permitted, under construction, or delivered in the last 24 months. Stage is stated because entitled units and delivered units are not the same risk.</t>
         </is>
       </c>
       <c r="E215" s="5" t="inlineStr">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="H215" s="26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Entitlement</t>
         </is>
       </c>
     </row>
@@ -11743,7 +11743,7 @@
       </c>
       <c r="B216" s="5" t="inlineStr">
         <is>
-          <t>supply_units</t>
+          <t>supply_projects</t>
         </is>
       </c>
       <c r="C216" s="5" t="inlineStr">
@@ -11753,7 +11753,7 @@
       </c>
       <c r="D216" s="26" t="inlineStr">
         <is>
-          <t>Units at that ring and stage.</t>
+          <t>Projects at that ring and stage.</t>
         </is>
       </c>
       <c r="E216" s="5" t="inlineStr">
@@ -11763,7 +11763,7 @@
       </c>
       <c r="F216" s="26" t="inlineStr">
         <is>
-          <t>Competing supply / absorption</t>
+          <t>Competing supply</t>
         </is>
       </c>
       <c r="G216" s="26" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="H216" s="26" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="B217" s="5" t="inlineStr">
         <is>
-          <t>supply_ring_total_units</t>
+          <t>supply_units</t>
         </is>
       </c>
       <c r="C217" s="5" t="inlineStr">
@@ -11795,17 +11795,17 @@
       </c>
       <c r="D217" s="26" t="inlineStr">
         <is>
-          <t>All pipeline units in the ring across stages.</t>
+          <t>Units at that ring and stage.</t>
         </is>
       </c>
       <c r="E217" s="5" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Public permit / entitlement records</t>
         </is>
       </c>
       <c r="F217" s="26" t="inlineStr">
         <is>
-          <t>Competing supply</t>
+          <t>Competing supply / absorption</t>
         </is>
       </c>
       <c r="G217" s="26" t="inlineStr">
@@ -11815,7 +11815,7 @@
       </c>
       <c r="H217" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>72</t>
         </is>
       </c>
     </row>
@@ -11827,17 +11827,17 @@
       </c>
       <c r="B218" s="5" t="inlineStr">
         <is>
-          <t>supply_pct_of_ring_stock</t>
+          <t>supply_ring_total_units</t>
         </is>
       </c>
       <c r="C218" s="5" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D218" s="26" t="inlineStr">
         <is>
-          <t>Pipeline units as a share of the ring's existing stock, where stock is known.</t>
+          <t>All pipeline units in the ring across stages.</t>
         </is>
       </c>
       <c r="E218" s="5" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="F218" s="26" t="inlineStr">
         <is>
-          <t>Supply pressure</t>
+          <t>Competing supply</t>
         </is>
       </c>
       <c r="G218" s="26" t="inlineStr">
@@ -11869,27 +11869,27 @@
       </c>
       <c r="B219" s="5" t="inlineStr">
         <is>
-          <t>supply_project_name</t>
+          <t>supply_pct_of_ring_stock</t>
         </is>
       </c>
       <c r="C219" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="D219" s="26" t="inlineStr">
         <is>
-          <t>One development inside three miles, named. The ring rows say how many projects were counted; these say which ones.</t>
+          <t>Pipeline units as a share of the ring's existing stock, where stock is known.</t>
         </is>
       </c>
       <c r="E219" s="5" t="inlineStr">
         <is>
-          <t>Public permit / entitlement records</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F219" s="26" t="inlineStr">
         <is>
-          <t>Competing supply</t>
+          <t>Supply pressure</t>
         </is>
       </c>
       <c r="G219" s="26" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="H219" s="26" t="inlineStr">
         <is>
-          <t>Reed Park Residences</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -11911,22 +11911,22 @@
       </c>
       <c r="B220" s="5" t="inlineStr">
         <is>
-          <t>supply_project_miles</t>
+          <t>supply_project_name</t>
         </is>
       </c>
       <c r="C220" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D220" s="26" t="inlineStr">
         <is>
-          <t>Distance from the subject, at the nearest record any lifecycle layer carried.</t>
+          <t>One development inside three miles, named. The ring rows say how many projects were counted; these say which ones.</t>
         </is>
       </c>
       <c r="E220" s="5" t="inlineStr">
         <is>
-          <t>Derived by the pipeline</t>
+          <t>Public permit / entitlement records</t>
         </is>
       </c>
       <c r="F220" s="26" t="inlineStr">
@@ -11941,7 +11941,7 @@
       </c>
       <c r="H220" s="26" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>Reed Park Residences</t>
         </is>
       </c>
     </row>
@@ -11953,22 +11953,22 @@
       </c>
       <c r="B221" s="5" t="inlineStr">
         <is>
-          <t>supply_project_stage</t>
+          <t>supply_project_miles</t>
         </is>
       </c>
       <c r="C221" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D221" s="26" t="inlineStr">
         <is>
-          <t>The furthest tracked stage the pipeline shows for that development — the stage it was counted at.</t>
+          <t>Distance from the subject, at the nearest record any lifecycle layer carried.</t>
         </is>
       </c>
       <c r="E221" s="5" t="inlineStr">
         <is>
-          <t>Public permit / entitlement records</t>
+          <t>Derived by the pipeline</t>
         </is>
       </c>
       <c r="F221" s="26" t="inlineStr">
@@ -11983,7 +11983,7 @@
       </c>
       <c r="H221" s="26" t="inlineStr">
         <is>
-          <t>Entitlement</t>
+          <t>0.9</t>
         </is>
       </c>
     </row>
@@ -11995,17 +11995,17 @@
       </c>
       <c r="B222" s="5" t="inlineStr">
         <is>
-          <t>supply_project_units</t>
+          <t>supply_project_stage</t>
         </is>
       </c>
       <c r="C222" s="5" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D222" s="26" t="inlineStr">
         <is>
-          <t>Units where a layer stated them. Blank means the source did not state a count, never zero.</t>
+          <t>The furthest tracked stage the pipeline shows for that development — the stage it was counted at.</t>
         </is>
       </c>
       <c r="E222" s="5" t="inlineStr">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="F222" s="26" t="inlineStr">
         <is>
-          <t>Competing supply / absorption</t>
+          <t>Competing supply</t>
         </is>
       </c>
       <c r="G222" s="26" t="inlineStr">
@@ -12025,7 +12025,7 @@
       </c>
       <c r="H222" s="26" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>Entitlement</t>
         </is>
       </c>
     </row>
@@ -12037,17 +12037,17 @@
       </c>
       <c r="B223" s="5" t="inlineStr">
         <is>
-          <t>supply_project_product</t>
+          <t>supply_project_units</t>
         </is>
       </c>
       <c r="C223" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="D223" s="26" t="inlineStr">
         <is>
-          <t>Product the pipeline records for the development.</t>
+          <t>Units where a layer stated them. Blank means the source did not state a count, never zero.</t>
         </is>
       </c>
       <c r="E223" s="5" t="inlineStr">
@@ -12057,7 +12057,7 @@
       </c>
       <c r="F223" s="26" t="inlineStr">
         <is>
-          <t>Competing supply</t>
+          <t>Competing supply / absorption</t>
         </is>
       </c>
       <c r="G223" s="26" t="inlineStr">
@@ -12067,7 +12067,7 @@
       </c>
       <c r="H223" s="26" t="inlineStr">
         <is>
-          <t>multifamily</t>
+          <t>72</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="B224" s="5" t="inlineStr">
         <is>
-          <t>supply_project_address</t>
+          <t>supply_project_product</t>
         </is>
       </c>
       <c r="C224" s="5" t="inlineStr">
@@ -12089,7 +12089,7 @@
       </c>
       <c r="D224" s="26" t="inlineStr">
         <is>
-          <t>Street address where a layer carried one.</t>
+          <t>Product the pipeline records for the development.</t>
         </is>
       </c>
       <c r="E224" s="5" t="inlineStr">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="H224" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>multifamily</t>
         </is>
       </c>
     </row>
@@ -12121,7 +12121,7 @@
       </c>
       <c r="B225" s="5" t="inlineStr">
         <is>
-          <t>supply_project_city</t>
+          <t>supply_project_address</t>
         </is>
       </c>
       <c r="C225" s="5" t="inlineStr">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="D225" s="26" t="inlineStr">
         <is>
-          <t>City where a layer carried one.</t>
+          <t>Street address where a layer carried one.</t>
         </is>
       </c>
       <c r="E225" s="5" t="inlineStr">
@@ -12163,17 +12163,17 @@
       </c>
       <c r="B226" s="5" t="inlineStr">
         <is>
-          <t>supply_project_acres</t>
+          <t>supply_project_city</t>
         </is>
       </c>
       <c r="C226" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D226" s="26" t="inlineStr">
         <is>
-          <t>Site acreage where a layer carried one.</t>
+          <t>City where a layer carried one.</t>
         </is>
       </c>
       <c r="E226" s="5" t="inlineStr">
@@ -12193,7 +12193,7 @@
       </c>
       <c r="H226" s="26" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -12205,17 +12205,17 @@
       </c>
       <c r="B227" s="5" t="inlineStr">
         <is>
-          <t>supply_project_developer</t>
+          <t>supply_project_acres</t>
         </is>
       </c>
       <c r="C227" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D227" s="26" t="inlineStr">
         <is>
-          <t>Developer where a layer named one.</t>
+          <t>Site acreage where a layer carried one.</t>
         </is>
       </c>
       <c r="E227" s="5" t="inlineStr">
@@ -12235,7 +12235,7 @@
       </c>
       <c r="H227" s="26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3.2</t>
         </is>
       </c>
     </row>
@@ -12247,17 +12247,17 @@
       </c>
       <c r="B228" s="5" t="inlineStr">
         <is>
-          <t>supply_project_filed</t>
+          <t>supply_project_developer</t>
         </is>
       </c>
       <c r="C228" s="5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D228" s="26" t="inlineStr">
         <is>
-          <t>Earliest filing date across the layers the development appears on.</t>
+          <t>Developer where a layer named one.</t>
         </is>
       </c>
       <c r="E228" s="5" t="inlineStr">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="H228" s="26" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>—</t>
         </is>
       </c>
     </row>
@@ -12289,7 +12289,7 @@
       </c>
       <c r="B229" s="5" t="inlineStr">
         <is>
-          <t>supply_project_latest</t>
+          <t>supply_project_filed</t>
         </is>
       </c>
       <c r="C229" s="5" t="inlineStr">
@@ -12299,7 +12299,7 @@
       </c>
       <c r="D229" s="26" t="inlineStr">
         <is>
-          <t>Latest activity date across those layers.</t>
+          <t>Earliest filing date across the layers the development appears on.</t>
         </is>
       </c>
       <c r="E229" s="5" t="inlineStr">
@@ -12331,95 +12331,95 @@
       </c>
       <c r="B230" s="5" t="inlineStr">
         <is>
+          <t>supply_project_latest</t>
+        </is>
+      </c>
+      <c r="C230" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="D230" s="26" t="inlineStr">
+        <is>
+          <t>Latest activity date across those layers.</t>
+        </is>
+      </c>
+      <c r="E230" s="5" t="inlineStr">
+        <is>
+          <t>Public permit / entitlement records</t>
+        </is>
+      </c>
+      <c r="F230" s="26" t="inlineStr">
+        <is>
+          <t>Competing supply</t>
+        </is>
+      </c>
+      <c r="G230" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H230" s="26" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="5" t="inlineStr">
+        <is>
+          <t>Supply</t>
+        </is>
+      </c>
+      <c r="B231" s="5" t="inlineStr">
+        <is>
           <t>supply_project_layers</t>
         </is>
       </c>
-      <c r="C230" s="5" t="inlineStr">
+      <c r="C231" s="5" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="D230" s="26" t="inlineStr">
+      <c r="D231" s="26" t="inlineStr">
         <is>
           <t>The pipeline layers the development appeared on. Layers are lifecycle views of the same market, so one development can appear on several and is counted once.</t>
         </is>
       </c>
-      <c r="E230" s="5" t="inlineStr">
+      <c r="E231" s="5" t="inlineStr">
         <is>
           <t>Public permit / entitlement records</t>
         </is>
       </c>
-      <c r="F230" s="26" t="inlineStr">
+      <c r="F231" s="26" t="inlineStr">
         <is>
           <t>Reference only — not a model input</t>
         </is>
       </c>
-      <c r="G230" s="26" t="inlineStr">
+      <c r="G231" s="26" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H230" s="26" t="inlineStr">
+      <c r="H231" s="26" t="inlineStr">
         <is>
           <t>1 entries</t>
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="4" t="inlineStr">
+    <row r="232">
+      <c r="A232" s="4" t="inlineStr">
         <is>
           <t>OM comparables</t>
         </is>
       </c>
-      <c r="B231" s="4" t="n"/>
-      <c r="C231" s="4" t="n"/>
-      <c r="D231" s="4" t="n"/>
-      <c r="E231" s="4" t="n"/>
-      <c r="F231" s="4" t="n"/>
-      <c r="G231" s="4" t="n"/>
-      <c r="H231" s="4" t="n"/>
-    </row>
-    <row r="232">
-      <c r="A232" s="5" t="inlineStr">
-        <is>
-          <t>OM comparables</t>
-        </is>
-      </c>
-      <c r="B232" s="5" t="inlineStr">
-        <is>
-          <t>om_rent_comp_community</t>
-        </is>
-      </c>
-      <c r="C232" s="5" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="D232" s="26" t="inlineStr">
-        <is>
-          <t>A rent comparable the memorandum states, by name; one row per comparable in the interchange.</t>
-        </is>
-      </c>
-      <c r="E232" s="5" t="inlineStr">
-        <is>
-          <t>Offering memorandum / marketing package</t>
-        </is>
-      </c>
-      <c r="F232" s="26" t="inlineStr">
-        <is>
-          <t>Rent comps (broker-stated)</t>
-        </is>
-      </c>
-      <c r="G232" s="26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H232" s="26" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="B232" s="4" t="n"/>
+      <c r="C232" s="4" t="n"/>
+      <c r="D232" s="4" t="n"/>
+      <c r="E232" s="4" t="n"/>
+      <c r="F232" s="4" t="n"/>
+      <c r="G232" s="4" t="n"/>
+      <c r="H232" s="4" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="5" t="inlineStr">
@@ -12429,17 +12429,17 @@
       </c>
       <c r="B233" s="5" t="inlineStr">
         <is>
-          <t>om_rent_comp_distance_mi</t>
+          <t>om_rent_comp_community</t>
         </is>
       </c>
       <c r="C233" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D233" s="26" t="inlineStr">
         <is>
-          <t>Distance from the subject as the memorandum states it.</t>
+          <t>A rent comparable the memorandum states, by name; one row per comparable in the interchange.</t>
         </is>
       </c>
       <c r="E233" s="5" t="inlineStr">
@@ -12471,17 +12471,17 @@
       </c>
       <c r="B234" s="5" t="inlineStr">
         <is>
-          <t>om_rent_comp_rent</t>
+          <t>om_rent_comp_distance_mi</t>
         </is>
       </c>
       <c r="C234" s="5" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D234" s="26" t="inlineStr">
         <is>
-          <t>The monthly rent figure the memorandum states for that comparable; its basis is on the row.</t>
+          <t>Distance from the subject as the memorandum states it.</t>
         </is>
       </c>
       <c r="E234" s="5" t="inlineStr">
@@ -12513,17 +12513,17 @@
       </c>
       <c r="B235" s="5" t="inlineStr">
         <is>
-          <t>om_sale_comp_property</t>
+          <t>om_rent_comp_rent</t>
         </is>
       </c>
       <c r="C235" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D235" s="26" t="inlineStr">
         <is>
-          <t>A whole-community sale comparable the memorandum cites, by name.</t>
+          <t>The monthly rent figure the memorandum states for that comparable; its basis is on the row.</t>
         </is>
       </c>
       <c r="E235" s="5" t="inlineStr">
@@ -12533,7 +12533,7 @@
       </c>
       <c r="F235" s="26" t="inlineStr">
         <is>
-          <t>Sale comps (institutional)</t>
+          <t>Rent comps (broker-stated)</t>
         </is>
       </c>
       <c r="G235" s="26" t="inlineStr">
@@ -12555,17 +12555,17 @@
       </c>
       <c r="B236" s="5" t="inlineStr">
         <is>
-          <t>om_sale_comp_price</t>
+          <t>om_sale_comp_property</t>
         </is>
       </c>
       <c r="C236" s="5" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>text</t>
         </is>
       </c>
       <c r="D236" s="26" t="inlineStr">
         <is>
-          <t>The stated sale price.</t>
+          <t>A whole-community sale comparable the memorandum cites, by name.</t>
         </is>
       </c>
       <c r="E236" s="5" t="inlineStr">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="B237" s="5" t="inlineStr">
         <is>
-          <t>om_sale_comp_price_per_unit</t>
+          <t>om_sale_comp_price</t>
         </is>
       </c>
       <c r="C237" s="5" t="inlineStr">
@@ -12607,7 +12607,7 @@
       </c>
       <c r="D237" s="26" t="inlineStr">
         <is>
-          <t>The stated price per unit.</t>
+          <t>The stated sale price.</t>
         </is>
       </c>
       <c r="E237" s="5" t="inlineStr">
@@ -12639,17 +12639,17 @@
       </c>
       <c r="B238" s="5" t="inlineStr">
         <is>
-          <t>om_sale_comp_cap_rate</t>
+          <t>om_sale_comp_price_per_unit</t>
         </is>
       </c>
       <c r="C238" s="5" t="inlineStr">
         <is>
-          <t>percent</t>
+          <t>currency</t>
         </is>
       </c>
       <c r="D238" s="26" t="inlineStr">
         <is>
-          <t>The stated cap rate, as a fraction.</t>
+          <t>The stated price per unit.</t>
         </is>
       </c>
       <c r="E238" s="5" t="inlineStr">
@@ -12681,35 +12681,77 @@
       </c>
       <c r="B239" s="5" t="inlineStr">
         <is>
+          <t>om_sale_comp_cap_rate</t>
+        </is>
+      </c>
+      <c r="C239" s="5" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
+      <c r="D239" s="26" t="inlineStr">
+        <is>
+          <t>The stated cap rate, as a fraction.</t>
+        </is>
+      </c>
+      <c r="E239" s="5" t="inlineStr">
+        <is>
+          <t>Offering memorandum / marketing package</t>
+        </is>
+      </c>
+      <c r="F239" s="26" t="inlineStr">
+        <is>
+          <t>Sale comps (institutional)</t>
+        </is>
+      </c>
+      <c r="G239" s="26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H239" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="5" t="inlineStr">
+        <is>
+          <t>OM comparables</t>
+        </is>
+      </c>
+      <c r="B240" s="5" t="inlineStr">
+        <is>
           <t>om_sale_comp_date</t>
         </is>
       </c>
-      <c r="C239" s="5" t="inlineStr">
+      <c r="C240" s="5" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
-      <c r="D239" s="26" t="inlineStr">
+      <c r="D240" s="26" t="inlineStr">
         <is>
           <t>The sale date as written.</t>
         </is>
       </c>
-      <c r="E239" s="5" t="inlineStr">
+      <c r="E240" s="5" t="inlineStr">
         <is>
           <t>Offering memorandum / marketing package</t>
         </is>
       </c>
-      <c r="F239" s="26" t="inlineStr">
+      <c r="F240" s="26" t="inlineStr">
         <is>
           <t>Sale comps (institutional)</t>
         </is>
       </c>
-      <c r="G239" s="26" t="inlineStr">
+      <c r="G240" s="26" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="H239" s="26" t="inlineStr">
+      <c r="H240" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
